--- a/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D670681C-9A86-4CFF-9464-9555340C4CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -237,8 +243,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,13 +307,1540 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.9139999999999996E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8051000000000009E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9758700000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22436320000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BDS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.7169999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.183E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1504000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1933899999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.1950000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2577000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6950999999999989E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.80442E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5239999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6727999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8626E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1253619</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5859999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3979999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0564E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0586199999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.4630000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.8302000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9685799999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22379499999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.7370000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7453999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8205999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2119598</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1087387407"/>
+        <c:axId val="1087393167"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1087387407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087393167"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087393167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087387407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5C4D782-24FE-6BA0-2C4E-0F028702A851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -345,7 +1878,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -379,6 +1912,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -413,9 +1947,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,11 +2123,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +2150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -623,22 +2158,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0005914</v>
+        <v>5.9139999999999996E-4</v>
       </c>
       <c r="D2">
-        <v>0.003805100000000001</v>
+        <v>3.8051000000000009E-3</v>
       </c>
       <c r="E2">
-        <v>0.02975870000000001</v>
+        <v>2.9758700000000009E-2</v>
       </c>
       <c r="F2">
-        <v>0.2243632</v>
+        <v>0.22436320000000001</v>
       </c>
       <c r="G2">
-        <v>0.06462960000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>6.4629600000000009E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -646,22 +2181,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0002717</v>
+        <v>2.7169999999999999E-4</v>
       </c>
       <c r="D3">
-        <v>0.001183</v>
+        <v>1.183E-3</v>
       </c>
       <c r="E3">
-        <v>0.0051504</v>
+        <v>5.1504000000000003E-3</v>
       </c>
       <c r="F3">
-        <v>0.0219339</v>
+        <v>2.1933899999999999E-2</v>
       </c>
       <c r="G3">
-        <v>0.00713475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>7.1347499999999996E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -669,22 +2204,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0004195</v>
+        <v>4.1950000000000001E-4</v>
       </c>
       <c r="D4">
-        <v>0.0012577</v>
+        <v>1.2577000000000001E-3</v>
       </c>
       <c r="E4">
-        <v>0.004695099999999999</v>
+        <v>4.6950999999999989E-3</v>
       </c>
       <c r="F4">
-        <v>0.0380442</v>
+        <v>3.80442E-2</v>
       </c>
       <c r="G4">
-        <v>0.011104125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1.1104124999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -692,22 +2227,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0004524</v>
+        <v>4.5239999999999999E-4</v>
       </c>
       <c r="D5">
-        <v>0.0026728</v>
+        <v>2.6727999999999999E-3</v>
       </c>
       <c r="E5">
-        <v>0.018626</v>
+        <v>1.8626E-2</v>
       </c>
       <c r="F5">
         <v>0.1253619</v>
       </c>
       <c r="G5">
-        <v>0.036778275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>3.6778274999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -715,22 +2250,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.0004586</v>
+        <v>4.5859999999999998E-4</v>
       </c>
       <c r="D6">
-        <v>0.001398</v>
+        <v>1.3979999999999999E-3</v>
       </c>
       <c r="E6">
-        <v>0.0050564</v>
+        <v>5.0564E-3</v>
       </c>
       <c r="F6">
-        <v>0.0205862</v>
+        <v>2.0586199999999999E-2</v>
       </c>
       <c r="G6">
-        <v>0.006874799999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>6.8747999999999986E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -738,22 +2273,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0006463</v>
+        <v>6.4630000000000004E-4</v>
       </c>
       <c r="D7">
-        <v>0.0038302</v>
+        <v>3.8302000000000002E-3</v>
       </c>
       <c r="E7">
-        <v>0.0296858</v>
+        <v>2.9685799999999998E-2</v>
       </c>
       <c r="F7">
-        <v>0.223795</v>
+        <v>0.22379499999999999</v>
       </c>
       <c r="G7">
-        <v>0.064489325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>6.4489325E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -761,22 +2296,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0005737</v>
+        <v>5.7370000000000001E-4</v>
       </c>
       <c r="D8">
-        <v>0.0037454</v>
+        <v>3.7453999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>0.028206</v>
+        <v>2.8205999999999998E-2</v>
       </c>
       <c r="F8">
         <v>0.2119598</v>
       </c>
       <c r="G8">
-        <v>0.06112122499999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>6.1121224999999987E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -784,22 +2319,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.0004062</v>
+        <v>4.0620000000000001E-4</v>
       </c>
       <c r="D9">
-        <v>0.0010988</v>
+        <v>1.0988E-3</v>
       </c>
       <c r="E9">
-        <v>0.0033801</v>
+        <v>3.3801E-3</v>
       </c>
       <c r="F9">
-        <v>0.0126698</v>
+        <v>1.26698E-2</v>
       </c>
       <c r="G9">
-        <v>0.004388725</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>4.3887249999999996E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,22 +2342,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0003114</v>
+        <v>3.1139999999999998E-4</v>
       </c>
       <c r="D10">
-        <v>0.0014929</v>
+        <v>1.4928999999999999E-3</v>
       </c>
       <c r="E10">
-        <v>0.006343300000000001</v>
+        <v>6.3433000000000014E-3</v>
       </c>
       <c r="F10">
-        <v>0.0269066</v>
+        <v>2.6906599999999999E-2</v>
       </c>
       <c r="G10">
-        <v>0.008763549999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>8.7635499999999984E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -830,22 +2365,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.0003051</v>
+        <v>3.0509999999999999E-4</v>
       </c>
       <c r="D11">
-        <v>0.0012741</v>
+        <v>1.2741E-3</v>
       </c>
       <c r="E11">
-        <v>0.0053764</v>
+        <v>5.3763999999999999E-3</v>
       </c>
       <c r="F11">
-        <v>0.0228973</v>
+        <v>2.2897299999999999E-2</v>
       </c>
       <c r="G11">
-        <v>0.007463225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>7.4632250000000004E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -853,22 +2388,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0003507</v>
+        <v>3.5070000000000001E-4</v>
       </c>
       <c r="D12">
-        <v>0.0013986</v>
+        <v>1.3986000000000001E-3</v>
       </c>
       <c r="E12">
-        <v>0.005228500000000001</v>
+        <v>5.2285000000000014E-3</v>
       </c>
       <c r="F12">
-        <v>0.0227903</v>
+        <v>2.2790299999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.007442025</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>7.4420249999999997E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -876,22 +2411,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0004394000000000001</v>
+        <v>4.3940000000000011E-4</v>
       </c>
       <c r="D13">
-        <v>0.0013513</v>
+        <v>1.3512999999999999E-3</v>
       </c>
       <c r="E13">
-        <v>0.004957</v>
+        <v>4.9569999999999996E-3</v>
       </c>
       <c r="F13">
-        <v>0.03903519999999999</v>
+        <v>3.9035199999999992E-2</v>
       </c>
       <c r="G13">
-        <v>0.011445725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1.1445725E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -899,22 +2434,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0004438</v>
+        <v>4.438E-4</v>
       </c>
       <c r="D14">
-        <v>0.001317</v>
+        <v>1.317E-3</v>
       </c>
       <c r="E14">
-        <v>0.0049015</v>
+        <v>4.9014999999999996E-3</v>
       </c>
       <c r="F14">
-        <v>0.03227380000000001</v>
+        <v>3.2273800000000012E-2</v>
       </c>
       <c r="G14">
-        <v>0.009734025000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>9.7340250000000021E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -922,22 +2457,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.0004275</v>
+        <v>4.2749999999999998E-4</v>
       </c>
       <c r="D15">
-        <v>0.0013331</v>
+        <v>1.3331E-3</v>
       </c>
       <c r="E15">
-        <v>0.0056214</v>
+        <v>5.6214000000000004E-3</v>
       </c>
       <c r="F15">
-        <v>0.0315685</v>
+        <v>3.1568499999999999E-2</v>
       </c>
       <c r="G15">
-        <v>0.009737625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>9.7376249999999998E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -945,22 +2480,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0004996</v>
+        <v>4.996E-4</v>
       </c>
       <c r="D16">
-        <v>0.0027619</v>
+        <v>2.7618999999999999E-3</v>
       </c>
       <c r="E16">
-        <v>0.0186439</v>
+        <v>1.8643900000000001E-2</v>
       </c>
       <c r="F16">
         <v>0.1260309</v>
       </c>
       <c r="G16">
-        <v>0.036984075</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>3.6984074999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -968,22 +2503,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0004639</v>
+        <v>4.639E-4</v>
       </c>
       <c r="D17">
-        <v>0.0028879</v>
+        <v>2.8879000000000001E-3</v>
       </c>
       <c r="E17">
-        <v>0.0178973</v>
+        <v>1.7897300000000001E-2</v>
       </c>
       <c r="F17">
-        <v>0.1143249</v>
+        <v>0.11432489999999999</v>
       </c>
       <c r="G17">
-        <v>0.0338935</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>3.38935E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -991,22 +2526,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0003618</v>
+        <v>3.6180000000000001E-4</v>
       </c>
       <c r="D18">
-        <v>0.0009571</v>
+        <v>9.5710000000000001E-4</v>
       </c>
       <c r="E18">
-        <v>0.003013</v>
+        <v>3.0130000000000001E-3</v>
       </c>
       <c r="F18">
-        <v>0.0107975</v>
+        <v>1.07975E-2</v>
       </c>
       <c r="G18">
-        <v>0.00378235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>3.7823499999999999E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1014,22 +2549,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0003118</v>
+        <v>3.1179999999999999E-4</v>
       </c>
       <c r="D19">
-        <v>0.0006669</v>
+        <v>6.669E-4</v>
       </c>
       <c r="E19">
-        <v>0.0024747</v>
+        <v>2.4746999999999998E-3</v>
       </c>
       <c r="F19">
-        <v>0.008995400000000001</v>
+        <v>8.9954000000000006E-3</v>
       </c>
       <c r="G19">
-        <v>0.0031122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>3.1121999999999999E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1037,22 +2572,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0004029</v>
+        <v>4.0289999999999998E-4</v>
       </c>
       <c r="D20">
-        <v>0.0011866</v>
+        <v>1.1865999999999999E-3</v>
       </c>
       <c r="E20">
-        <v>0.0038961</v>
+        <v>3.8961E-3</v>
       </c>
       <c r="F20">
-        <v>0.0147949</v>
+        <v>1.47949E-2</v>
       </c>
       <c r="G20">
-        <v>0.005070125000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>5.0701250000000008E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1060,22 +2595,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0004939</v>
+        <v>4.9390000000000002E-4</v>
       </c>
       <c r="D21">
-        <v>0.0014488</v>
+        <v>1.4488000000000001E-3</v>
       </c>
       <c r="E21">
-        <v>0.005144</v>
+        <v>5.1440000000000001E-3</v>
       </c>
       <c r="F21">
-        <v>0.0208315</v>
+        <v>2.0831499999999999E-2</v>
       </c>
       <c r="G21">
-        <v>0.006979550000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>6.979550000000001E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1083,22 +2618,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.0004522</v>
+        <v>4.5219999999999999E-4</v>
       </c>
       <c r="D22">
-        <v>0.0013975</v>
+        <v>1.3975000000000001E-3</v>
       </c>
       <c r="E22">
-        <v>0.0049699</v>
+        <v>4.9699000000000002E-3</v>
       </c>
       <c r="F22">
-        <v>0.0186989</v>
+        <v>1.8698900000000001E-2</v>
       </c>
       <c r="G22">
-        <v>0.006379625</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>6.3796249999999999E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1106,22 +2641,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0006191000000000001</v>
+        <v>6.1910000000000014E-4</v>
       </c>
       <c r="D23">
-        <v>0.0038284</v>
+        <v>3.8284E-3</v>
       </c>
       <c r="E23">
-        <v>0.0282388</v>
+        <v>2.8238800000000001E-2</v>
       </c>
       <c r="F23">
         <v>0.2121102</v>
       </c>
       <c r="G23">
-        <v>0.061199125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>6.1199125E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1129,22 +2664,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.0004171</v>
+        <v>4.171E-4</v>
       </c>
       <c r="D24">
-        <v>0.0012131</v>
+        <v>1.2130999999999999E-3</v>
       </c>
       <c r="E24">
-        <v>0.0036339</v>
+        <v>3.6338999999999998E-3</v>
       </c>
       <c r="F24">
-        <v>0.0134493</v>
+        <v>1.3449300000000001E-2</v>
       </c>
       <c r="G24">
-        <v>0.00467835</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>4.6783500000000004E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1152,22 +2687,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0004269</v>
+        <v>4.2690000000000002E-4</v>
       </c>
       <c r="D25">
-        <v>0.0012131</v>
+        <v>1.2130999999999999E-3</v>
       </c>
       <c r="E25">
-        <v>0.0034827</v>
+        <v>3.4827E-3</v>
       </c>
       <c r="F25">
-        <v>0.0136862</v>
+        <v>1.3686200000000001E-2</v>
       </c>
       <c r="G25">
-        <v>0.004702225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>4.702225E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1175,22 +2710,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.0004447</v>
+        <v>4.4470000000000002E-4</v>
       </c>
       <c r="D26">
-        <v>0.0012749</v>
+        <v>1.2749E-3</v>
       </c>
       <c r="E26">
-        <v>0.004038000000000001</v>
+        <v>4.0380000000000008E-3</v>
       </c>
       <c r="F26">
-        <v>0.0156348</v>
+        <v>1.5634800000000001E-2</v>
       </c>
       <c r="G26">
-        <v>0.0053481</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>5.3480999999999997E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1198,22 +2733,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0003541</v>
+        <v>3.5409999999999999E-4</v>
       </c>
       <c r="D27">
-        <v>0.0015437</v>
+        <v>1.5437000000000001E-3</v>
       </c>
       <c r="E27">
-        <v>0.006577899999999999</v>
+        <v>6.5778999999999994E-3</v>
       </c>
       <c r="F27">
-        <v>0.0277541</v>
+        <v>2.77541E-2</v>
       </c>
       <c r="G27">
-        <v>0.009057450000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>9.0574500000000016E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1221,22 +2756,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0003646</v>
+        <v>3.6460000000000003E-4</v>
       </c>
       <c r="D28">
-        <v>0.0015867</v>
+        <v>1.5866999999999999E-3</v>
       </c>
       <c r="E28">
-        <v>0.006358</v>
+        <v>6.3579999999999999E-3</v>
       </c>
       <c r="F28">
-        <v>0.0264056</v>
+        <v>2.6405600000000001E-2</v>
       </c>
       <c r="G28">
-        <v>0.008678725</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>8.678725E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1244,22 +2779,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.0003893000000000001</v>
+        <v>3.8930000000000008E-4</v>
       </c>
       <c r="D29">
-        <v>0.0014827</v>
+        <v>1.4827E-3</v>
       </c>
       <c r="E29">
-        <v>0.005843</v>
+        <v>5.8430000000000001E-3</v>
       </c>
       <c r="F29">
-        <v>0.0234511</v>
+        <v>2.3451099999999999E-2</v>
       </c>
       <c r="G29">
-        <v>0.007791525</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>7.7915249999999997E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1267,22 +2802,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0005120999999999999</v>
+        <v>5.1209999999999993E-4</v>
       </c>
       <c r="D30">
-        <v>0.001398</v>
+        <v>1.3979999999999999E-3</v>
       </c>
       <c r="E30">
-        <v>0.0051314</v>
+        <v>5.1314000000000004E-3</v>
       </c>
       <c r="F30">
-        <v>0.0328823</v>
+        <v>3.2882300000000003E-2</v>
       </c>
       <c r="G30">
-        <v>0.009980949999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>9.9809499999999989E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1290,22 +2825,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0004598</v>
+        <v>4.5980000000000001E-4</v>
       </c>
       <c r="D31">
-        <v>0.0014379</v>
+        <v>1.4379E-3</v>
       </c>
       <c r="E31">
-        <v>0.005847199999999999</v>
+        <v>5.8471999999999986E-3</v>
       </c>
       <c r="F31">
-        <v>0.0325215</v>
+        <v>3.2521500000000002E-2</v>
       </c>
       <c r="G31">
-        <v>0.0100666</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>1.00666E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1313,22 +2848,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0004541</v>
+        <v>4.5409999999999998E-4</v>
       </c>
       <c r="D32">
-        <v>0.0013855</v>
+        <v>1.3855E-3</v>
       </c>
       <c r="E32">
-        <v>0.0055382</v>
+        <v>5.5382000000000001E-3</v>
       </c>
       <c r="F32">
-        <v>0.0301725</v>
+        <v>3.0172500000000001E-2</v>
       </c>
       <c r="G32">
-        <v>0.009387575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>9.3875750000000004E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1336,22 +2871,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0005053999999999999</v>
+        <v>5.0539999999999992E-4</v>
       </c>
       <c r="D33">
-        <v>0.0029744</v>
+        <v>2.9743999999999999E-3</v>
       </c>
       <c r="E33">
-        <v>0.0183395</v>
+        <v>1.8339500000000002E-2</v>
       </c>
       <c r="F33">
         <v>0.1149911</v>
       </c>
       <c r="G33">
-        <v>0.0342026</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>3.42026E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1359,22 +2894,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0003438</v>
+        <v>3.4380000000000001E-4</v>
       </c>
       <c r="D34">
-        <v>0.0009783999999999999</v>
+        <v>9.7839999999999993E-4</v>
       </c>
       <c r="E34">
-        <v>0.0033655</v>
+        <v>3.3655E-3</v>
       </c>
       <c r="F34">
-        <v>0.012399</v>
+        <v>1.2399E-2</v>
       </c>
       <c r="G34">
-        <v>0.004271675000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>4.2716750000000008E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1382,22 +2917,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0003766</v>
+        <v>3.7659999999999999E-4</v>
       </c>
       <c r="D35">
-        <v>0.0013138</v>
+        <v>1.3138E-3</v>
       </c>
       <c r="E35">
-        <v>0.0029817</v>
+        <v>2.9816999999999999E-3</v>
       </c>
       <c r="F35">
-        <v>0.0112662</v>
+        <v>1.1266200000000001E-2</v>
       </c>
       <c r="G35">
-        <v>0.003984575</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>3.9845749999999997E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1405,22 +2940,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.0003968999999999999</v>
+        <v>3.9689999999999989E-4</v>
       </c>
       <c r="D36">
-        <v>0.0011502</v>
+        <v>1.1502000000000001E-3</v>
       </c>
       <c r="E36">
-        <v>0.0030831</v>
+        <v>3.0831000000000001E-3</v>
       </c>
       <c r="F36">
-        <v>0.0108686</v>
+        <v>1.0868600000000001E-2</v>
       </c>
       <c r="G36">
-        <v>0.0038747</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>3.8747E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1428,22 +2963,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0003399</v>
+        <v>3.3990000000000002E-4</v>
       </c>
       <c r="D37">
-        <v>0.0011378</v>
+        <v>1.1378E-3</v>
       </c>
       <c r="E37">
-        <v>0.004116399999999999</v>
+        <v>4.1163999999999992E-3</v>
       </c>
       <c r="F37">
-        <v>0.0210795</v>
+        <v>2.1079500000000001E-2</v>
       </c>
       <c r="G37">
-        <v>0.0066684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>6.6683999999999997E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1451,22 +2986,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0003416</v>
+        <v>3.4160000000000001E-4</v>
       </c>
       <c r="D38">
-        <v>0.0007455</v>
+        <v>7.4549999999999996E-4</v>
       </c>
       <c r="E38">
-        <v>0.0025635</v>
+        <v>2.5634999999999998E-3</v>
       </c>
       <c r="F38">
-        <v>0.009144099999999999</v>
+        <v>9.1440999999999988E-3</v>
       </c>
       <c r="G38">
-        <v>0.003198675</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>3.1986750000000002E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1474,22 +3009,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.0003249</v>
+        <v>3.2489999999999998E-4</v>
       </c>
       <c r="D39">
-        <v>0.0006692</v>
+        <v>6.692E-4</v>
       </c>
       <c r="E39">
-        <v>0.0024692</v>
+        <v>2.4692E-3</v>
       </c>
       <c r="F39">
-        <v>0.0090197</v>
+        <v>9.0197000000000003E-3</v>
       </c>
       <c r="G39">
-        <v>0.00312075</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>3.1207499999999998E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1497,22 +3032,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0002982</v>
+        <v>2.9819999999999998E-4</v>
       </c>
       <c r="D40">
-        <v>0.000724</v>
+        <v>7.2400000000000003E-4</v>
       </c>
       <c r="E40">
-        <v>0.0020174</v>
+        <v>2.0173999999999999E-3</v>
       </c>
       <c r="F40">
-        <v>0.0085758</v>
+        <v>8.5757999999999997E-3</v>
       </c>
       <c r="G40">
-        <v>0.00290385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>2.9038499999999999E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1520,22 +3055,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0004123</v>
+        <v>4.1229999999999999E-4</v>
       </c>
       <c r="D41">
-        <v>0.0012535</v>
+        <v>1.2535000000000001E-3</v>
       </c>
       <c r="E41">
-        <v>0.0040108</v>
+        <v>4.0108000000000001E-3</v>
       </c>
       <c r="F41">
-        <v>0.0150234</v>
+        <v>1.5023399999999999E-2</v>
       </c>
       <c r="G41">
-        <v>0.005175000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>5.1750000000000008E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1543,22 +3078,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0003877</v>
+        <v>3.8769999999999999E-4</v>
       </c>
       <c r="D42">
-        <v>0.0012249</v>
+        <v>1.2248999999999999E-3</v>
       </c>
       <c r="E42">
-        <v>0.0037012</v>
+        <v>3.7012E-3</v>
       </c>
       <c r="F42">
-        <v>0.0140005</v>
+        <v>1.4000500000000001E-2</v>
       </c>
       <c r="G42">
-        <v>0.004828575</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>4.8285749999999999E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1566,22 +3101,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.0005020000000000001</v>
+        <v>5.0200000000000006E-4</v>
       </c>
       <c r="D43">
-        <v>0.0014654</v>
+        <v>1.4653999999999999E-3</v>
       </c>
       <c r="E43">
-        <v>0.004994699999999999</v>
+        <v>4.9946999999999986E-3</v>
       </c>
       <c r="F43">
-        <v>0.0187753</v>
+        <v>1.8775300000000002E-2</v>
       </c>
       <c r="G43">
-        <v>0.006434349999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>6.4343499999999993E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1589,22 +3124,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0004674</v>
+        <v>4.6739999999999998E-4</v>
       </c>
       <c r="D44">
-        <v>0.0012957</v>
+        <v>1.2957000000000001E-3</v>
       </c>
       <c r="E44">
-        <v>0.0037837</v>
+        <v>3.7837000000000001E-3</v>
       </c>
       <c r="F44">
-        <v>0.0144103</v>
+        <v>1.4410299999999999E-2</v>
       </c>
       <c r="G44">
-        <v>0.004989275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>4.9892749999999996E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1612,22 +3147,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0004758</v>
+        <v>4.7580000000000002E-4</v>
       </c>
       <c r="D45">
-        <v>0.0013593</v>
+        <v>1.3592999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>0.0042342</v>
+        <v>4.2341999999999996E-3</v>
       </c>
       <c r="F45">
-        <v>0.0164799</v>
+        <v>1.6479899999999999E-2</v>
       </c>
       <c r="G45">
-        <v>0.0056373</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>5.6372999999999996E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1635,22 +3170,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.0004544999999999999</v>
+        <v>4.5449999999999988E-4</v>
       </c>
       <c r="D46">
-        <v>0.001308</v>
+        <v>1.3079999999999999E-3</v>
       </c>
       <c r="E46">
-        <v>0.0041232</v>
+        <v>4.1231999999999996E-3</v>
       </c>
       <c r="F46">
-        <v>0.0153006</v>
+        <v>1.5300599999999999E-2</v>
       </c>
       <c r="G46">
-        <v>0.005296575</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>5.2965750000000004E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1658,22 +3193,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0004086</v>
+        <v>4.0860000000000001E-4</v>
       </c>
       <c r="D47">
-        <v>0.0016903</v>
+        <v>1.6903E-3</v>
       </c>
       <c r="E47">
-        <v>0.006644600000000001</v>
+        <v>6.6446000000000014E-3</v>
       </c>
       <c r="F47">
-        <v>0.0272774</v>
+        <v>2.72774E-2</v>
       </c>
       <c r="G47">
-        <v>0.009005224999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>9.0052249999999986E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1681,22 +3216,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0004901</v>
+        <v>4.9010000000000004E-4</v>
       </c>
       <c r="D48">
-        <v>0.0014552</v>
+        <v>1.4552E-3</v>
       </c>
       <c r="E48">
-        <v>0.005725099999999999</v>
+        <v>5.7250999999999986E-3</v>
       </c>
       <c r="F48">
-        <v>0.0309024</v>
+        <v>3.09024E-2</v>
       </c>
       <c r="G48">
-        <v>0.009643200000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>9.6432000000000011E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1704,22 +3239,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0003855</v>
+        <v>3.8549999999999999E-4</v>
       </c>
       <c r="D49">
-        <v>0.0014495</v>
+        <v>1.4495000000000001E-3</v>
       </c>
       <c r="E49">
-        <v>0.003502</v>
+        <v>3.5019999999999999E-3</v>
       </c>
       <c r="F49">
-        <v>0.012658</v>
+        <v>1.2658000000000001E-2</v>
       </c>
       <c r="G49">
-        <v>0.004498749999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>4.4987499999999993E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1727,22 +3262,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>0.0004071</v>
+        <v>4.0709999999999997E-4</v>
       </c>
       <c r="D50">
-        <v>0.0013606</v>
+        <v>1.3606E-3</v>
       </c>
       <c r="E50">
-        <v>0.004187700000000001</v>
+        <v>4.1877000000000008E-3</v>
       </c>
       <c r="F50">
-        <v>0.0155244</v>
+        <v>1.5524400000000001E-2</v>
       </c>
       <c r="G50">
-        <v>0.00536995</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>5.3699500000000001E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1750,22 +3285,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>0.0004605000000000001</v>
+        <v>4.6050000000000008E-4</v>
       </c>
       <c r="D51">
-        <v>0.00103</v>
+        <v>1.0300000000000001E-3</v>
       </c>
       <c r="E51">
-        <v>0.0030911</v>
+        <v>3.0910999999999998E-3</v>
       </c>
       <c r="F51">
-        <v>0.0115095</v>
+        <v>1.1509500000000001E-2</v>
       </c>
       <c r="G51">
-        <v>0.004022775</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>4.0227750000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1773,22 +3308,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>0.0004148</v>
+        <v>4.148E-4</v>
       </c>
       <c r="D52">
-        <v>0.0014373</v>
+        <v>1.4373000000000001E-3</v>
       </c>
       <c r="E52">
-        <v>0.003085</v>
+        <v>3.0850000000000001E-3</v>
       </c>
       <c r="F52">
-        <v>0.0114287</v>
+        <v>1.14287E-2</v>
       </c>
       <c r="G52">
-        <v>0.00409145</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>4.0914499999999999E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1796,22 +3331,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>0.0003947</v>
+        <v>3.947E-4</v>
       </c>
       <c r="D53">
-        <v>0.000917</v>
+        <v>9.1699999999999995E-4</v>
       </c>
       <c r="E53">
-        <v>0.0029235</v>
+        <v>2.9234999999999999E-3</v>
       </c>
       <c r="F53">
-        <v>0.0143697</v>
+        <v>1.4369699999999999E-2</v>
       </c>
       <c r="G53">
-        <v>0.004651225</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>4.6512250000000002E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1819,22 +3354,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>0.000393</v>
+        <v>3.9300000000000001E-4</v>
       </c>
       <c r="D54">
-        <v>0.0011881</v>
+        <v>1.1881000000000001E-3</v>
       </c>
       <c r="E54">
-        <v>0.0042031</v>
+        <v>4.2031000000000004E-3</v>
       </c>
       <c r="F54">
-        <v>0.0213751</v>
+        <v>2.1375100000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.006789825</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>6.7898250000000002E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1842,22 +3377,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>0.0003595</v>
+        <v>3.5950000000000001E-4</v>
       </c>
       <c r="D55">
-        <v>0.0007592</v>
+        <v>7.5920000000000002E-4</v>
       </c>
       <c r="E55">
-        <v>0.0025756</v>
+        <v>2.5755999999999999E-3</v>
       </c>
       <c r="F55">
-        <v>0.009144299999999999</v>
+        <v>9.1442999999999993E-3</v>
       </c>
       <c r="G55">
-        <v>0.00320965</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>3.2096500000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1865,22 +3400,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>0.0003463</v>
+        <v>3.4630000000000001E-4</v>
       </c>
       <c r="D56">
-        <v>0.0007559999999999999</v>
+        <v>7.5599999999999994E-4</v>
       </c>
       <c r="E56">
-        <v>0.0021701</v>
+        <v>2.1700999999999999E-3</v>
       </c>
       <c r="F56">
-        <v>0.008711599999999998</v>
+        <v>8.7115999999999982E-3</v>
       </c>
       <c r="G56">
-        <v>0.002996</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>2.996E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1888,22 +3423,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>0.0003092</v>
+        <v>3.0919999999999998E-4</v>
       </c>
       <c r="D57">
-        <v>0.0007329999999999999</v>
+        <v>7.3299999999999993E-4</v>
       </c>
       <c r="E57">
-        <v>0.0019907</v>
+        <v>1.9907000000000002E-3</v>
       </c>
       <c r="F57">
-        <v>0.0085609</v>
+        <v>8.5608999999999998E-3</v>
       </c>
       <c r="G57">
-        <v>0.00289845</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>2.8984499999999999E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1911,22 +3446,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>0.0004246</v>
+        <v>4.2460000000000002E-4</v>
       </c>
       <c r="D58">
-        <v>0.00126</v>
+        <v>1.2600000000000001E-3</v>
       </c>
       <c r="E58">
-        <v>0.0038092</v>
+        <v>3.8092E-3</v>
       </c>
       <c r="F58">
-        <v>0.0141655</v>
+        <v>1.4165499999999999E-2</v>
       </c>
       <c r="G58">
-        <v>0.004914825</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>4.9148250000000003E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1934,22 +3469,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>0.0005392</v>
+        <v>5.3919999999999999E-4</v>
       </c>
       <c r="D59">
-        <v>0.0013931</v>
+        <v>1.3931E-3</v>
       </c>
       <c r="E59">
-        <v>0.0043406</v>
+        <v>4.3406E-3</v>
       </c>
       <c r="F59">
-        <v>0.0162938</v>
+        <v>1.6293800000000001E-2</v>
       </c>
       <c r="G59">
-        <v>0.005641675000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>5.6416750000000014E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1957,22 +3492,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>0.0004412</v>
+        <v>4.4119999999999999E-4</v>
       </c>
       <c r="D60">
-        <v>0.0012108</v>
+        <v>1.2107999999999999E-3</v>
       </c>
       <c r="E60">
-        <v>0.0043237</v>
+        <v>4.3236999999999998E-3</v>
       </c>
       <c r="F60">
-        <v>0.0156312</v>
+        <v>1.5631200000000001E-2</v>
       </c>
       <c r="G60">
-        <v>0.005401725</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>5.4017249999999996E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1980,22 +3515,22 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>0.0004574</v>
+        <v>4.574E-4</v>
       </c>
       <c r="D61">
-        <v>0.0010906</v>
+        <v>1.0905999999999999E-3</v>
       </c>
       <c r="E61">
-        <v>0.003174300000000001</v>
+        <v>3.174300000000001E-3</v>
       </c>
       <c r="F61">
-        <v>0.0117327</v>
+        <v>1.17327E-2</v>
       </c>
       <c r="G61">
-        <v>0.004113749999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>4.1137499999999994E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2003,22 +3538,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>0.0004398</v>
+        <v>4.3980000000000001E-4</v>
       </c>
       <c r="D62">
-        <v>0.0011071</v>
+        <v>1.1071E-3</v>
       </c>
       <c r="E62">
-        <v>0.0027353</v>
+        <v>2.7353E-3</v>
       </c>
       <c r="F62">
-        <v>0.0124596</v>
+        <v>1.2459599999999999E-2</v>
       </c>
       <c r="G62">
-        <v>0.004185449999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>4.1854499999999994E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -2026,22 +3561,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>0.0004350000000000001</v>
+        <v>4.3500000000000011E-4</v>
       </c>
       <c r="D63">
-        <v>0.0009707</v>
+        <v>9.7070000000000001E-4</v>
       </c>
       <c r="E63">
-        <v>0.0030463</v>
+        <v>3.0463E-3</v>
       </c>
       <c r="F63">
-        <v>0.0145481</v>
+        <v>1.45481E-2</v>
       </c>
       <c r="G63">
-        <v>0.004750025</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>4.7500249999999997E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -2049,22 +3584,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>0.0003492</v>
+        <v>3.4919999999999998E-4</v>
       </c>
       <c r="D64">
-        <v>0.0008776000000000001</v>
+        <v>8.7760000000000008E-4</v>
       </c>
       <c r="E64">
-        <v>0.0021052</v>
+        <v>2.1052000000000002E-3</v>
       </c>
       <c r="F64">
-        <v>0.008714299999999999</v>
+        <v>8.7142999999999995E-3</v>
       </c>
       <c r="G64">
-        <v>0.003011575</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>3.0115749999999998E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2072,32 +3607,33 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>0.0005185000000000001</v>
+        <v>5.1850000000000008E-4</v>
       </c>
       <c r="D65">
-        <v>0.0012325</v>
+        <v>1.2325000000000001E-3</v>
       </c>
       <c r="E65">
-        <v>0.0028352</v>
+        <v>2.8352E-3</v>
       </c>
       <c r="F65">
-        <v>0.0126508</v>
+        <v>1.26508E-2</v>
       </c>
       <c r="G65">
-        <v>0.00430925</v>
+        <v>4.3092499999999997E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +3656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +3679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2166,7 +3702,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2189,7 +3725,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2212,7 +3748,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2235,7 +3771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2258,7 +3794,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2281,7 +3817,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2304,7 +3840,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2327,7 +3863,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2350,7 +3886,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2373,7 +3909,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2396,7 +3932,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2419,7 +3955,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2442,7 +3978,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2465,7 +4001,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2488,7 +4024,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2511,7 +4047,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2534,7 +4070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2557,7 +4093,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2580,7 +4116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2603,7 +4139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2626,7 +4162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2649,7 +4185,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2672,7 +4208,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2695,7 +4231,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2718,7 +4254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2741,7 +4277,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2764,7 +4300,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2787,7 +4323,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2810,7 +4346,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2833,7 +4369,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2856,7 +4392,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2879,7 +4415,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2902,7 +4438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2925,7 +4461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2948,7 +4484,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2971,7 +4507,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -2994,7 +4530,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3017,7 +4553,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -3040,7 +4576,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -3063,7 +4599,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -3086,7 +4622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3109,7 +4645,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3132,7 +4668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3155,7 +4691,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3178,7 +4714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -3201,7 +4737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -3224,7 +4760,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3247,7 +4783,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -3270,7 +4806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -3293,7 +4829,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3316,7 +4852,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -3339,7 +4875,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -3362,7 +4898,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -3385,7 +4921,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -3408,7 +4944,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -3431,7 +4967,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3454,7 +4990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -3477,7 +5013,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -3500,7 +5036,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3523,7 +5059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -3546,7 +5082,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -3569,7 +5105,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -3598,11 +5134,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3636,19 +5172,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D2">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E2">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F2">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G2">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3656,22 +5192,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D3">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E3">
-        <v>99.29646455628166</v>
+        <v>99.296464556281663</v>
       </c>
       <c r="F3">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G3">
-        <v>93.05382386916239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>93.053823869162386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3682,19 +5218,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D4">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E4">
-        <v>99.05382386916236</v>
+        <v>99.053823869162358</v>
       </c>
       <c r="F4">
-        <v>201.7645019878171</v>
+        <v>201.76450198781711</v>
       </c>
       <c r="G4">
-        <v>93.22539674441617</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>93.225396744416173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3705,19 +5241,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D5">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E5">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F5">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G5">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3728,19 +5264,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D6">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E6">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F6">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G6">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3748,22 +5284,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D7">
-        <v>47.35427739496249</v>
+        <v>47.354277394962487</v>
       </c>
       <c r="E7">
-        <v>94.35610639961114</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F7">
         <v>193.5523624359607</v>
       </c>
       <c r="G7">
-        <v>89.60451849562072</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>89.604518495620724</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3774,19 +5310,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D8">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E8">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F8">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G8">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3794,22 +5330,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D9">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E9">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F9">
-        <v>200.8355697996826</v>
+        <v>200.83556979968259</v>
       </c>
       <c r="G9">
-        <v>93.05382386916237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>93.053823869162372</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3817,22 +5353,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D10">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E10">
-        <v>99.29646455628166</v>
+        <v>99.296464556281663</v>
       </c>
       <c r="F10">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G10">
-        <v>93.05382386916239</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>93.053823869162386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3840,22 +5376,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D11">
-        <v>47.30608777088271</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E11">
-        <v>93.3583331166767</v>
+        <v>93.358333116676704</v>
       </c>
       <c r="F11">
         <v>189.2486212678381</v>
       </c>
       <c r="G11">
-        <v>88.20410850128535</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>88.204108501285347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3863,22 +5399,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D12">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E12">
-        <v>99.29646455628166</v>
+        <v>99.296464556281663</v>
       </c>
       <c r="F12">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G12">
-        <v>93.05382386916239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>93.053823869162386</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3886,22 +5422,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D13">
-        <v>47.04260386248743</v>
+        <v>47.042603862487432</v>
       </c>
       <c r="E13">
-        <v>95.39930759975792</v>
+        <v>95.399307599757918</v>
       </c>
       <c r="F13">
-        <v>192.0671497050838</v>
+        <v>192.06714970508381</v>
       </c>
       <c r="G13">
-        <v>89.35311325426825</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>89.353113254268251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3912,19 +5448,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D14">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E14">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F14">
-        <v>201.1787155501902</v>
+        <v>201.17871555019019</v>
       </c>
       <c r="G14">
-        <v>92.93250352560273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>92.932503525602726</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3935,19 +5471,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D15">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E15">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F15">
         <v>198.9360748630709</v>
       </c>
       <c r="G15">
-        <v>92.3718433538229</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>92.371843353822896</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3955,22 +5491,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>22.95741732923815</v>
+        <v>22.957417329238151</v>
       </c>
       <c r="D16">
-        <v>45.92781077919376</v>
+        <v>45.927810779193763</v>
       </c>
       <c r="E16">
-        <v>92.74013947171844</v>
+        <v>92.740139471718436</v>
       </c>
       <c r="F16">
-        <v>186.491272090702</v>
+        <v>186.49127209070201</v>
       </c>
       <c r="G16">
-        <v>87.02915991771309</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>87.029159917713088</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3981,19 +5517,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D17">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E17">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F17">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G17">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4004,19 +5540,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D18">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E18">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F18">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G18">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4024,10 +5560,10 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D19">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E19">
         <v>100.8111831820431</v>
@@ -4036,10 +5572,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G19">
-        <v>94.42209588551708</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>94.422095885517081</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4050,19 +5586,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D20">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E20">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F20">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G20">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4070,22 +5606,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D21">
-        <v>46.48980268944821</v>
+        <v>46.489802689448211</v>
       </c>
       <c r="E21">
-        <v>94.35610639961114</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F21">
-        <v>194.813138631082</v>
+        <v>194.81313863108201</v>
       </c>
       <c r="G21">
-        <v>89.70359386802247</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>89.703593868022466</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4096,19 +5632,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D22">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E22">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F22">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G22">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4116,22 +5652,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>22.61228391298839</v>
+        <v>22.612283912988389</v>
       </c>
       <c r="D23">
-        <v>46.75919574225016</v>
+        <v>46.759195742250157</v>
       </c>
       <c r="E23">
-        <v>95.66561268321651</v>
+        <v>95.665612683216509</v>
       </c>
       <c r="F23">
-        <v>193.0528320254188</v>
+        <v>193.05283202541881</v>
       </c>
       <c r="G23">
-        <v>89.52248109096848</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>89.522481090968483</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4139,22 +5675,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D24">
-        <v>47.30608777088271</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E24">
-        <v>95.79970819323297</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F24">
-        <v>192.3951352985629</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G24">
-        <v>89.60108077810561</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>89.601080778105612</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4162,22 +5698,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D25">
-        <v>49.1126983722081</v>
+        <v>49.112698372208101</v>
       </c>
       <c r="E25">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F25">
         <v>200.0071426749364</v>
       </c>
       <c r="G25">
-        <v>92.99316369738256</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>92.993163697382556</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4185,22 +5721,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D26">
-        <v>49.1126983722081</v>
+        <v>49.112698372208101</v>
       </c>
       <c r="E26">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F26">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G26">
-        <v>92.786056916196</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>92.786056916196003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4208,22 +5744,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D27">
-        <v>47.05415186867799</v>
+        <v>47.054151868677991</v>
       </c>
       <c r="E27">
-        <v>95.17284061197759</v>
+        <v>95.172840611977591</v>
       </c>
       <c r="F27">
-        <v>191.0485857191981</v>
+        <v>191.04858571919809</v>
       </c>
       <c r="G27">
-        <v>89.04474251239938</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>89.044742512399381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4231,22 +5767,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D28">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E28">
-        <v>99.29646455628166</v>
+        <v>99.296464556281663</v>
       </c>
       <c r="F28">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G28">
-        <v>93.05382386916239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>93.053823869162386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -4254,10 +5790,10 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D29">
-        <v>46.80221596647328</v>
+        <v>46.802215966473277</v>
       </c>
       <c r="E29">
         <v>95.10870539248485</v>
@@ -4266,10 +5802,10 @@
         <v>190.8044325344818</v>
       </c>
       <c r="G29">
-        <v>88.96767041134711</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>88.967670411347115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -4277,22 +5813,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D30">
-        <v>47.04260386248743</v>
+        <v>47.042603862487432</v>
       </c>
       <c r="E30">
-        <v>95.36889432883548</v>
+        <v>95.368894328835481</v>
       </c>
       <c r="F30">
         <v>192.0991124527755</v>
       </c>
       <c r="G30">
-        <v>89.35350062346056</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>89.353500623460562</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -4303,19 +5839,19 @@
         <v>22.93494128361905</v>
       </c>
       <c r="D31">
-        <v>47.1272013040363</v>
+        <v>47.127201304036298</v>
       </c>
       <c r="E31">
-        <v>95.36889432883548</v>
+        <v>95.368894328835481</v>
       </c>
       <c r="F31">
         <v>192.0991124527755</v>
       </c>
       <c r="G31">
-        <v>89.38253734231658</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>89.382537342316581</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4326,19 +5862,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D32">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E32">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F32">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G32">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4346,22 +5882,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>22.95741732923815</v>
+        <v>22.957417329238151</v>
       </c>
       <c r="D33">
-        <v>45.92781077919376</v>
+        <v>45.927810779193763</v>
       </c>
       <c r="E33">
-        <v>92.74013947171844</v>
+        <v>92.740139471718436</v>
       </c>
       <c r="F33">
-        <v>186.491272090702</v>
+        <v>186.49127209070201</v>
       </c>
       <c r="G33">
-        <v>87.02915991771309</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>87.029159917713088</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4372,19 +5908,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D34">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E34">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F34">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G34">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4395,19 +5931,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D35">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E35">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F35">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G35">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4418,19 +5954,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D36">
-        <v>47.14260879307493</v>
+        <v>47.142608793074928</v>
       </c>
       <c r="E36">
-        <v>95.64392974814447</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F36">
         <v>192.6542644043582</v>
       </c>
       <c r="G36">
-        <v>89.63197465251324</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>89.631974652513236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4441,19 +5977,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D37">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E37">
-        <v>101.6396103067893</v>
+        <v>101.63961030678929</v>
       </c>
       <c r="F37">
-        <v>251.2792206135786</v>
+        <v>251.27922061357859</v>
       </c>
       <c r="G37">
         <v>106.4576297914498</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4461,22 +5997,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>23.78584445398434</v>
+        <v>23.785844453984339</v>
       </c>
       <c r="D38">
-        <v>48.10712726326643</v>
+        <v>48.107127263266428</v>
       </c>
       <c r="E38">
-        <v>97.59075554724757</v>
+        <v>97.590755547247568</v>
       </c>
       <c r="F38">
-        <v>196.5637619091765</v>
+        <v>196.56376190917649</v>
       </c>
       <c r="G38">
-        <v>91.5118722934187</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>91.511872293418705</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4484,10 +6020,10 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D39">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E39">
         <v>100.8111831820431</v>
@@ -4496,10 +6032,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G39">
-        <v>94.42209588551708</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>94.422095885517081</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4510,19 +6046,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D40">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E40">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F40">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G40">
-        <v>94.77564927611036</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>94.775649276110357</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4530,22 +6066,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>22.97718216707523</v>
+        <v>22.977182167075231</v>
       </c>
       <c r="D41">
-        <v>46.48980268944821</v>
+        <v>46.489802689448211</v>
       </c>
       <c r="E41">
-        <v>94.35610639961114</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F41">
-        <v>190.0944636139037</v>
+        <v>190.09446361390371</v>
       </c>
       <c r="G41">
-        <v>88.47938871750956</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>88.479388717509565</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4556,19 +6092,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D42">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E42">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F42">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G42">
-        <v>92.22539674441617</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>92.225396744416173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4576,22 +6112,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D43">
-        <v>46.48980268944821</v>
+        <v>46.489802689448211</v>
       </c>
       <c r="E43">
-        <v>94.35610639961114</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F43">
-        <v>194.813138631082</v>
+        <v>194.81313863108201</v>
       </c>
       <c r="G43">
-        <v>89.70359386802247</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>89.703593868022466</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4599,22 +6135,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D44">
-        <v>47.30608777088271</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E44">
-        <v>95.79970819323297</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F44">
-        <v>192.8064508314586</v>
+        <v>192.80645083145859</v>
       </c>
       <c r="G44">
-        <v>89.70390966132952</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>89.703909661329519</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4622,22 +6158,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D45">
-        <v>47.30608777088271</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E45">
-        <v>95.79970819323297</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F45">
-        <v>192.3951352985629</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G45">
-        <v>89.60108077810561</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>89.601080778105612</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4645,22 +6181,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D46">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E46">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F46">
-        <v>199.1787155501902</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G46">
         <v>92.63961030678928</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4668,22 +6204,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D47">
-        <v>47.05415186867799</v>
+        <v>47.054151868677991</v>
       </c>
       <c r="E47">
-        <v>95.17284061197759</v>
+        <v>95.172840611977591</v>
       </c>
       <c r="F47">
-        <v>191.0485857191981</v>
+        <v>191.04858571919809</v>
       </c>
       <c r="G47">
-        <v>89.04474251239938</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>89.044742512399381</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4694,19 +6230,19 @@
         <v>22.93494128361905</v>
       </c>
       <c r="D48">
-        <v>47.04260386248743</v>
+        <v>47.042603862487432</v>
       </c>
       <c r="E48">
-        <v>95.36889432883548</v>
+        <v>95.368894328835481</v>
       </c>
       <c r="F48">
-        <v>192.0382859109307</v>
+        <v>192.03828591093071</v>
       </c>
       <c r="G48">
-        <v>89.34618134646816</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>89.346181346468157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -4714,22 +6250,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>23.20005801635744</v>
+        <v>23.200058016357438</v>
       </c>
       <c r="D49">
-        <v>46.3684244370276</v>
+        <v>46.368424437027599</v>
       </c>
       <c r="E49">
-        <v>93.77985577935667</v>
+        <v>93.779855779356666</v>
       </c>
       <c r="F49">
-        <v>188.6730564525274</v>
+        <v>188.67305645252739</v>
       </c>
       <c r="G49">
-        <v>88.00534867131728</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>88.005348671317279</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -4740,19 +6276,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D50">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E50">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F50">
         <v>218.4507934888324</v>
       </c>
       <c r="G50">
-        <v>97.25052301026327</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>97.250523010263265</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -4763,19 +6299,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D51">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E51">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F51">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G51">
-        <v>94.77564927611036</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>94.775649276110357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -4786,19 +6322,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D52">
-        <v>46.38680108646078</v>
+        <v>46.386801086460778</v>
       </c>
       <c r="E52">
-        <v>95.64392974814447</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F52">
         <v>192.6542644043582</v>
       </c>
       <c r="G52">
-        <v>89.44302272585969</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>89.443022725859691</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -4806,22 +6342,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>24.38477631085024</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D53">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E53">
-        <v>101.6396103067893</v>
+        <v>101.63961030678929</v>
       </c>
       <c r="F53">
         <v>203.8650070512054</v>
       </c>
       <c r="G53">
-        <v>94.8111831820431</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>94.811183182043095</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -4832,19 +6368,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D54">
-        <v>48.08541237931293</v>
+        <v>48.085412379312928</v>
       </c>
       <c r="E54">
         <v>98.46403379269465</v>
       </c>
       <c r="F54">
-        <v>231.7617225552038</v>
+        <v>231.76172255520379</v>
       </c>
       <c r="G54">
         <v>100.3495660979217</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -4852,22 +6388,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>23.78584445398434</v>
+        <v>23.785844453984339</v>
       </c>
       <c r="D55">
-        <v>48.10712726326643</v>
+        <v>48.107127263266428</v>
       </c>
       <c r="E55">
-        <v>97.59075554724757</v>
+        <v>97.590755547247568</v>
       </c>
       <c r="F55">
-        <v>196.5637619091765</v>
+        <v>196.56376190917649</v>
       </c>
       <c r="G55">
-        <v>91.5118722934187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>91.511872293418705</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -4875,22 +6411,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D56">
         <v>47.6694714437428</v>
       </c>
       <c r="E56">
-        <v>96.7154439082003</v>
+        <v>96.715443908200299</v>
       </c>
       <c r="F56">
         <v>201.3376443991751</v>
       </c>
       <c r="G56">
-        <v>92.21947187576669</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>92.219471875766686</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4901,19 +6437,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D57">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E57">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F57">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G57">
-        <v>94.77564927611036</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>94.775649276110357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4921,22 +6457,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>22.97718216707523</v>
+        <v>22.977182167075231</v>
       </c>
       <c r="D58">
-        <v>46.48980268944821</v>
+        <v>46.489802689448211</v>
       </c>
       <c r="E58">
-        <v>94.35610639961114</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F58">
-        <v>190.0944636139037</v>
+        <v>190.09446361390371</v>
       </c>
       <c r="G58">
-        <v>88.47938871750956</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>88.479388717509565</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -4944,22 +6480,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>22.90339184974382</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D59">
-        <v>47.30608777088271</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E59">
-        <v>95.79970819323297</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F59">
-        <v>192.3951352985629</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G59">
-        <v>89.60108077810561</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>89.601080778105612</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -4970,19 +6506,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D60">
-        <v>46.3684244370276</v>
+        <v>46.368424437027599</v>
       </c>
       <c r="E60">
-        <v>96.7154439082003</v>
+        <v>96.715443908200299</v>
       </c>
       <c r="F60">
-        <v>202.2980581135191</v>
+        <v>202.29805811351909</v>
       </c>
       <c r="G60">
-        <v>92.11725553080556</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>92.117255530805565</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -4993,19 +6529,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D61">
-        <v>47.14260879307493</v>
+        <v>47.142608793074928</v>
       </c>
       <c r="E61">
-        <v>95.64392974814447</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F61">
-        <v>199.1787701724513</v>
+        <v>199.17877017245129</v>
       </c>
       <c r="G61">
-        <v>91.26310109453651</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>91.263101094536509</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5013,22 +6549,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>26.38477631085023</v>
+        <v>26.384776310850231</v>
       </c>
       <c r="D62">
-        <v>49.35533905932738</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E62">
-        <v>101.6396103067893</v>
+        <v>101.63961030678929</v>
       </c>
       <c r="F62">
         <v>218.4507934888324</v>
       </c>
       <c r="G62">
-        <v>98.95762979144982</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>98.957629791449818</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5039,19 +6575,19 @@
         <v>24.02848514110363</v>
       </c>
       <c r="D63">
-        <v>48.06132626728805</v>
+        <v>48.061326267288052</v>
       </c>
       <c r="E63">
-        <v>98.44713706158336</v>
+        <v>98.447137061583362</v>
       </c>
       <c r="F63">
-        <v>197.5157161275332</v>
+        <v>197.51571612753321</v>
       </c>
       <c r="G63">
-        <v>92.01316614937704</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>92.013166149377042</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5059,22 +6595,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>23.15532775194854</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D64">
         <v>47.6694714437428</v>
       </c>
       <c r="E64">
-        <v>96.7154439082003</v>
+        <v>96.715443908200299</v>
       </c>
       <c r="F64">
         <v>201.3376443991751</v>
       </c>
       <c r="G64">
-        <v>92.21947187576669</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>92.219471875766686</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5085,16 +6621,16 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D65">
-        <v>48.06132626728805</v>
+        <v>48.061326267288052</v>
       </c>
       <c r="E65">
-        <v>98.44713706158336</v>
+        <v>98.447137061583362</v>
       </c>
       <c r="F65">
-        <v>202.2980581135191</v>
+        <v>202.29805811351909</v>
       </c>
       <c r="G65">
-        <v>92.97340427671645</v>
+        <v>92.973404276716451</v>
       </c>
     </row>
   </sheetData>
@@ -5103,11 +6639,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5130,7 +6666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5153,7 +6689,7 @@
         <v>343.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5176,7 +6712,7 @@
         <v>356.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5199,7 +6735,7 @@
         <v>238.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5222,7 +6758,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5245,7 +6781,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5268,7 +6804,7 @@
         <v>343.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5291,7 +6827,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5314,7 +6850,7 @@
         <v>281.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5337,7 +6873,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5360,7 +6896,7 @@
         <v>356.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5383,7 +6919,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5406,7 +6942,7 @@
         <v>238.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5429,7 +6965,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5452,7 +6988,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5475,7 +7011,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +7034,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5521,7 +7057,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5544,7 +7080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5567,7 +7103,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5590,7 +7126,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5613,7 +7149,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5636,7 +7172,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5659,7 +7195,7 @@
         <v>281.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5682,7 +7218,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -5705,7 +7241,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -5728,7 +7264,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -5751,7 +7287,7 @@
         <v>236.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5774,7 +7310,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5797,7 +7333,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5820,7 +7356,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5843,7 +7379,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5866,7 +7402,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5889,7 +7425,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5912,7 +7448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5935,7 +7471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5958,7 +7494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5981,7 +7517,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6004,7 +7540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -6027,7 +7563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6050,7 +7586,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6073,7 +7609,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6096,7 +7632,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6119,7 +7655,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6142,7 +7678,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6165,7 +7701,7 @@
         <v>253.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6188,7 +7724,7 @@
         <v>236.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -6211,7 +7747,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -6234,7 +7770,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -6257,7 +7793,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -6280,7 +7816,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -6303,7 +7839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -6326,7 +7862,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -6349,7 +7885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -6372,7 +7908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -6395,7 +7931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -6418,7 +7954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6441,7 +7977,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -6464,7 +8000,7 @@
         <v>253.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -6487,7 +8023,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -6510,7 +8046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -6533,7 +8069,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -6556,7 +8092,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6579,7 +8115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -6608,11 +8144,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6635,7 +8171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6658,7 +8194,7 @@
         <v>1587.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6681,7 +8217,7 @@
         <v>1186.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6704,7 +8240,7 @@
         <v>200.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6727,7 +8263,7 @@
         <v>953.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6750,7 +8286,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6773,7 +8309,7 @@
         <v>1587.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6796,7 +8332,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6819,7 +8355,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6842,7 +8378,7 @@
         <v>971.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6865,7 +8401,7 @@
         <v>1186.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6888,7 +8424,7 @@
         <v>1133.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6911,7 +8447,7 @@
         <v>200.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6934,7 +8470,7 @@
         <v>176.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6957,7 +8493,7 @@
         <v>171.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6980,7 +8516,7 @@
         <v>953.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7003,7 +8539,7 @@
         <v>962.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7026,7 +8562,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7049,7 +8585,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7072,7 +8608,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7095,7 +8631,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7118,7 +8654,7 @@
         <v>55.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -7141,7 +8677,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7164,7 +8700,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7187,7 +8723,7 @@
         <v>216.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7210,7 +8746,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7233,7 +8769,7 @@
         <v>971.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7256,7 +8792,7 @@
         <v>974.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7279,7 +8815,7 @@
         <v>1133.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7302,7 +8838,7 @@
         <v>176.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7325,7 +8861,7 @@
         <v>171.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7348,7 +8884,7 @@
         <v>166.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7371,7 +8907,7 @@
         <v>962.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7394,7 +8930,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7417,7 +8953,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7440,7 +8976,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7463,7 +8999,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7486,7 +9022,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -7509,7 +9045,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -7532,7 +9068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -7555,7 +9091,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -7578,7 +9114,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -7601,7 +9137,7 @@
         <v>55.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7624,7 +9160,7 @@
         <v>216.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7647,7 +9183,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7670,7 +9206,7 @@
         <v>215.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7693,7 +9229,7 @@
         <v>974.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -7716,7 +9252,7 @@
         <v>166.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -7739,7 +9275,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -7762,7 +9298,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -7785,7 +9321,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -7808,7 +9344,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -7831,7 +9367,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -7854,7 +9390,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -7877,7 +9413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -7900,7 +9436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -7923,7 +9459,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -7946,7 +9482,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -7969,7 +9505,7 @@
         <v>215.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -7992,7 +9528,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -8015,7 +9551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -8038,7 +9574,7 @@
         <v>33.25</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -8061,7 +9597,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -8084,7 +9620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -8113,11 +9649,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +9676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8163,7 +9699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8186,7 +9722,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8209,7 +9745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8232,7 +9768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8255,7 +9791,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8278,7 +9814,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8301,7 +9837,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8324,7 +9860,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8347,7 +9883,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8370,7 +9906,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8393,7 +9929,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8416,7 +9952,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8439,7 +9975,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8462,7 +9998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8485,7 +10021,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8508,7 +10044,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8531,7 +10067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8554,7 +10090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8577,7 +10113,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8600,7 +10136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8623,7 +10159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -8646,7 +10182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8669,7 +10205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8692,7 +10228,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8715,7 +10251,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8738,7 +10274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8761,7 +10297,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8784,7 +10320,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8807,7 +10343,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8830,7 +10366,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8853,7 +10389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8876,7 +10412,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8899,7 +10435,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8922,7 +10458,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8945,7 +10481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8968,7 +10504,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8991,7 +10527,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9014,7 +10550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -9037,7 +10573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -9060,7 +10596,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -9083,7 +10619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -9106,7 +10642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -9129,7 +10665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -9152,7 +10688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -9175,7 +10711,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -9198,7 +10734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -9221,7 +10757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -9244,7 +10780,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -9267,7 +10803,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -9290,7 +10826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -9313,7 +10849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -9336,7 +10872,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -9359,7 +10895,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -9382,7 +10918,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -9405,7 +10941,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -9428,7 +10964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -9451,7 +10987,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -9474,7 +11010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -9497,7 +11033,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -9520,7 +11056,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -9543,7 +11079,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -9566,7 +11102,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -9589,7 +11125,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D670681C-9A86-4CFF-9464-9555340C4CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6C298A-4490-4456-A526-992277B51D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="55">
   <si>
     <t>Jumlah Kombinasi</t>
   </si>
@@ -108,9 +108,6 @@
     <t>JPS-PPO</t>
   </si>
   <si>
-    <t>JPS-TPF</t>
-  </si>
-  <si>
     <t>TPF-PPO</t>
   </si>
   <si>
@@ -153,25 +150,13 @@
     <t>JPS-BDS-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-TPF</t>
-  </si>
-  <si>
     <t>JPS-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF</t>
   </si>
   <si>
     <t>JPS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-GL-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-BRC-TPF-PPO</t>
@@ -192,52 +177,19 @@
     <t>JPS-BDS-BRC-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-BDS-GL-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-GL-BRC-TPF-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF-PPO</t>
   </si>
 </sst>
 </file>
@@ -433,16 +385,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.9139999999999996E-4</c:v>
+                  <c:v>5.7899999999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.8051000000000009E-3</c:v>
+                  <c:v>3.7523000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9758700000000009E-2</c:v>
+                  <c:v>2.96428E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22436320000000001</c:v>
+                  <c:v>0.21238599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -450,7 +402,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000000-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -519,16 +471,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.7169999999999999E-4</c:v>
+                  <c:v>2.5090000000000003E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.183E-3</c:v>
+                  <c:v>1.1521000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1504000000000003E-3</c:v>
+                  <c:v>4.8651999999999992E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.1933899999999999E-2</c:v>
+                  <c:v>2.0291699999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -536,7 +488,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000001-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -605,16 +557,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.1950000000000001E-4</c:v>
+                  <c:v>3.9910000000000011E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2577000000000001E-3</c:v>
+                  <c:v>1.2661E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6950999999999989E-3</c:v>
+                  <c:v>4.5457000000000006E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.80442E-2</c:v>
+                  <c:v>3.6123799999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -622,7 +574,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000002-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -691,16 +643,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5239999999999999E-4</c:v>
+                  <c:v>4.4989999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6727999999999999E-3</c:v>
+                  <c:v>2.5777E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8626E-2</c:v>
+                  <c:v>1.7207E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1253619</c:v>
+                  <c:v>0.1204027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -708,7 +660,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000003-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -777,16 +729,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5859999999999998E-4</c:v>
+                  <c:v>4.2939999999999997E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3979999999999999E-3</c:v>
+                  <c:v>1.3361E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.0564E-3</c:v>
+                  <c:v>4.8003999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0586199999999999E-2</c:v>
+                  <c:v>1.93978E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,7 +746,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000004-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -863,16 +815,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>6.4630000000000004E-4</c:v>
+                  <c:v>6.0129999999999992E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.8302000000000002E-3</c:v>
+                  <c:v>3.6993E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9685799999999998E-2</c:v>
+                  <c:v>2.8210300000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22379499999999999</c:v>
+                  <c:v>0.21230650000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -880,7 +832,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000005-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -955,16 +907,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.7370000000000001E-4</c:v>
+                  <c:v>6.3259999999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.7453999999999999E-3</c:v>
+                  <c:v>3.5785999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8205999999999998E-2</c:v>
+                  <c:v>2.6404199999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2119598</c:v>
+                  <c:v>0.20061399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -972,7 +924,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-C8D0-4B39-8FAC-DD1C8AAB728D}"/>
+              <c16:uniqueId val="{00000006-285E-4447-96E5-7B20C4588DEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1000,11 +952,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1087387407"/>
-        <c:axId val="1087393167"/>
+        <c:axId val="651940351"/>
+        <c:axId val="651941791"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1087387407"/>
+        <c:axId val="651940351"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1077,7 +1029,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1087393167"/>
+        <c:crossAx val="651941791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1085,7 +1037,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1087393167"/>
+        <c:axId val="651941791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1166,7 +1118,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1087387407"/>
+        <c:crossAx val="651940351"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1816,7 +1768,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5C4D782-24FE-6BA0-2C4E-0F028702A851}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{330600D5-724E-9EEB-BA2C-FC5E2EDDAA96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1840,7 +1792,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Red Orange">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1848,34 +1800,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="505046"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="E84C22"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="FFBD47"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="B64926"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FF8427"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="CC9900"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="B22600"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="CC9900"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="666699"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
@@ -2124,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -2158,19 +2110,19 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>5.9139999999999996E-4</v>
+        <v>5.7899999999999998E-4</v>
       </c>
       <c r="D2">
-        <v>3.8051000000000009E-3</v>
+        <v>3.7523000000000001E-3</v>
       </c>
       <c r="E2">
-        <v>2.9758700000000009E-2</v>
+        <v>2.96428E-2</v>
       </c>
       <c r="F2">
-        <v>0.22436320000000001</v>
+        <v>0.21238599999999999</v>
       </c>
       <c r="G2">
-        <v>6.4629600000000009E-2</v>
+        <v>6.1590025000000007E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2181,19 +2133,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.7169999999999999E-4</v>
+        <v>2.5090000000000003E-4</v>
       </c>
       <c r="D3">
-        <v>1.183E-3</v>
+        <v>1.1521000000000001E-3</v>
       </c>
       <c r="E3">
-        <v>5.1504000000000003E-3</v>
+        <v>4.8651999999999992E-3</v>
       </c>
       <c r="F3">
-        <v>2.1933899999999999E-2</v>
+        <v>2.0291699999999999E-2</v>
       </c>
       <c r="G3">
-        <v>7.1347499999999996E-3</v>
+        <v>6.6399750000000011E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2204,19 +2156,19 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4.1950000000000001E-4</v>
+        <v>3.9910000000000011E-4</v>
       </c>
       <c r="D4">
-        <v>1.2577000000000001E-3</v>
+        <v>1.2661E-3</v>
       </c>
       <c r="E4">
-        <v>4.6950999999999989E-3</v>
+        <v>4.5457000000000006E-3</v>
       </c>
       <c r="F4">
-        <v>3.80442E-2</v>
+        <v>3.6123799999999998E-2</v>
       </c>
       <c r="G4">
-        <v>1.1104124999999999E-2</v>
+        <v>1.0583675000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2227,19 +2179,19 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>4.5239999999999999E-4</v>
+        <v>4.4989999999999999E-4</v>
       </c>
       <c r="D5">
-        <v>2.6727999999999999E-3</v>
+        <v>2.5777E-3</v>
       </c>
       <c r="E5">
-        <v>1.8626E-2</v>
+        <v>1.7207E-2</v>
       </c>
       <c r="F5">
-        <v>0.1253619</v>
+        <v>0.1204027</v>
       </c>
       <c r="G5">
-        <v>3.6778274999999999E-2</v>
+        <v>3.5159324999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2250,19 +2202,19 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>4.5859999999999998E-4</v>
+        <v>4.2939999999999997E-4</v>
       </c>
       <c r="D6">
-        <v>1.3979999999999999E-3</v>
+        <v>1.3361E-3</v>
       </c>
       <c r="E6">
-        <v>5.0564E-3</v>
+        <v>4.8003999999999998E-3</v>
       </c>
       <c r="F6">
-        <v>2.0586199999999999E-2</v>
+        <v>1.93978E-2</v>
       </c>
       <c r="G6">
-        <v>6.8747999999999986E-3</v>
+        <v>6.4909249999999998E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2273,19 +2225,19 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>6.4630000000000004E-4</v>
+        <v>6.0129999999999992E-4</v>
       </c>
       <c r="D7">
-        <v>3.8302000000000002E-3</v>
+        <v>3.6993E-3</v>
       </c>
       <c r="E7">
-        <v>2.9685799999999998E-2</v>
+        <v>2.8210300000000001E-2</v>
       </c>
       <c r="F7">
-        <v>0.22379499999999999</v>
+        <v>0.21230650000000001</v>
       </c>
       <c r="G7">
-        <v>6.4489325E-2</v>
+        <v>6.1204349999999991E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2296,19 +2248,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>5.7370000000000001E-4</v>
+        <v>6.3259999999999998E-4</v>
       </c>
       <c r="D8">
-        <v>3.7453999999999999E-3</v>
+        <v>3.5785999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>2.8205999999999998E-2</v>
+        <v>2.6404199999999999E-2</v>
       </c>
       <c r="F8">
-        <v>0.2119598</v>
+        <v>0.20061399999999999</v>
       </c>
       <c r="G8">
-        <v>6.1121224999999987E-2</v>
+        <v>5.7807349999999993E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2319,19 +2271,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>4.0620000000000001E-4</v>
+        <v>3.9760000000000002E-4</v>
       </c>
       <c r="D9">
-        <v>1.0988E-3</v>
+        <v>1.0709999999999999E-3</v>
       </c>
       <c r="E9">
-        <v>3.3801E-3</v>
+        <v>3.1621000000000002E-3</v>
       </c>
       <c r="F9">
-        <v>1.26698E-2</v>
+        <v>1.1674800000000001E-2</v>
       </c>
       <c r="G9">
-        <v>4.3887249999999996E-3</v>
+        <v>4.0763750000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2342,19 +2294,19 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>3.1139999999999998E-4</v>
+        <v>2.8509999999999999E-4</v>
       </c>
       <c r="D10">
-        <v>1.4928999999999999E-3</v>
+        <v>1.4450000000000001E-3</v>
       </c>
       <c r="E10">
-        <v>6.3433000000000014E-3</v>
+        <v>5.9503999999999998E-3</v>
       </c>
       <c r="F10">
-        <v>2.6906599999999999E-2</v>
+        <v>2.5019799999999998E-2</v>
       </c>
       <c r="G10">
-        <v>8.7635499999999984E-3</v>
+        <v>8.1750750000000004E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2365,19 +2317,19 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>3.0509999999999999E-4</v>
+        <v>2.9050000000000001E-4</v>
       </c>
       <c r="D11">
-        <v>1.2741E-3</v>
+        <v>1.2293E-3</v>
       </c>
       <c r="E11">
-        <v>5.3763999999999999E-3</v>
+        <v>5.0981999999999998E-3</v>
       </c>
       <c r="F11">
-        <v>2.2897299999999999E-2</v>
+        <v>2.1068300000000002E-2</v>
       </c>
       <c r="G11">
-        <v>7.4632250000000004E-3</v>
+        <v>6.9215750000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2388,19 +2340,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>3.5070000000000001E-4</v>
+        <v>3.436E-4</v>
       </c>
       <c r="D12">
-        <v>1.3986000000000001E-3</v>
+        <v>1.4032000000000001E-3</v>
       </c>
       <c r="E12">
-        <v>5.2285000000000014E-3</v>
+        <v>5.4543999999999999E-3</v>
       </c>
       <c r="F12">
-        <v>2.2790299999999999E-2</v>
+        <v>2.16294E-2</v>
       </c>
       <c r="G12">
-        <v>7.4420249999999997E-3</v>
+        <v>7.2076499999999986E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2411,19 +2363,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.3940000000000011E-4</v>
+        <v>4.5229999999999988E-4</v>
       </c>
       <c r="D13">
-        <v>1.3512999999999999E-3</v>
+        <v>1.2750000000000001E-3</v>
       </c>
       <c r="E13">
-        <v>4.9569999999999996E-3</v>
+        <v>4.7063000000000009E-3</v>
       </c>
       <c r="F13">
-        <v>3.9035199999999992E-2</v>
+        <v>3.6254699999999987E-2</v>
       </c>
       <c r="G13">
-        <v>1.1445725E-2</v>
+        <v>1.0672075E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2434,19 +2386,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.438E-4</v>
+        <v>4.217E-4</v>
       </c>
       <c r="D14">
-        <v>1.317E-3</v>
+        <v>1.3135E-3</v>
       </c>
       <c r="E14">
-        <v>4.9014999999999996E-3</v>
+        <v>4.7132000000000007E-3</v>
       </c>
       <c r="F14">
-        <v>3.2273800000000012E-2</v>
+        <v>3.0981100000000001E-2</v>
       </c>
       <c r="G14">
-        <v>9.7340250000000021E-3</v>
+        <v>9.3573750000000011E-3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2457,19 +2409,19 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>4.2749999999999998E-4</v>
+        <v>4.1550000000000002E-4</v>
       </c>
       <c r="D15">
-        <v>1.3331E-3</v>
+        <v>1.3136999999999999E-3</v>
       </c>
       <c r="E15">
-        <v>5.6214000000000004E-3</v>
+        <v>5.2727999999999994E-3</v>
       </c>
       <c r="F15">
-        <v>3.1568499999999999E-2</v>
+        <v>3.0270399999999999E-2</v>
       </c>
       <c r="G15">
-        <v>9.7376249999999998E-3</v>
+        <v>9.318100000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2480,19 +2432,19 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>4.996E-4</v>
+        <v>4.6690000000000002E-4</v>
       </c>
       <c r="D16">
-        <v>2.7618999999999999E-3</v>
+        <v>2.6624999999999999E-3</v>
       </c>
       <c r="E16">
-        <v>1.8643900000000001E-2</v>
+        <v>1.75604E-2</v>
       </c>
       <c r="F16">
-        <v>0.1260309</v>
+        <v>0.1195623</v>
       </c>
       <c r="G16">
-        <v>3.6984074999999998E-2</v>
+        <v>3.5063024999999998E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2503,19 +2455,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>4.639E-4</v>
+        <v>5.0109999999999998E-4</v>
       </c>
       <c r="D17">
-        <v>2.8879000000000001E-3</v>
+        <v>2.8057999999999998E-3</v>
       </c>
       <c r="E17">
-        <v>1.7897300000000001E-2</v>
+        <v>1.7082199999999999E-2</v>
       </c>
       <c r="F17">
-        <v>0.11432489999999999</v>
+        <v>0.108762</v>
       </c>
       <c r="G17">
-        <v>3.38935E-2</v>
+        <v>3.2287774999999998E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2526,19 +2478,19 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3.6180000000000001E-4</v>
+        <v>3.4519999999999999E-4</v>
       </c>
       <c r="D18">
-        <v>9.5710000000000001E-4</v>
+        <v>9.1719999999999996E-4</v>
       </c>
       <c r="E18">
-        <v>3.0130000000000001E-3</v>
+        <v>2.9456E-3</v>
       </c>
       <c r="F18">
-        <v>1.07975E-2</v>
+        <v>1.01119E-2</v>
       </c>
       <c r="G18">
-        <v>3.7823499999999999E-3</v>
+        <v>3.579975E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2549,19 +2501,19 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.1179999999999999E-4</v>
+        <v>3.0259999999999998E-4</v>
       </c>
       <c r="D19">
-        <v>6.669E-4</v>
+        <v>6.4720000000000001E-4</v>
       </c>
       <c r="E19">
-        <v>2.4746999999999998E-3</v>
+        <v>2.3709E-3</v>
       </c>
       <c r="F19">
-        <v>8.9954000000000006E-3</v>
+        <v>8.5762999999999985E-3</v>
       </c>
       <c r="G19">
-        <v>3.1121999999999999E-3</v>
+        <v>2.974249999999999E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2572,19 +2524,19 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>4.0289999999999998E-4</v>
+        <v>3.6240000000000003E-4</v>
       </c>
       <c r="D20">
-        <v>1.1865999999999999E-3</v>
+        <v>1.1299000000000001E-3</v>
       </c>
       <c r="E20">
-        <v>3.8961E-3</v>
+        <v>3.7607000000000001E-3</v>
       </c>
       <c r="F20">
-        <v>1.47949E-2</v>
+        <v>1.39936E-2</v>
       </c>
       <c r="G20">
-        <v>5.0701250000000008E-3</v>
+        <v>4.8116499999999998E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2595,19 +2547,19 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>4.9390000000000002E-4</v>
+        <v>4.6079999999999998E-4</v>
       </c>
       <c r="D21">
-        <v>1.4488000000000001E-3</v>
+        <v>1.3504999999999999E-3</v>
       </c>
       <c r="E21">
-        <v>5.1440000000000001E-3</v>
+        <v>4.8694000000000003E-3</v>
       </c>
       <c r="F21">
-        <v>2.0831499999999999E-2</v>
+        <v>1.96356E-2</v>
       </c>
       <c r="G21">
-        <v>6.979550000000001E-3</v>
+        <v>6.5790750000000002E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2618,42 +2570,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>4.5219999999999999E-4</v>
+        <v>6.4709999999999995E-4</v>
       </c>
       <c r="D22">
-        <v>1.3975000000000001E-3</v>
+        <v>3.7268000000000002E-3</v>
       </c>
       <c r="E22">
-        <v>4.9699000000000002E-3</v>
+        <v>2.6713899999999999E-2</v>
       </c>
       <c r="F22">
-        <v>1.8698900000000001E-2</v>
+        <v>0.2003856</v>
       </c>
       <c r="G22">
-        <v>6.3796249999999999E-3</v>
+        <v>5.7868349999999999E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>6.1910000000000014E-4</v>
+        <v>3.9390000000000009E-4</v>
       </c>
       <c r="D23">
-        <v>3.8284E-3</v>
+        <v>1.1657E-3</v>
       </c>
       <c r="E23">
-        <v>2.8238800000000001E-2</v>
+        <v>3.3812E-3</v>
       </c>
       <c r="F23">
-        <v>0.2121102</v>
+        <v>1.31025E-2</v>
       </c>
       <c r="G23">
-        <v>6.1199125E-2</v>
+        <v>4.5108250000000004E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2664,19 +2616,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>4.171E-4</v>
+        <v>4.0870000000000001E-4</v>
       </c>
       <c r="D24">
-        <v>1.2130999999999999E-3</v>
+        <v>1.1922E-3</v>
       </c>
       <c r="E24">
-        <v>3.6338999999999998E-3</v>
+        <v>3.4302999999999998E-3</v>
       </c>
       <c r="F24">
-        <v>1.3449300000000001E-2</v>
+        <v>1.2855999999999999E-2</v>
       </c>
       <c r="G24">
-        <v>4.6783500000000004E-3</v>
+        <v>4.4717999999999997E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2687,19 +2639,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>4.2690000000000002E-4</v>
+        <v>4.6769999999999998E-4</v>
       </c>
       <c r="D25">
-        <v>1.2130999999999999E-3</v>
+        <v>1.2600999999999999E-3</v>
       </c>
       <c r="E25">
-        <v>3.4827E-3</v>
+        <v>3.9680999999999996E-3</v>
       </c>
       <c r="F25">
-        <v>1.3686200000000001E-2</v>
+        <v>1.44168E-2</v>
       </c>
       <c r="G25">
-        <v>4.702225E-3</v>
+        <v>5.0281750000000002E-3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2710,19 +2662,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>4.4470000000000002E-4</v>
+        <v>3.59E-4</v>
       </c>
       <c r="D26">
-        <v>1.2749E-3</v>
+        <v>1.457E-3</v>
       </c>
       <c r="E26">
-        <v>4.0380000000000008E-3</v>
+        <v>6.2226999999999994E-3</v>
       </c>
       <c r="F26">
-        <v>1.5634800000000001E-2</v>
+        <v>2.58129E-2</v>
       </c>
       <c r="G26">
-        <v>5.3480999999999997E-3</v>
+        <v>8.4628999999999989E-3</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2733,19 +2685,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>3.5409999999999999E-4</v>
+        <v>3.5770000000000002E-4</v>
       </c>
       <c r="D27">
-        <v>1.5437000000000001E-3</v>
+        <v>1.5666E-3</v>
       </c>
       <c r="E27">
-        <v>6.5778999999999994E-3</v>
+        <v>6.2203999999999992E-3</v>
       </c>
       <c r="F27">
-        <v>2.77541E-2</v>
+        <v>2.54874E-2</v>
       </c>
       <c r="G27">
-        <v>9.0574500000000016E-3</v>
+        <v>8.4080249999999995E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2756,19 +2708,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.6460000000000003E-4</v>
+        <v>3.9619999999999998E-4</v>
       </c>
       <c r="D28">
-        <v>1.5866999999999999E-3</v>
+        <v>1.4492999999999999E-3</v>
       </c>
       <c r="E28">
-        <v>6.3579999999999999E-3</v>
+        <v>5.3001999999999997E-3</v>
       </c>
       <c r="F28">
-        <v>2.6405600000000001E-2</v>
+        <v>2.2402499999999999E-2</v>
       </c>
       <c r="G28">
-        <v>8.678725E-3</v>
+        <v>7.3870499999999992E-3</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2779,19 +2731,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>3.8930000000000008E-4</v>
+        <v>4.5730000000000011E-4</v>
       </c>
       <c r="D29">
-        <v>1.4827E-3</v>
+        <v>1.4059999999999999E-3</v>
       </c>
       <c r="E29">
-        <v>5.8430000000000001E-3</v>
+        <v>4.8935000000000003E-3</v>
       </c>
       <c r="F29">
-        <v>2.3451099999999999E-2</v>
+        <v>3.2951599999999998E-2</v>
       </c>
       <c r="G29">
-        <v>7.7915249999999997E-3</v>
+        <v>9.9271000000000012E-3</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2802,19 +2754,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>5.1209999999999993E-4</v>
+        <v>4.4860000000000001E-4</v>
       </c>
       <c r="D30">
-        <v>1.3979999999999999E-3</v>
+        <v>1.3891999999999999E-3</v>
       </c>
       <c r="E30">
-        <v>5.1314000000000004E-3</v>
+        <v>5.5275000000000003E-3</v>
       </c>
       <c r="F30">
-        <v>3.2882300000000003E-2</v>
+        <v>3.06004E-2</v>
       </c>
       <c r="G30">
-        <v>9.9809499999999989E-3</v>
+        <v>9.4914249999999995E-3</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2825,19 +2777,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>4.5980000000000001E-4</v>
+        <v>4.2329999999999999E-4</v>
       </c>
       <c r="D31">
-        <v>1.4379E-3</v>
+        <v>1.2757000000000001E-3</v>
       </c>
       <c r="E31">
-        <v>5.8471999999999986E-3</v>
+        <v>5.4469999999999996E-3</v>
       </c>
       <c r="F31">
-        <v>3.2521500000000002E-2</v>
+        <v>2.8499099999999999E-2</v>
       </c>
       <c r="G31">
-        <v>1.00666E-2</v>
+        <v>8.9112749999999998E-3</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2848,19 +2800,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>4.5409999999999998E-4</v>
+        <v>5.5690000000000015E-4</v>
       </c>
       <c r="D32">
-        <v>1.3855E-3</v>
+        <v>2.8116999999999999E-3</v>
       </c>
       <c r="E32">
-        <v>5.5382000000000001E-3</v>
+        <v>1.7639599999999998E-2</v>
       </c>
       <c r="F32">
-        <v>3.0172500000000001E-2</v>
+        <v>0.1097167</v>
       </c>
       <c r="G32">
-        <v>9.3875750000000004E-3</v>
+        <v>3.2681225000000001E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2871,19 +2823,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>5.0539999999999992E-4</v>
+        <v>3.3480000000000001E-4</v>
       </c>
       <c r="D33">
-        <v>2.9743999999999999E-3</v>
+        <v>9.6080000000000004E-4</v>
       </c>
       <c r="E33">
-        <v>1.8339500000000002E-2</v>
+        <v>3.4223999999999999E-3</v>
       </c>
       <c r="F33">
-        <v>0.1149911</v>
+        <v>1.1478199999999999E-2</v>
       </c>
       <c r="G33">
-        <v>3.42026E-2</v>
+        <v>4.0490500000000002E-3</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2894,19 +2846,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>3.4380000000000001E-4</v>
+        <v>3.4650000000000002E-4</v>
       </c>
       <c r="D34">
-        <v>9.7839999999999993E-4</v>
+        <v>1.2093E-3</v>
       </c>
       <c r="E34">
-        <v>3.3655E-3</v>
+        <v>2.7206000000000001E-3</v>
       </c>
       <c r="F34">
-        <v>1.2399E-2</v>
+        <v>1.04828E-2</v>
       </c>
       <c r="G34">
-        <v>4.2716750000000008E-3</v>
+        <v>3.6898E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2917,19 +2869,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>3.7659999999999999E-4</v>
+        <v>4.17E-4</v>
       </c>
       <c r="D35">
-        <v>1.3138E-3</v>
+        <v>9.5399999999999999E-4</v>
       </c>
       <c r="E35">
-        <v>2.9816999999999999E-3</v>
+        <v>2.8495999999999999E-3</v>
       </c>
       <c r="F35">
-        <v>1.1266200000000001E-2</v>
+        <v>1.0089300000000001E-2</v>
       </c>
       <c r="G35">
-        <v>3.9845749999999997E-3</v>
+        <v>3.5774750000000001E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2940,19 +2892,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.9689999999999989E-4</v>
+        <v>3.321E-4</v>
       </c>
       <c r="D36">
-        <v>1.1502000000000001E-3</v>
+        <v>6.533E-4</v>
       </c>
       <c r="E36">
-        <v>3.0831000000000001E-3</v>
+        <v>2.4242000000000001E-3</v>
       </c>
       <c r="F36">
-        <v>1.0868600000000001E-2</v>
+        <v>8.5919000000000013E-3</v>
       </c>
       <c r="G36">
-        <v>3.8747E-3</v>
+        <v>3.000375E-3</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2963,19 +2915,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>3.3990000000000002E-4</v>
+        <v>2.8679999999999998E-4</v>
       </c>
       <c r="D37">
-        <v>1.1378E-3</v>
+        <v>6.8689999999999995E-4</v>
       </c>
       <c r="E37">
-        <v>4.1163999999999992E-3</v>
+        <v>1.9995999999999998E-3</v>
       </c>
       <c r="F37">
-        <v>2.1079500000000001E-2</v>
+        <v>8.0951000000000009E-3</v>
       </c>
       <c r="G37">
-        <v>6.6683999999999997E-3</v>
+        <v>2.7671000000000002E-3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2986,134 +2938,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>3.4160000000000001E-4</v>
+        <v>4.0939999999999998E-4</v>
       </c>
       <c r="D38">
-        <v>7.4549999999999996E-4</v>
+        <v>1.2592E-3</v>
       </c>
       <c r="E38">
-        <v>2.5634999999999998E-3</v>
+        <v>3.8595000000000001E-3</v>
       </c>
       <c r="F38">
-        <v>9.1440999999999988E-3</v>
+        <v>1.3997799999999999E-2</v>
       </c>
       <c r="G38">
-        <v>3.1986750000000002E-3</v>
+        <v>4.8814749999999997E-3</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>3.2489999999999998E-4</v>
+        <v>4.7150000000000002E-4</v>
       </c>
       <c r="D39">
-        <v>6.692E-4</v>
+        <v>1.2359999999999999E-3</v>
       </c>
       <c r="E39">
-        <v>2.4692E-3</v>
+        <v>3.7206000000000001E-3</v>
       </c>
       <c r="F39">
-        <v>9.0197000000000003E-3</v>
+        <v>1.3164E-2</v>
       </c>
       <c r="G39">
-        <v>3.1207499999999998E-3</v>
+        <v>4.6480250000000001E-3</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>2.9819999999999998E-4</v>
+        <v>4.2830000000000011E-4</v>
       </c>
       <c r="D40">
-        <v>7.2400000000000003E-4</v>
+        <v>1.315E-3</v>
       </c>
       <c r="E40">
-        <v>2.0173999999999999E-3</v>
+        <v>4.1281999999999994E-3</v>
       </c>
       <c r="F40">
-        <v>8.5757999999999997E-3</v>
+        <v>1.5266999999999999E-2</v>
       </c>
       <c r="G40">
-        <v>2.9038499999999999E-3</v>
+        <v>5.2846249999999994E-3</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>4.1229999999999999E-4</v>
+        <v>4.6860000000000001E-4</v>
       </c>
       <c r="D41">
-        <v>1.2535000000000001E-3</v>
+        <v>1.2955E-3</v>
       </c>
       <c r="E41">
-        <v>4.0108000000000001E-3</v>
+        <v>4.003399999999999E-3</v>
       </c>
       <c r="F41">
-        <v>1.5023399999999999E-2</v>
+        <v>1.45238E-2</v>
       </c>
       <c r="G41">
-        <v>5.1750000000000008E-3</v>
+        <v>5.0728250000000004E-3</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>3.8769999999999999E-4</v>
+        <v>4.014E-4</v>
       </c>
       <c r="D42">
-        <v>1.2248999999999999E-3</v>
+        <v>1.6611E-3</v>
       </c>
       <c r="E42">
-        <v>3.7012E-3</v>
+        <v>6.3416999999999996E-3</v>
       </c>
       <c r="F42">
-        <v>1.4000500000000001E-2</v>
+        <v>2.60238E-2</v>
       </c>
       <c r="G42">
-        <v>4.8285749999999999E-3</v>
+        <v>8.6070000000000001E-3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.0200000000000006E-4</v>
+        <v>5.0760000000000009E-4</v>
       </c>
       <c r="D43">
-        <v>1.4653999999999999E-3</v>
+        <v>1.3917999999999999E-3</v>
       </c>
       <c r="E43">
-        <v>4.9946999999999986E-3</v>
+        <v>5.4738E-3</v>
       </c>
       <c r="F43">
-        <v>1.8775300000000002E-2</v>
+        <v>2.8909799999999999E-2</v>
       </c>
       <c r="G43">
-        <v>6.4343499999999993E-3</v>
+        <v>9.070749999999999E-3</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -3124,19 +3076,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>4.6739999999999998E-4</v>
+        <v>3.9780000000000002E-4</v>
       </c>
       <c r="D44">
-        <v>1.2957000000000001E-3</v>
+        <v>1.0667999999999999E-3</v>
       </c>
       <c r="E44">
-        <v>3.7837000000000001E-3</v>
+        <v>3.2905999999999999E-3</v>
       </c>
       <c r="F44">
-        <v>1.4410299999999999E-2</v>
+        <v>1.1816E-2</v>
       </c>
       <c r="G44">
-        <v>4.9892749999999996E-3</v>
+        <v>4.1427999999999986E-3</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -3147,19 +3099,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>4.7580000000000002E-4</v>
+        <v>4.5179999999999998E-4</v>
       </c>
       <c r="D45">
-        <v>1.3592999999999999E-3</v>
+        <v>1.0483999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>4.2341999999999996E-3</v>
+        <v>3.0376000000000001E-3</v>
       </c>
       <c r="F45">
-        <v>1.6479899999999999E-2</v>
+        <v>1.0771599999999999E-2</v>
       </c>
       <c r="G45">
-        <v>5.6372999999999996E-3</v>
+        <v>3.8273500000000002E-3</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -3170,19 +3122,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>4.5449999999999988E-4</v>
+        <v>3.8610000000000001E-4</v>
       </c>
       <c r="D46">
-        <v>1.3079999999999999E-3</v>
+        <v>1.2695E-3</v>
       </c>
       <c r="E46">
-        <v>4.1231999999999996E-3</v>
+        <v>2.8814999999999999E-3</v>
       </c>
       <c r="F46">
-        <v>1.5300599999999999E-2</v>
+        <v>1.05725E-2</v>
       </c>
       <c r="G46">
-        <v>5.2965750000000004E-3</v>
+        <v>3.7774000000000002E-3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -3193,433 +3145,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>4.0860000000000001E-4</v>
+        <v>3.2130000000000011E-4</v>
       </c>
       <c r="D47">
-        <v>1.6903E-3</v>
+        <v>7.1730000000000003E-4</v>
       </c>
       <c r="E47">
-        <v>6.6446000000000014E-3</v>
+        <v>1.9192E-3</v>
       </c>
       <c r="F47">
-        <v>2.72774E-2</v>
+        <v>8.1326000000000002E-3</v>
       </c>
       <c r="G47">
-        <v>9.0052249999999986E-3</v>
+        <v>2.7726000000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>4.9010000000000004E-4</v>
+        <v>4.994E-4</v>
       </c>
       <c r="D48">
-        <v>1.4552E-3</v>
+        <v>1.3496999999999999E-3</v>
       </c>
       <c r="E48">
-        <v>5.7250999999999986E-3</v>
+        <v>4.1098000000000011E-3</v>
       </c>
       <c r="F48">
-        <v>3.09024E-2</v>
+        <v>1.5264700000000001E-2</v>
       </c>
       <c r="G48">
-        <v>9.6432000000000011E-3</v>
+        <v>5.3059000000000014E-3</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>3.8549999999999999E-4</v>
+        <v>4.3239999999999999E-4</v>
       </c>
       <c r="D49">
-        <v>1.4495000000000001E-3</v>
+        <v>1.049E-3</v>
       </c>
       <c r="E49">
-        <v>3.5019999999999999E-3</v>
+        <v>3.0717000000000001E-3</v>
       </c>
       <c r="F49">
-        <v>1.2658000000000001E-2</v>
+        <v>1.08083E-2</v>
       </c>
       <c r="G49">
-        <v>4.4987499999999993E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>4.0709999999999997E-4</v>
-      </c>
-      <c r="D50">
-        <v>1.3606E-3</v>
-      </c>
-      <c r="E50">
-        <v>4.1877000000000008E-3</v>
-      </c>
-      <c r="F50">
-        <v>1.5524400000000001E-2</v>
-      </c>
-      <c r="G50">
-        <v>5.3699500000000001E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>4.6050000000000008E-4</v>
-      </c>
-      <c r="D51">
-        <v>1.0300000000000001E-3</v>
-      </c>
-      <c r="E51">
-        <v>3.0910999999999998E-3</v>
-      </c>
-      <c r="F51">
-        <v>1.1509500000000001E-2</v>
-      </c>
-      <c r="G51">
-        <v>4.0227750000000001E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>4.148E-4</v>
-      </c>
-      <c r="D52">
-        <v>1.4373000000000001E-3</v>
-      </c>
-      <c r="E52">
-        <v>3.0850000000000001E-3</v>
-      </c>
-      <c r="F52">
-        <v>1.14287E-2</v>
-      </c>
-      <c r="G52">
-        <v>4.0914499999999999E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>3.947E-4</v>
-      </c>
-      <c r="D53">
-        <v>9.1699999999999995E-4</v>
-      </c>
-      <c r="E53">
-        <v>2.9234999999999999E-3</v>
-      </c>
-      <c r="F53">
-        <v>1.4369699999999999E-2</v>
-      </c>
-      <c r="G53">
-        <v>4.6512250000000002E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>3.9300000000000001E-4</v>
-      </c>
-      <c r="D54">
-        <v>1.1881000000000001E-3</v>
-      </c>
-      <c r="E54">
-        <v>4.2031000000000004E-3</v>
-      </c>
-      <c r="F54">
-        <v>2.1375100000000001E-2</v>
-      </c>
-      <c r="G54">
-        <v>6.7898250000000002E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>3.5950000000000001E-4</v>
-      </c>
-      <c r="D55">
-        <v>7.5920000000000002E-4</v>
-      </c>
-      <c r="E55">
-        <v>2.5755999999999999E-3</v>
-      </c>
-      <c r="F55">
-        <v>9.1442999999999993E-3</v>
-      </c>
-      <c r="G55">
-        <v>3.2096500000000001E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>3.4630000000000001E-4</v>
-      </c>
-      <c r="D56">
-        <v>7.5599999999999994E-4</v>
-      </c>
-      <c r="E56">
-        <v>2.1700999999999999E-3</v>
-      </c>
-      <c r="F56">
-        <v>8.7115999999999982E-3</v>
-      </c>
-      <c r="G56">
-        <v>2.996E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>3.0919999999999998E-4</v>
-      </c>
-      <c r="D57">
-        <v>7.3299999999999993E-4</v>
-      </c>
-      <c r="E57">
-        <v>1.9907000000000002E-3</v>
-      </c>
-      <c r="F57">
-        <v>8.5608999999999998E-3</v>
-      </c>
-      <c r="G57">
-        <v>2.8984499999999999E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>4.2460000000000002E-4</v>
-      </c>
-      <c r="D58">
-        <v>1.2600000000000001E-3</v>
-      </c>
-      <c r="E58">
-        <v>3.8092E-3</v>
-      </c>
-      <c r="F58">
-        <v>1.4165499999999999E-2</v>
-      </c>
-      <c r="G58">
-        <v>4.9148250000000003E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>5.3919999999999999E-4</v>
-      </c>
-      <c r="D59">
-        <v>1.3931E-3</v>
-      </c>
-      <c r="E59">
-        <v>4.3406E-3</v>
-      </c>
-      <c r="F59">
-        <v>1.6293800000000001E-2</v>
-      </c>
-      <c r="G59">
-        <v>5.6416750000000014E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>4.4119999999999999E-4</v>
-      </c>
-      <c r="D60">
-        <v>1.2107999999999999E-3</v>
-      </c>
-      <c r="E60">
-        <v>4.3236999999999998E-3</v>
-      </c>
-      <c r="F60">
-        <v>1.5631200000000001E-2</v>
-      </c>
-      <c r="G60">
-        <v>5.4017249999999996E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>4.574E-4</v>
-      </c>
-      <c r="D61">
-        <v>1.0905999999999999E-3</v>
-      </c>
-      <c r="E61">
-        <v>3.174300000000001E-3</v>
-      </c>
-      <c r="F61">
-        <v>1.17327E-2</v>
-      </c>
-      <c r="G61">
-        <v>4.1137499999999994E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>4.3980000000000001E-4</v>
-      </c>
-      <c r="D62">
-        <v>1.1071E-3</v>
-      </c>
-      <c r="E62">
-        <v>2.7353E-3</v>
-      </c>
-      <c r="F62">
-        <v>1.2459599999999999E-2</v>
-      </c>
-      <c r="G62">
-        <v>4.1854499999999994E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>4.3500000000000011E-4</v>
-      </c>
-      <c r="D63">
-        <v>9.7070000000000001E-4</v>
-      </c>
-      <c r="E63">
-        <v>3.0463E-3</v>
-      </c>
-      <c r="F63">
-        <v>1.45481E-2</v>
-      </c>
-      <c r="G63">
-        <v>4.7500249999999997E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>3.4919999999999998E-4</v>
-      </c>
-      <c r="D64">
-        <v>8.7760000000000008E-4</v>
-      </c>
-      <c r="E64">
-        <v>2.1052000000000002E-3</v>
-      </c>
-      <c r="F64">
-        <v>8.7142999999999995E-3</v>
-      </c>
-      <c r="G64">
-        <v>3.0115749999999998E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>5.1850000000000008E-4</v>
-      </c>
-      <c r="D65">
-        <v>1.2325000000000001E-3</v>
-      </c>
-      <c r="E65">
-        <v>2.8352E-3</v>
-      </c>
-      <c r="F65">
-        <v>1.26508E-2</v>
-      </c>
-      <c r="G65">
-        <v>4.3092499999999997E-3</v>
+        <v>3.8403500000000002E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3630,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -4124,24 +3708,24 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -4156,10 +3740,10 @@
         <v>9</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -4170,19 +3754,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="G24">
-        <v>9.25</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4216,19 +3800,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>75.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4239,19 +3823,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4262,19 +3846,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="F28">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -4285,16 +3869,16 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>9</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G29">
         <v>9.5</v>
@@ -4317,10 +3901,10 @@
         <v>9</v>
       </c>
       <c r="F30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4331,19 +3915,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="G31">
-        <v>9.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -4354,19 +3938,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="F32">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -4377,19 +3961,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D33">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G33">
-        <v>11.25</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -4403,7 +3987,7 @@
         <v>18</v>
       </c>
       <c r="D34">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>23</v>
@@ -4412,7 +3996,7 @@
         <v>23</v>
       </c>
       <c r="G34">
-        <v>21.75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -4423,19 +4007,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -4446,19 +4030,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -4472,16 +4056,16 @@
         <v>18</v>
       </c>
       <c r="D37">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E37">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>23.75</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -4492,116 +4076,116 @@
         <v>43</v>
       </c>
       <c r="C38">
+        <v>12</v>
+      </c>
+      <c r="D38">
         <v>11</v>
       </c>
-      <c r="D38">
-        <v>10</v>
-      </c>
       <c r="E38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G39">
-        <v>21</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E40">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>21.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="F41">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="G41">
-        <v>11.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>22.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
@@ -4610,16 +4194,16 @@
         <v>9</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43">
         <v>9</v>
       </c>
       <c r="G43">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -4630,19 +4214,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44">
-        <v>9.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -4653,19 +4237,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G45">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -4676,19 +4260,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D46">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E46">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="F46">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="G46">
-        <v>75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -4699,24 +4283,24 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -4739,392 +4323,24 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>9</v>
+      </c>
+      <c r="F49">
         <v>12</v>
       </c>
-      <c r="D49">
-        <v>11</v>
-      </c>
-      <c r="E49">
-        <v>11</v>
-      </c>
-      <c r="F49">
-        <v>11</v>
-      </c>
       <c r="G49">
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>18</v>
-      </c>
-      <c r="D50">
-        <v>23</v>
-      </c>
-      <c r="E50">
-        <v>22</v>
-      </c>
-      <c r="F50">
-        <v>24</v>
-      </c>
-      <c r="G50">
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>18</v>
-      </c>
-      <c r="D51">
-        <v>23</v>
-      </c>
-      <c r="E51">
-        <v>23</v>
-      </c>
-      <c r="F51">
-        <v>24</v>
-      </c>
-      <c r="G51">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>9</v>
-      </c>
-      <c r="D52">
-        <v>10</v>
-      </c>
-      <c r="E52">
-        <v>9</v>
-      </c>
-      <c r="F52">
-        <v>9</v>
-      </c>
-      <c r="G52">
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>19</v>
-      </c>
-      <c r="D53">
-        <v>24</v>
-      </c>
-      <c r="E53">
-        <v>25</v>
-      </c>
-      <c r="F53">
-        <v>24</v>
-      </c>
-      <c r="G53">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>9</v>
-      </c>
-      <c r="D54">
-        <v>12</v>
-      </c>
-      <c r="E54">
-        <v>11</v>
-      </c>
-      <c r="F54">
-        <v>13</v>
-      </c>
-      <c r="G54">
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>11</v>
-      </c>
-      <c r="D55">
-        <v>10</v>
-      </c>
-      <c r="E55">
-        <v>10</v>
-      </c>
-      <c r="F55">
-        <v>10</v>
-      </c>
-      <c r="G55">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>9</v>
-      </c>
-      <c r="D56">
-        <v>9</v>
-      </c>
-      <c r="E56">
-        <v>9</v>
-      </c>
-      <c r="F56">
-        <v>12</v>
-      </c>
-      <c r="G56">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>18</v>
-      </c>
-      <c r="D57">
-        <v>22</v>
-      </c>
-      <c r="E57">
-        <v>22</v>
-      </c>
-      <c r="F57">
-        <v>23</v>
-      </c>
-      <c r="G57">
-        <v>21.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>12</v>
-      </c>
-      <c r="D58">
-        <v>11</v>
-      </c>
-      <c r="E58">
-        <v>11</v>
-      </c>
-      <c r="F58">
-        <v>11</v>
-      </c>
-      <c r="G58">
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>9</v>
-      </c>
-      <c r="D59">
-        <v>9</v>
-      </c>
-      <c r="E59">
-        <v>9</v>
-      </c>
-      <c r="F59">
-        <v>9</v>
-      </c>
-      <c r="G59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>9</v>
-      </c>
-      <c r="D60">
-        <v>11</v>
-      </c>
-      <c r="E60">
-        <v>9</v>
-      </c>
-      <c r="F60">
-        <v>9</v>
-      </c>
-      <c r="G60">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>9</v>
-      </c>
-      <c r="D61">
-        <v>9</v>
-      </c>
-      <c r="E61">
-        <v>9</v>
-      </c>
-      <c r="F61">
-        <v>12</v>
-      </c>
-      <c r="G61">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>20</v>
-      </c>
-      <c r="D62">
-        <v>24</v>
-      </c>
-      <c r="E62">
-        <v>24</v>
-      </c>
-      <c r="F62">
-        <v>24</v>
-      </c>
-      <c r="G62">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>12</v>
-      </c>
-      <c r="D63">
-        <v>11</v>
-      </c>
-      <c r="E63">
-        <v>10</v>
-      </c>
-      <c r="F63">
-        <v>10</v>
-      </c>
-      <c r="G63">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>9</v>
-      </c>
-      <c r="D64">
-        <v>9</v>
-      </c>
-      <c r="E64">
-        <v>9</v>
-      </c>
-      <c r="F64">
-        <v>12</v>
-      </c>
-      <c r="G64">
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>9</v>
-      </c>
-      <c r="D65">
-        <v>11</v>
-      </c>
-      <c r="E65">
-        <v>10</v>
-      </c>
-      <c r="F65">
-        <v>9</v>
-      </c>
-      <c r="G65">
         <v>9.75</v>
       </c>
     </row>
@@ -5135,7 +4351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -5629,42 +4845,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>23.55634918610405</v>
+        <v>22.612283912988389</v>
       </c>
       <c r="D22">
-        <v>48.526911934581179</v>
+        <v>46.759195742250157</v>
       </c>
       <c r="E22">
-        <v>98.468037431535464</v>
+        <v>95.665612683216509</v>
       </c>
       <c r="F22">
-        <v>198.35028842544401</v>
+        <v>193.05283202541881</v>
       </c>
       <c r="G22">
-        <v>92.225396744416173</v>
+        <v>89.522481090968483</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>22.612283912988389</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D23">
-        <v>46.759195742250157</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E23">
-        <v>95.665612683216509</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F23">
-        <v>193.05283202541881</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G23">
-        <v>89.522481090968483</v>
+        <v>89.601080778105612</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -5675,19 +4891,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>22.903391849743819</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D24">
-        <v>47.306087770882712</v>
+        <v>49.112698372208101</v>
       </c>
       <c r="E24">
-        <v>95.799708193232973</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F24">
-        <v>192.39513529856291</v>
+        <v>200.83556979968259</v>
       </c>
       <c r="G24">
-        <v>89.601080778105612</v>
+        <v>93.200270478569109</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -5707,10 +4923,10 @@
         <v>98.468037431535464</v>
       </c>
       <c r="F25">
-        <v>200.0071426749364</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G25">
-        <v>92.993163697382556</v>
+        <v>92.786056916196003</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -5721,19 +4937,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24.384776310850238</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D26">
-        <v>49.112698372208101</v>
+        <v>47.054151868677991</v>
       </c>
       <c r="E26">
-        <v>98.468037431535464</v>
+        <v>95.172840611977591</v>
       </c>
       <c r="F26">
-        <v>199.17871555019019</v>
+        <v>191.04858571919809</v>
       </c>
       <c r="G26">
-        <v>92.786056916196003</v>
+        <v>89.044742512399381</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -5744,19 +4960,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>22.903391849743819</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D27">
-        <v>47.054151868677991</v>
+        <v>49.355339059327378</v>
       </c>
       <c r="E27">
-        <v>95.172840611977591</v>
+        <v>99.296464556281663</v>
       </c>
       <c r="F27">
-        <v>191.04858571919809</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G27">
-        <v>89.044742512399381</v>
+        <v>93.053823869162386</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -5767,19 +4983,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>24.384776310850238</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D28">
-        <v>49.355339059327378</v>
+        <v>46.802215966473277</v>
       </c>
       <c r="E28">
-        <v>99.296464556281663</v>
+        <v>95.993720869188977</v>
       </c>
       <c r="F28">
-        <v>199.17871555019019</v>
+        <v>192.94076421973639</v>
       </c>
       <c r="G28">
-        <v>93.053823869162386</v>
+        <v>89.723007201836793</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -5790,19 +5006,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>23.155327751948541</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D29">
-        <v>46.802215966473277</v>
+        <v>47.042603862487432</v>
       </c>
       <c r="E29">
-        <v>95.10870539248485</v>
+        <v>95.368894328835481</v>
       </c>
       <c r="F29">
-        <v>190.8044325344818</v>
+        <v>192.0991124527755</v>
       </c>
       <c r="G29">
-        <v>88.967670411347115</v>
+        <v>89.353500623460562</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -5813,10 +5029,10 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>22.903391849743819</v>
+        <v>22.93494128361905</v>
       </c>
       <c r="D30">
-        <v>47.042603862487432</v>
+        <v>47.127201304036298</v>
       </c>
       <c r="E30">
         <v>95.368894328835481</v>
@@ -5825,7 +5041,7 @@
         <v>192.0991124527755</v>
       </c>
       <c r="G30">
-        <v>89.353500623460562</v>
+        <v>89.382537342316581</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -5836,19 +5052,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>22.93494128361905</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D31">
-        <v>47.127201304036298</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E31">
-        <v>95.368894328835481</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F31">
-        <v>192.0991124527755</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G31">
-        <v>89.382537342316581</v>
+        <v>92.225396744416173</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -5859,19 +5075,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>23.55634918610405</v>
+        <v>22.957417329238151</v>
       </c>
       <c r="D32">
-        <v>48.526911934581179</v>
+        <v>45.927810779193763</v>
       </c>
       <c r="E32">
-        <v>98.468037431535464</v>
+        <v>92.740139471718436</v>
       </c>
       <c r="F32">
-        <v>198.35028842544401</v>
+        <v>186.49127209070201</v>
       </c>
       <c r="G32">
-        <v>92.225396744416173</v>
+        <v>87.029159917713088</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -5882,19 +5098,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>22.957417329238151</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D33">
-        <v>45.927810779193763</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E33">
-        <v>92.740139471718436</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F33">
-        <v>186.49127209070201</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="G33">
-        <v>87.029159917713088</v>
+        <v>92.225396744416173</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -5928,19 +5144,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>23.55634918610405</v>
+        <v>23.08709566447531</v>
       </c>
       <c r="D35">
-        <v>48.526911934581179</v>
+        <v>47.142608793074928</v>
       </c>
       <c r="E35">
-        <v>98.468037431535464</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F35">
-        <v>198.35028842544401</v>
+        <v>192.6542644043582</v>
       </c>
       <c r="G35">
-        <v>92.225396744416173</v>
+        <v>89.631974652513236</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5951,19 +5167,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>23.08709566447531</v>
+        <v>23.785844453984339</v>
       </c>
       <c r="D36">
-        <v>47.142608793074928</v>
+        <v>48.107127263266428</v>
       </c>
       <c r="E36">
-        <v>95.643929748144473</v>
+        <v>97.590755547247568</v>
       </c>
       <c r="F36">
-        <v>192.6542644043582</v>
+        <v>196.56376190917649</v>
       </c>
       <c r="G36">
-        <v>89.631974652513236</v>
+        <v>91.511872293418705</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -5977,16 +5193,16 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D37">
-        <v>49.355339059327378</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E37">
-        <v>101.63961030678929</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F37">
-        <v>251.27922061357859</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G37">
-        <v>106.4576297914498</v>
+        <v>94.775649276110357</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -5997,134 +5213,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>23.785844453984339</v>
+        <v>22.977182167075231</v>
       </c>
       <c r="D38">
-        <v>48.107127263266428</v>
+        <v>46.489802689448211</v>
       </c>
       <c r="E38">
-        <v>97.590755547247568</v>
+        <v>94.356106399611136</v>
       </c>
       <c r="F38">
-        <v>196.56376190917649</v>
+        <v>190.09446361390371</v>
       </c>
       <c r="G38">
-        <v>91.511872293418705</v>
+        <v>88.479388717509565</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>24.142135623730951</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D39">
-        <v>49.698484809834987</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E39">
-        <v>100.8111831820431</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F39">
-        <v>203.0365799264593</v>
+        <v>192.528335978423</v>
       </c>
       <c r="G39">
-        <v>94.422095885517081</v>
+        <v>89.634380948070628</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>23.55634918610405</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D40">
-        <v>48.526911934581179</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E40">
-        <v>98.468037431535464</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F40">
-        <v>208.55129855222069</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G40">
-        <v>94.775649276110357</v>
+        <v>89.601080778105612</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>22.977182167075231</v>
+        <v>24.384776310850238</v>
       </c>
       <c r="D41">
-        <v>46.489802689448211</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E41">
-        <v>94.356106399611136</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F41">
-        <v>190.09446361390371</v>
+        <v>199.17871555019019</v>
       </c>
       <c r="G41">
-        <v>88.479388717509565</v>
+        <v>92.63961030678928</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>23.55634918610405</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D42">
-        <v>48.526911934581179</v>
+        <v>47.054151868677991</v>
       </c>
       <c r="E42">
-        <v>98.468037431535464</v>
+        <v>95.172840611977591</v>
       </c>
       <c r="F42">
-        <v>198.35028842544401</v>
+        <v>191.04858571919809</v>
       </c>
       <c r="G42">
-        <v>92.225396744416173</v>
+        <v>89.044742512399381</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>23.155327751948541</v>
+        <v>22.93494128361905</v>
       </c>
       <c r="D43">
-        <v>46.489802689448211</v>
+        <v>47.042603862487432</v>
       </c>
       <c r="E43">
-        <v>94.356106399611136</v>
+        <v>95.368894328835481</v>
       </c>
       <c r="F43">
-        <v>194.81313863108201</v>
+        <v>192.03828591093071</v>
       </c>
       <c r="G43">
-        <v>89.703593868022466</v>
+        <v>89.346181346468157</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6135,19 +5351,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>22.903391849743819</v>
+        <v>23.200058016357438</v>
       </c>
       <c r="D44">
-        <v>47.306087770882712</v>
+        <v>46.368424437027599</v>
       </c>
       <c r="E44">
-        <v>95.799708193232973</v>
+        <v>93.779855779356666</v>
       </c>
       <c r="F44">
-        <v>192.80645083145859</v>
+        <v>188.67305645252739</v>
       </c>
       <c r="G44">
-        <v>89.703909661329519</v>
+        <v>88.005348671317279</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -6158,19 +5374,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>22.903391849743819</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D45">
-        <v>47.306087770882712</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E45">
-        <v>95.799708193232973</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F45">
-        <v>192.39513529856291</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="G45">
-        <v>89.601080778105612</v>
+        <v>94.775649276110357</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -6181,19 +5397,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>24.384776310850238</v>
+        <v>23.08709566447531</v>
       </c>
       <c r="D46">
-        <v>48.526911934581179</v>
+        <v>46.386801086460778</v>
       </c>
       <c r="E46">
-        <v>98.468037431535464</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F46">
-        <v>199.17871555019019</v>
+        <v>192.6542644043582</v>
       </c>
       <c r="G46">
-        <v>92.63961030678928</v>
+        <v>89.443022725859691</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -6204,433 +5420,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>22.903391849743819</v>
+        <v>23.155327751948541</v>
       </c>
       <c r="D47">
-        <v>47.054151868677991</v>
+        <v>47.6694714437428</v>
       </c>
       <c r="E47">
-        <v>95.172840611977591</v>
+        <v>96.715443908200299</v>
       </c>
       <c r="F47">
-        <v>191.04858571919809</v>
+        <v>201.3376443991751</v>
       </c>
       <c r="G47">
-        <v>89.044742512399381</v>
+        <v>92.219471875766686</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>22.93494128361905</v>
+        <v>22.903391849743819</v>
       </c>
       <c r="D48">
-        <v>47.042603862487432</v>
+        <v>47.306087770882712</v>
       </c>
       <c r="E48">
-        <v>95.368894328835481</v>
+        <v>95.799708193232973</v>
       </c>
       <c r="F48">
-        <v>192.03828591093071</v>
+        <v>192.39513529856291</v>
       </c>
       <c r="G48">
-        <v>89.346181346468157</v>
+        <v>89.601080778105612</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>23.200058016357438</v>
+        <v>23.08709566447531</v>
       </c>
       <c r="D49">
-        <v>46.368424437027599</v>
+        <v>47.142608793074928</v>
       </c>
       <c r="E49">
-        <v>93.779855779356666</v>
+        <v>95.643929748144473</v>
       </c>
       <c r="F49">
-        <v>188.67305645252739</v>
+        <v>199.17877017245129</v>
       </c>
       <c r="G49">
-        <v>88.005348671317279</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>23.55634918610405</v>
-      </c>
-      <c r="D50">
-        <v>48.526911934581179</v>
-      </c>
-      <c r="E50">
-        <v>98.468037431535464</v>
-      </c>
-      <c r="F50">
-        <v>218.4507934888324</v>
-      </c>
-      <c r="G50">
-        <v>97.250523010263265</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>23.55634918610405</v>
-      </c>
-      <c r="D51">
-        <v>48.526911934581179</v>
-      </c>
-      <c r="E51">
-        <v>98.468037431535464</v>
-      </c>
-      <c r="F51">
-        <v>208.55129855222069</v>
-      </c>
-      <c r="G51">
-        <v>94.775649276110357</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>23.08709566447531</v>
-      </c>
-      <c r="D52">
-        <v>46.386801086460778</v>
-      </c>
-      <c r="E52">
-        <v>95.643929748144473</v>
-      </c>
-      <c r="F52">
-        <v>192.6542644043582</v>
-      </c>
-      <c r="G52">
-        <v>89.443022725859691</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>24.384776310850238</v>
-      </c>
-      <c r="D53">
-        <v>49.355339059327378</v>
-      </c>
-      <c r="E53">
-        <v>101.63961030678929</v>
-      </c>
-      <c r="F53">
-        <v>203.8650070512054</v>
-      </c>
-      <c r="G53">
-        <v>94.811183182043095</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>23.08709566447531</v>
-      </c>
-      <c r="D54">
-        <v>48.085412379312928</v>
-      </c>
-      <c r="E54">
-        <v>98.46403379269465</v>
-      </c>
-      <c r="F54">
-        <v>231.76172255520379</v>
-      </c>
-      <c r="G54">
-        <v>100.3495660979217</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>23.785844453984339</v>
-      </c>
-      <c r="D55">
-        <v>48.107127263266428</v>
-      </c>
-      <c r="E55">
-        <v>97.590755547247568</v>
-      </c>
-      <c r="F55">
-        <v>196.56376190917649</v>
-      </c>
-      <c r="G55">
-        <v>91.511872293418705</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>23.155327751948541</v>
-      </c>
-      <c r="D56">
-        <v>47.6694714437428</v>
-      </c>
-      <c r="E56">
-        <v>96.715443908200299</v>
-      </c>
-      <c r="F56">
-        <v>201.3376443991751</v>
-      </c>
-      <c r="G56">
-        <v>92.219471875766686</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>23.55634918610405</v>
-      </c>
-      <c r="D57">
-        <v>48.526911934581179</v>
-      </c>
-      <c r="E57">
-        <v>98.468037431535464</v>
-      </c>
-      <c r="F57">
-        <v>208.55129855222069</v>
-      </c>
-      <c r="G57">
-        <v>94.775649276110357</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>22.977182167075231</v>
-      </c>
-      <c r="D58">
-        <v>46.489802689448211</v>
-      </c>
-      <c r="E58">
-        <v>94.356106399611136</v>
-      </c>
-      <c r="F58">
-        <v>190.09446361390371</v>
-      </c>
-      <c r="G58">
-        <v>88.479388717509565</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>22.903391849743819</v>
-      </c>
-      <c r="D59">
-        <v>47.306087770882712</v>
-      </c>
-      <c r="E59">
-        <v>95.799708193232973</v>
-      </c>
-      <c r="F59">
-        <v>192.39513529856291</v>
-      </c>
-      <c r="G59">
-        <v>89.601080778105612</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>23.08709566447531</v>
-      </c>
-      <c r="D60">
-        <v>46.368424437027599</v>
-      </c>
-      <c r="E60">
-        <v>96.715443908200299</v>
-      </c>
-      <c r="F60">
-        <v>202.29805811351909</v>
-      </c>
-      <c r="G60">
-        <v>92.117255530805565</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>23.08709566447531</v>
-      </c>
-      <c r="D61">
-        <v>47.142608793074928</v>
-      </c>
-      <c r="E61">
-        <v>95.643929748144473</v>
-      </c>
-      <c r="F61">
-        <v>199.17877017245129</v>
-      </c>
-      <c r="G61">
         <v>91.263101094536509</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>26.384776310850231</v>
-      </c>
-      <c r="D62">
-        <v>49.355339059327378</v>
-      </c>
-      <c r="E62">
-        <v>101.63961030678929</v>
-      </c>
-      <c r="F62">
-        <v>218.4507934888324</v>
-      </c>
-      <c r="G62">
-        <v>98.957629791449818</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>24.02848514110363</v>
-      </c>
-      <c r="D63">
-        <v>48.061326267288052</v>
-      </c>
-      <c r="E63">
-        <v>98.447137061583362</v>
-      </c>
-      <c r="F63">
-        <v>197.51571612753321</v>
-      </c>
-      <c r="G63">
-        <v>92.013166149377042</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>23.155327751948541</v>
-      </c>
-      <c r="D64">
-        <v>47.6694714437428</v>
-      </c>
-      <c r="E64">
-        <v>96.715443908200299</v>
-      </c>
-      <c r="F64">
-        <v>201.3376443991751</v>
-      </c>
-      <c r="G64">
-        <v>92.219471875766686</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>23.08709566447531</v>
-      </c>
-      <c r="D65">
-        <v>48.061326267288052</v>
-      </c>
-      <c r="E65">
-        <v>98.447137061583362</v>
-      </c>
-      <c r="F65">
-        <v>202.29805811351909</v>
-      </c>
-      <c r="G65">
-        <v>92.973404276716451</v>
       </c>
     </row>
   </sheetData>
@@ -6640,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -6812,19 +5660,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E8">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F8">
-        <v>744</v>
+        <v>706</v>
       </c>
       <c r="G8">
-        <v>293</v>
+        <v>278.75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6907,16 +5755,16 @@
         <v>40</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E12">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="F12">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="G12">
-        <v>294</v>
+        <v>278.75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -6956,13 +5804,13 @@
         <v>90</v>
       </c>
       <c r="E14">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F14">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="G14">
-        <v>230.25</v>
+        <v>227.25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -7019,19 +5867,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>107</v>
       </c>
       <c r="E17">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F17">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="G17">
-        <v>247</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -7134,42 +5982,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D22">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>706</v>
       </c>
       <c r="G22">
-        <v>20.75</v>
+        <v>278.75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E23">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F23">
-        <v>744</v>
+        <v>698</v>
       </c>
       <c r="G23">
-        <v>293</v>
+        <v>281.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -7183,16 +6031,16 @@
         <v>39</v>
       </c>
       <c r="D24">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E24">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="F24">
-        <v>698</v>
+        <v>641</v>
       </c>
       <c r="G24">
-        <v>281.75</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -7206,16 +6054,16 @@
         <v>39</v>
       </c>
       <c r="D25">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E25">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="F25">
-        <v>718</v>
+        <v>587</v>
       </c>
       <c r="G25">
-        <v>281</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -7229,16 +6077,16 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E26">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="F26">
-        <v>587</v>
+        <v>479</v>
       </c>
       <c r="G26">
-        <v>245</v>
+        <v>206.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -7249,19 +6097,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D27">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E27">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F27">
-        <v>479</v>
+        <v>547</v>
       </c>
       <c r="G27">
-        <v>206.75</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -7272,19 +6120,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D28">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E28">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="F28">
-        <v>556</v>
+        <v>685</v>
       </c>
       <c r="G28">
-        <v>236.75</v>
+        <v>278.75</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -7295,19 +6143,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D29">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E29">
-        <v>314</v>
+        <v>217</v>
       </c>
       <c r="F29">
-        <v>702</v>
+        <v>566</v>
       </c>
       <c r="G29">
-        <v>294</v>
+        <v>227.25</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7318,19 +6166,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D30">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E30">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F30">
-        <v>577</v>
+        <v>497</v>
       </c>
       <c r="G30">
-        <v>230.25</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -7344,16 +6192,16 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E31">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F31">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="G31">
-        <v>214</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -7364,19 +6212,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="E32">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="F32">
-        <v>521</v>
+        <v>560</v>
       </c>
       <c r="G32">
-        <v>219</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -7387,19 +6235,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E33">
-        <v>268</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>571</v>
+        <v>22</v>
       </c>
       <c r="G33">
-        <v>247</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -7410,19 +6258,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E34">
+        <v>21</v>
+      </c>
+      <c r="F34">
+        <v>23</v>
+      </c>
+      <c r="G34">
         <v>22</v>
-      </c>
-      <c r="F34">
-        <v>22</v>
-      </c>
-      <c r="G34">
-        <v>19.75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -7433,19 +6281,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E35">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -7456,19 +6304,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -7479,19 +6327,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -7502,134 +6350,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G38">
-        <v>14</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="F39">
-        <v>15</v>
+        <v>641</v>
       </c>
       <c r="G39">
-        <v>14</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>250</v>
       </c>
       <c r="F40">
-        <v>18</v>
+        <v>587</v>
       </c>
       <c r="G40">
-        <v>15</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D41">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="E41">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>606</v>
       </c>
       <c r="G41">
-        <v>21.75</v>
+        <v>253.25</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D42">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="E42">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>547</v>
       </c>
       <c r="G42">
-        <v>21.75</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D43">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="F43">
-        <v>23</v>
+        <v>516</v>
       </c>
       <c r="G43">
-        <v>20.75</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -7640,19 +6488,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>270</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>718</v>
+        <v>22</v>
       </c>
       <c r="G44">
-        <v>281</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -7663,19 +6511,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D45">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="E45">
-        <v>250</v>
+        <v>24</v>
       </c>
       <c r="F45">
-        <v>587</v>
+        <v>26</v>
       </c>
       <c r="G45">
-        <v>245</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -7686,19 +6534,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D46">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="E46">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="F46">
-        <v>607</v>
+        <v>23</v>
       </c>
       <c r="G46">
-        <v>253.75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -7709,433 +6557,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="D47">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>556</v>
+        <v>18</v>
       </c>
       <c r="G47">
-        <v>236.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D48">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E48">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="F48">
-        <v>521</v>
+        <v>606</v>
       </c>
       <c r="G48">
-        <v>219</v>
+        <v>253.25</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D49">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F49">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G49">
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>18</v>
-      </c>
-      <c r="D50">
-        <v>19</v>
-      </c>
-      <c r="E50">
-        <v>30</v>
-      </c>
-      <c r="F50">
-        <v>27</v>
-      </c>
-      <c r="G50">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>18</v>
-      </c>
-      <c r="D51">
-        <v>24</v>
-      </c>
-      <c r="E51">
-        <v>24</v>
-      </c>
-      <c r="F51">
-        <v>26</v>
-      </c>
-      <c r="G51">
         <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>16</v>
-      </c>
-      <c r="D52">
-        <v>28</v>
-      </c>
-      <c r="E52">
-        <v>21</v>
-      </c>
-      <c r="F52">
-        <v>23</v>
-      </c>
-      <c r="G52">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>17</v>
-      </c>
-      <c r="D53">
-        <v>18</v>
-      </c>
-      <c r="E53">
-        <v>23</v>
-      </c>
-      <c r="F53">
-        <v>24</v>
-      </c>
-      <c r="G53">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>16</v>
-      </c>
-      <c r="D54">
-        <v>26</v>
-      </c>
-      <c r="E54">
-        <v>28</v>
-      </c>
-      <c r="F54">
-        <v>42</v>
-      </c>
-      <c r="G54">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>13</v>
-      </c>
-      <c r="D55">
-        <v>13</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-      <c r="F55">
-        <v>15</v>
-      </c>
-      <c r="G55">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>12</v>
-      </c>
-      <c r="D56">
-        <v>15</v>
-      </c>
-      <c r="E56">
-        <v>15</v>
-      </c>
-      <c r="F56">
-        <v>18</v>
-      </c>
-      <c r="G56">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>12</v>
-      </c>
-      <c r="D57">
-        <v>15</v>
-      </c>
-      <c r="E57">
-        <v>15</v>
-      </c>
-      <c r="F57">
-        <v>18</v>
-      </c>
-      <c r="G57">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>14</v>
-      </c>
-      <c r="D58">
-        <v>24</v>
-      </c>
-      <c r="E58">
-        <v>24</v>
-      </c>
-      <c r="F58">
-        <v>25</v>
-      </c>
-      <c r="G58">
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>40</v>
-      </c>
-      <c r="D59">
-        <v>104</v>
-      </c>
-      <c r="E59">
-        <v>264</v>
-      </c>
-      <c r="F59">
-        <v>607</v>
-      </c>
-      <c r="G59">
-        <v>253.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>18</v>
-      </c>
-      <c r="D60">
-        <v>19</v>
-      </c>
-      <c r="E60">
-        <v>30</v>
-      </c>
-      <c r="F60">
-        <v>27</v>
-      </c>
-      <c r="G60">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>18</v>
-      </c>
-      <c r="D61">
-        <v>24</v>
-      </c>
-      <c r="E61">
-        <v>24</v>
-      </c>
-      <c r="F61">
-        <v>26</v>
-      </c>
-      <c r="G61">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>17</v>
-      </c>
-      <c r="D62">
-        <v>23</v>
-      </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
-      <c r="F62">
-        <v>22</v>
-      </c>
-      <c r="G62">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>17</v>
-      </c>
-      <c r="D63">
-        <v>18</v>
-      </c>
-      <c r="E63">
-        <v>23</v>
-      </c>
-      <c r="F63">
-        <v>24</v>
-      </c>
-      <c r="G63">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>12</v>
-      </c>
-      <c r="D64">
-        <v>15</v>
-      </c>
-      <c r="E64">
-        <v>15</v>
-      </c>
-      <c r="F64">
-        <v>18</v>
-      </c>
-      <c r="G64">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>17</v>
-      </c>
-      <c r="D65">
-        <v>23</v>
-      </c>
-      <c r="E65">
-        <v>20</v>
-      </c>
-      <c r="F65">
-        <v>22</v>
-      </c>
-      <c r="G65">
-        <v>20.5</v>
       </c>
     </row>
   </sheetData>
@@ -8145,7 +6625,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -8317,7 +6797,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D8">
         <v>289</v>
@@ -8329,7 +6809,7 @@
         <v>4951</v>
       </c>
       <c r="G8">
-        <v>1630</v>
+        <v>1630.75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -8412,16 +6892,16 @@
         <v>54</v>
       </c>
       <c r="D12">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E12">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F12">
-        <v>3469</v>
+        <v>3472</v>
       </c>
       <c r="G12">
-        <v>1133.25</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -8464,10 +6944,10 @@
         <v>130</v>
       </c>
       <c r="F14">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G14">
-        <v>176.25</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -8524,7 +7004,7 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17">
         <v>192</v>
@@ -8536,7 +7016,7 @@
         <v>2870</v>
       </c>
       <c r="G17">
-        <v>962.25</v>
+        <v>962.75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -8639,42 +7119,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D22">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>1212</v>
       </c>
       <c r="F22">
-        <v>64</v>
+        <v>4951</v>
       </c>
       <c r="G22">
-        <v>55.25</v>
+        <v>1630.75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
+        <v>27</v>
+      </c>
+      <c r="D23">
         <v>68</v>
       </c>
-      <c r="D23">
-        <v>289</v>
-      </c>
       <c r="E23">
-        <v>1212</v>
+        <v>191</v>
       </c>
       <c r="F23">
-        <v>4951</v>
+        <v>529</v>
       </c>
       <c r="G23">
-        <v>1630</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -8688,16 +7168,16 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E24">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F24">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="G24">
-        <v>203.75</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -8708,19 +7188,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E25">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F25">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="G25">
-        <v>216.75</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -8731,19 +7211,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D26">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="E26">
-        <v>192</v>
+        <v>742</v>
       </c>
       <c r="F26">
-        <v>573</v>
+        <v>2901</v>
       </c>
       <c r="G26">
-        <v>217</v>
+        <v>971.25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -8754,19 +7234,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E27">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F27">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="G27">
-        <v>971.25</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -8777,19 +7257,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D28">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="E28">
-        <v>743</v>
+        <v>814</v>
       </c>
       <c r="F28">
-        <v>2905</v>
+        <v>3472</v>
       </c>
       <c r="G28">
-        <v>974.5</v>
+        <v>1138.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -8800,19 +7280,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D29">
-        <v>213</v>
+        <v>50</v>
       </c>
       <c r="E29">
-        <v>797</v>
+        <v>130</v>
       </c>
       <c r="F29">
-        <v>3469</v>
+        <v>503</v>
       </c>
       <c r="G29">
-        <v>1133.25</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -8823,19 +7303,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F30">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="G30">
-        <v>176.25</v>
+        <v>171.75</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -8849,16 +7329,16 @@
         <v>21</v>
       </c>
       <c r="D31">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F31">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="G31">
-        <v>171.75</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -8869,19 +7349,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D32">
-        <v>49</v>
+        <v>192</v>
       </c>
       <c r="E32">
-        <v>134</v>
+        <v>740</v>
       </c>
       <c r="F32">
-        <v>461</v>
+        <v>2870</v>
       </c>
       <c r="G32">
-        <v>166.25</v>
+        <v>962.75</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -8892,19 +7372,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D33">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="E33">
-        <v>740</v>
+        <v>41</v>
       </c>
       <c r="F33">
-        <v>2870</v>
+        <v>41</v>
       </c>
       <c r="G33">
-        <v>962.25</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -8915,19 +7395,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D34">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E34">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F34">
         <v>41</v>
       </c>
       <c r="G34">
-        <v>35.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -8938,19 +7418,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D35">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F35">
         <v>41</v>
       </c>
       <c r="G35">
-        <v>42</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -8961,19 +7441,19 @@
         <v>41</v>
       </c>
       <c r="C36">
+        <v>18</v>
+      </c>
+      <c r="D36">
+        <v>25</v>
+      </c>
+      <c r="E36">
         <v>31</v>
       </c>
-      <c r="D36">
-        <v>43</v>
-      </c>
-      <c r="E36">
-        <v>43</v>
-      </c>
       <c r="F36">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G36">
-        <v>39.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -8984,19 +7464,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D37">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E37">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F37">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -9007,70 +7487,70 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D38">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E38">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G38">
-        <v>26</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D39">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>547</v>
       </c>
       <c r="G39">
-        <v>26</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="F40">
-        <v>26</v>
+        <v>573</v>
       </c>
       <c r="G40">
-        <v>23</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -9079,62 +7559,62 @@
         <v>29</v>
       </c>
       <c r="D41">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E41">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="F41">
-        <v>50</v>
+        <v>566</v>
       </c>
       <c r="G41">
-        <v>44.5</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D42">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="E42">
-        <v>48</v>
+        <v>743</v>
       </c>
       <c r="F42">
-        <v>49</v>
+        <v>2900</v>
       </c>
       <c r="G42">
-        <v>44</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D43">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E43">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="F43">
-        <v>64</v>
+        <v>461</v>
       </c>
       <c r="G43">
-        <v>55.25</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -9145,19 +7625,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D44">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="E44">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="F44">
-        <v>586</v>
+        <v>41</v>
       </c>
       <c r="G44">
-        <v>216.75</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -9168,19 +7648,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="E45">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="F45">
-        <v>573</v>
+        <v>35</v>
       </c>
       <c r="G45">
-        <v>217</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -9191,19 +7671,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D46">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E46">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="F46">
-        <v>565</v>
+        <v>41</v>
       </c>
       <c r="G46">
-        <v>215.75</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -9214,433 +7694,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="D47">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E47">
-        <v>743</v>
+        <v>24</v>
       </c>
       <c r="F47">
-        <v>2905</v>
+        <v>26</v>
       </c>
       <c r="G47">
-        <v>974.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D48">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E48">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="F48">
-        <v>461</v>
+        <v>566</v>
       </c>
       <c r="G48">
-        <v>166.25</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E49">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F49">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G49">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>26</v>
-      </c>
-      <c r="D50">
-        <v>30</v>
-      </c>
-      <c r="E50">
-        <v>51</v>
-      </c>
-      <c r="F50">
-        <v>49</v>
-      </c>
-      <c r="G50">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>25</v>
-      </c>
-      <c r="D51">
-        <v>36</v>
-      </c>
-      <c r="E51">
-        <v>36</v>
-      </c>
-      <c r="F51">
-        <v>35</v>
-      </c>
-      <c r="G51">
         <v>33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>30</v>
-      </c>
-      <c r="D52">
-        <v>57</v>
-      </c>
-      <c r="E52">
-        <v>40</v>
-      </c>
-      <c r="F52">
-        <v>41</v>
-      </c>
-      <c r="G52">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>30</v>
-      </c>
-      <c r="D53">
-        <v>38</v>
-      </c>
-      <c r="E53">
-        <v>35</v>
-      </c>
-      <c r="F53">
-        <v>46</v>
-      </c>
-      <c r="G53">
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>30</v>
-      </c>
-      <c r="D54">
-        <v>49</v>
-      </c>
-      <c r="E54">
-        <v>51</v>
-      </c>
-      <c r="F54">
-        <v>66</v>
-      </c>
-      <c r="G54">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>18</v>
-      </c>
-      <c r="D55">
-        <v>25</v>
-      </c>
-      <c r="E55">
-        <v>31</v>
-      </c>
-      <c r="F55">
-        <v>30</v>
-      </c>
-      <c r="G55">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>17</v>
-      </c>
-      <c r="D56">
-        <v>25</v>
-      </c>
-      <c r="E56">
-        <v>24</v>
-      </c>
-      <c r="F56">
-        <v>26</v>
-      </c>
-      <c r="G56">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>17</v>
-      </c>
-      <c r="D57">
-        <v>25</v>
-      </c>
-      <c r="E57">
-        <v>24</v>
-      </c>
-      <c r="F57">
-        <v>26</v>
-      </c>
-      <c r="G57">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>29</v>
-      </c>
-      <c r="D58">
-        <v>50</v>
-      </c>
-      <c r="E58">
-        <v>48</v>
-      </c>
-      <c r="F58">
-        <v>49</v>
-      </c>
-      <c r="G58">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>29</v>
-      </c>
-      <c r="D59">
-        <v>71</v>
-      </c>
-      <c r="E59">
-        <v>198</v>
-      </c>
-      <c r="F59">
-        <v>565</v>
-      </c>
-      <c r="G59">
-        <v>215.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>26</v>
-      </c>
-      <c r="D60">
-        <v>30</v>
-      </c>
-      <c r="E60">
-        <v>51</v>
-      </c>
-      <c r="F60">
-        <v>49</v>
-      </c>
-      <c r="G60">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>25</v>
-      </c>
-      <c r="D61">
-        <v>36</v>
-      </c>
-      <c r="E61">
-        <v>36</v>
-      </c>
-      <c r="F61">
-        <v>35</v>
-      </c>
-      <c r="G61">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>26</v>
-      </c>
-      <c r="D62">
-        <v>38</v>
-      </c>
-      <c r="E62">
-        <v>30</v>
-      </c>
-      <c r="F62">
-        <v>39</v>
-      </c>
-      <c r="G62">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>30</v>
-      </c>
-      <c r="D63">
-        <v>38</v>
-      </c>
-      <c r="E63">
-        <v>35</v>
-      </c>
-      <c r="F63">
-        <v>46</v>
-      </c>
-      <c r="G63">
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>17</v>
-      </c>
-      <c r="D64">
-        <v>25</v>
-      </c>
-      <c r="E64">
-        <v>24</v>
-      </c>
-      <c r="F64">
-        <v>26</v>
-      </c>
-      <c r="G64">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>26</v>
-      </c>
-      <c r="D65">
-        <v>38</v>
-      </c>
-      <c r="E65">
-        <v>30</v>
-      </c>
-      <c r="F65">
-        <v>39</v>
-      </c>
-      <c r="G65">
-        <v>33.25</v>
       </c>
     </row>
   </sheetData>
@@ -9650,7 +7762,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -9914,7 +8026,7 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>16</v>
@@ -9926,7 +8038,7 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>13.5</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -10144,24 +8256,24 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -10190,19 +8302,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -10222,10 +8334,10 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>12.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -10236,19 +8348,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>11.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -10259,19 +8371,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -10282,19 +8394,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>14.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -10308,13 +8420,13 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>7</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>7.25</v>
@@ -10351,19 +8463,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>7.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -10377,16 +8489,16 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -10397,19 +8509,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G33">
-        <v>9.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -10420,19 +8532,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>12</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>12</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -10443,19 +8555,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>10.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -10466,19 +8578,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -10489,19 +8601,19 @@
         <v>42</v>
       </c>
       <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>9</v>
+      </c>
+      <c r="F37">
+        <v>13</v>
+      </c>
+      <c r="G37">
         <v>10</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37">
-        <v>12</v>
-      </c>
-      <c r="F37">
-        <v>15</v>
-      </c>
-      <c r="G37">
-        <v>12.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -10512,70 +8624,70 @@
         <v>43</v>
       </c>
       <c r="C38">
+        <v>10</v>
+      </c>
+      <c r="D38">
         <v>9</v>
       </c>
-      <c r="D38">
-        <v>8</v>
-      </c>
       <c r="E38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -10584,44 +8696,44 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G41">
-        <v>9.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G42">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
@@ -10630,16 +8742,16 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F43">
         <v>7</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -10650,19 +8762,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -10673,19 +8785,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -10696,19 +8808,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F46">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G46">
-        <v>10.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -10728,15 +8840,15 @@
         <v>7</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G47">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -10759,392 +8871,24 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
+        <v>7</v>
+      </c>
+      <c r="D49">
+        <v>7</v>
+      </c>
+      <c r="E49">
+        <v>7</v>
+      </c>
+      <c r="F49">
         <v>10</v>
       </c>
-      <c r="D49">
-        <v>9</v>
-      </c>
-      <c r="E49">
-        <v>9</v>
-      </c>
-      <c r="F49">
-        <v>9</v>
-      </c>
       <c r="G49">
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>10</v>
-      </c>
-      <c r="D50">
-        <v>12</v>
-      </c>
-      <c r="E50">
-        <v>9</v>
-      </c>
-      <c r="F50">
-        <v>11</v>
-      </c>
-      <c r="G50">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>10</v>
-      </c>
-      <c r="E51">
-        <v>10</v>
-      </c>
-      <c r="F51">
-        <v>14</v>
-      </c>
-      <c r="G51">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>7</v>
-      </c>
-      <c r="D52">
-        <v>7</v>
-      </c>
-      <c r="E52">
-        <v>7</v>
-      </c>
-      <c r="F52">
-        <v>7</v>
-      </c>
-      <c r="G52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>11</v>
-      </c>
-      <c r="D53">
-        <v>12</v>
-      </c>
-      <c r="E53">
-        <v>12</v>
-      </c>
-      <c r="F53">
-        <v>12</v>
-      </c>
-      <c r="G53">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>7</v>
-      </c>
-      <c r="D54">
-        <v>10</v>
-      </c>
-      <c r="E54">
-        <v>9</v>
-      </c>
-      <c r="F54">
-        <v>11</v>
-      </c>
-      <c r="G54">
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>9</v>
-      </c>
-      <c r="D55">
-        <v>8</v>
-      </c>
-      <c r="E55">
-        <v>8</v>
-      </c>
-      <c r="F55">
-        <v>8</v>
-      </c>
-      <c r="G55">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>7</v>
-      </c>
-      <c r="D56">
-        <v>7</v>
-      </c>
-      <c r="E56">
-        <v>7</v>
-      </c>
-      <c r="F56">
-        <v>10</v>
-      </c>
-      <c r="G56">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>9</v>
-      </c>
-      <c r="D57">
-        <v>9</v>
-      </c>
-      <c r="E57">
-        <v>9</v>
-      </c>
-      <c r="F57">
-        <v>13</v>
-      </c>
-      <c r="G57">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>10</v>
-      </c>
-      <c r="D58">
-        <v>9</v>
-      </c>
-      <c r="E58">
-        <v>9</v>
-      </c>
-      <c r="F58">
-        <v>9</v>
-      </c>
-      <c r="G58">
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>7</v>
-      </c>
-      <c r="D59">
-        <v>7</v>
-      </c>
-      <c r="E59">
-        <v>7</v>
-      </c>
-      <c r="F59">
-        <v>7</v>
-      </c>
-      <c r="G59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>7</v>
-      </c>
-      <c r="D60">
-        <v>9</v>
-      </c>
-      <c r="E60">
-        <v>7</v>
-      </c>
-      <c r="F60">
-        <v>7</v>
-      </c>
-      <c r="G60">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>7</v>
-      </c>
-      <c r="D61">
-        <v>7</v>
-      </c>
-      <c r="E61">
-        <v>7</v>
-      </c>
-      <c r="F61">
-        <v>10</v>
-      </c>
-      <c r="G61">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>11</v>
-      </c>
-      <c r="D62">
-        <v>12</v>
-      </c>
-      <c r="E62">
-        <v>12</v>
-      </c>
-      <c r="F62">
-        <v>11</v>
-      </c>
-      <c r="G62">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>10</v>
-      </c>
-      <c r="D63">
-        <v>9</v>
-      </c>
-      <c r="E63">
-        <v>8</v>
-      </c>
-      <c r="F63">
-        <v>8</v>
-      </c>
-      <c r="G63">
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>7</v>
-      </c>
-      <c r="D64">
-        <v>7</v>
-      </c>
-      <c r="E64">
-        <v>7</v>
-      </c>
-      <c r="F64">
-        <v>10</v>
-      </c>
-      <c r="G64">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>7</v>
-      </c>
-      <c r="D65">
-        <v>9</v>
-      </c>
-      <c r="E65">
-        <v>8</v>
-      </c>
-      <c r="F65">
-        <v>7</v>
-      </c>
-      <c r="G65">
         <v>7.75</v>
       </c>
     </row>

--- a/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6C298A-4490-4456-A526-992277B51D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -195,8 +189,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,1540 +253,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A*</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.7899999999999998E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.7523000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.96428E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.21238599999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BDS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2.5090000000000003E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1521000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.8651999999999992E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0291699999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BRC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.9910000000000011E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2661E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.5457000000000006E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.6123799999999998E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GL</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.4989999999999999E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.5777E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.7207E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1204027</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>JPS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.2939999999999997E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.3361E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.8003999999999998E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.93978E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PPO</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.0129999999999992E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.6993E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.8210300000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.21230650000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TPF</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.3259999999999998E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.5785999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.6404199999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.20061399999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-285E-4447-96E5-7B20C4588DEA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="651940351"/>
-        <c:axId val="651941791"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="651940351"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="651941791"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="651941791"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="651940351"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="id-ID"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{330600D5-724E-9EEB-BA2C-FC5E2EDDAA96}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Red Orange">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1800,37 +267,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="505046"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E84C22"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FFBD47"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="B64926"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FF8427"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="B22600"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="666699"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1864,7 +331,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1899,10 +365,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2075,11 +540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2110,22 +575,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>5.7899999999999998E-4</v>
+        <v>0.0005783</v>
       </c>
       <c r="D2">
-        <v>3.7523000000000001E-3</v>
+        <v>0.003767</v>
       </c>
       <c r="E2">
-        <v>2.96428E-2</v>
+        <v>0.0286037</v>
       </c>
       <c r="F2">
-        <v>0.21238599999999999</v>
+        <v>0.2149593</v>
       </c>
       <c r="G2">
-        <v>6.1590025000000007E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.061977075</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2133,22 +598,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.5090000000000003E-4</v>
+        <v>0.0002715</v>
       </c>
       <c r="D3">
-        <v>1.1521000000000001E-3</v>
+        <v>0.0011483</v>
       </c>
       <c r="E3">
-        <v>4.8651999999999992E-3</v>
+        <v>0.004915399999999999</v>
       </c>
       <c r="F3">
-        <v>2.0291699999999999E-2</v>
+        <v>0.0209806</v>
       </c>
       <c r="G3">
-        <v>6.6399750000000011E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006828949999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2156,22 +621,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>3.9910000000000011E-4</v>
+        <v>0.0003959</v>
       </c>
       <c r="D4">
-        <v>1.2661E-3</v>
+        <v>0.0011636</v>
       </c>
       <c r="E4">
-        <v>4.5457000000000006E-3</v>
+        <v>0.0044836</v>
       </c>
       <c r="F4">
-        <v>3.6123799999999998E-2</v>
+        <v>0.03712889999999999</v>
       </c>
       <c r="G4">
-        <v>1.0583675000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2179,22 +644,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>4.4989999999999999E-4</v>
+        <v>0.0004581999999999999</v>
       </c>
       <c r="D5">
-        <v>2.5777E-3</v>
+        <v>0.0026755</v>
       </c>
       <c r="E5">
-        <v>1.7207E-2</v>
+        <v>0.0174665</v>
       </c>
       <c r="F5">
-        <v>0.1204027</v>
+        <v>0.1189921</v>
       </c>
       <c r="G5">
-        <v>3.5159324999999998E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.034898075</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2202,22 +667,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>4.2939999999999997E-4</v>
+        <v>0.0004442</v>
       </c>
       <c r="D6">
-        <v>1.3361E-3</v>
+        <v>0.0013483</v>
       </c>
       <c r="E6">
-        <v>4.8003999999999998E-3</v>
+        <v>0.0049826</v>
       </c>
       <c r="F6">
-        <v>1.93978E-2</v>
+        <v>0.019699</v>
       </c>
       <c r="G6">
-        <v>6.4909249999999998E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006618525</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2225,22 +690,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>6.0129999999999992E-4</v>
+        <v>0.0006286</v>
       </c>
       <c r="D7">
-        <v>3.6993E-3</v>
+        <v>0.003816</v>
       </c>
       <c r="E7">
-        <v>2.8210300000000001E-2</v>
+        <v>0.0279235</v>
       </c>
       <c r="F7">
-        <v>0.21230650000000001</v>
+        <v>0.2154486</v>
       </c>
       <c r="G7">
-        <v>6.1204349999999991E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.06195417500000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2248,22 +713,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>6.3259999999999998E-4</v>
+        <v>0.0006267000000000001</v>
       </c>
       <c r="D8">
-        <v>3.5785999999999999E-3</v>
+        <v>0.003749</v>
       </c>
       <c r="E8">
-        <v>2.6404199999999999E-2</v>
+        <v>0.0266991</v>
       </c>
       <c r="F8">
-        <v>0.20061399999999999</v>
+        <v>0.2027803000000001</v>
       </c>
       <c r="G8">
-        <v>5.7807349999999993E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05846377500000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2271,22 +736,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>3.9760000000000002E-4</v>
+        <v>0.0003835</v>
       </c>
       <c r="D9">
-        <v>1.0709999999999999E-3</v>
+        <v>0.0010966</v>
       </c>
       <c r="E9">
-        <v>3.1621000000000002E-3</v>
+        <v>0.003306</v>
       </c>
       <c r="F9">
-        <v>1.1674800000000001E-2</v>
+        <v>0.0122514</v>
       </c>
       <c r="G9">
-        <v>4.0763750000000001E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004259374999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2294,22 +759,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>2.8509999999999999E-4</v>
+        <v>0.000313</v>
       </c>
       <c r="D10">
-        <v>1.4450000000000001E-3</v>
+        <v>0.0014555</v>
       </c>
       <c r="E10">
-        <v>5.9503999999999998E-3</v>
+        <v>0.006234600000000001</v>
       </c>
       <c r="F10">
-        <v>2.5019799999999998E-2</v>
+        <v>0.0264333</v>
       </c>
       <c r="G10">
-        <v>8.1750750000000004E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0086091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2317,22 +782,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>2.9050000000000001E-4</v>
+        <v>0.0002892</v>
       </c>
       <c r="D11">
-        <v>1.2293E-3</v>
+        <v>0.0012389</v>
       </c>
       <c r="E11">
-        <v>5.0981999999999998E-3</v>
+        <v>0.0052051</v>
       </c>
       <c r="F11">
-        <v>2.1068300000000002E-2</v>
+        <v>0.0219588</v>
       </c>
       <c r="G11">
-        <v>6.9215750000000001E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007173000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2340,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>3.436E-4</v>
+        <v>0.0003774</v>
       </c>
       <c r="D12">
-        <v>1.4032000000000001E-3</v>
+        <v>0.0014233</v>
       </c>
       <c r="E12">
-        <v>5.4543999999999999E-3</v>
+        <v>0.005132900000000001</v>
       </c>
       <c r="F12">
-        <v>2.16294E-2</v>
+        <v>0.0222551</v>
       </c>
       <c r="G12">
-        <v>7.2076499999999986E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007297175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2363,22 +828,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.5229999999999988E-4</v>
+        <v>0.0004580000000000001</v>
       </c>
       <c r="D13">
-        <v>1.2750000000000001E-3</v>
+        <v>0.0013757</v>
       </c>
       <c r="E13">
-        <v>4.7063000000000009E-3</v>
+        <v>0.004751500000000001</v>
       </c>
       <c r="F13">
-        <v>3.6254699999999987E-2</v>
+        <v>0.0368989</v>
       </c>
       <c r="G13">
-        <v>1.0672075E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.010871025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2386,22 +851,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.217E-4</v>
+        <v>0.0004426</v>
       </c>
       <c r="D14">
-        <v>1.3135E-3</v>
+        <v>0.0013237</v>
       </c>
       <c r="E14">
-        <v>4.7132000000000007E-3</v>
+        <v>0.0048246</v>
       </c>
       <c r="F14">
-        <v>3.0981100000000001E-2</v>
+        <v>0.0315905</v>
       </c>
       <c r="G14">
-        <v>9.3573750000000011E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009545350000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2409,22 +874,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>4.1550000000000002E-4</v>
+        <v>0.0004036000000000001</v>
       </c>
       <c r="D15">
-        <v>1.3136999999999999E-3</v>
+        <v>0.0013724</v>
       </c>
       <c r="E15">
-        <v>5.2727999999999994E-3</v>
+        <v>0.0053778</v>
       </c>
       <c r="F15">
-        <v>3.0270399999999999E-2</v>
+        <v>0.03072160000000001</v>
       </c>
       <c r="G15">
-        <v>9.318100000000001E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009468850000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2432,22 +897,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>4.6690000000000002E-4</v>
+        <v>0.0004763</v>
       </c>
       <c r="D16">
-        <v>2.6624999999999999E-3</v>
+        <v>0.0027162</v>
       </c>
       <c r="E16">
-        <v>1.75604E-2</v>
+        <v>0.0175045</v>
       </c>
       <c r="F16">
-        <v>0.1195623</v>
+        <v>0.1205907</v>
       </c>
       <c r="G16">
-        <v>3.5063024999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.035321925</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2455,22 +920,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>5.0109999999999998E-4</v>
+        <v>0.0005182</v>
       </c>
       <c r="D17">
-        <v>2.8057999999999998E-3</v>
+        <v>0.0028039</v>
       </c>
       <c r="E17">
-        <v>1.7082199999999999E-2</v>
+        <v>0.0172739</v>
       </c>
       <c r="F17">
-        <v>0.108762</v>
+        <v>0.1106523</v>
       </c>
       <c r="G17">
-        <v>3.2287774999999998E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.032812075</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2478,22 +943,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3.4519999999999999E-4</v>
+        <v>0.0003918</v>
       </c>
       <c r="D18">
-        <v>9.1719999999999996E-4</v>
+        <v>0.0009251999999999999</v>
       </c>
       <c r="E18">
-        <v>2.9456E-3</v>
+        <v>0.0028559</v>
       </c>
       <c r="F18">
-        <v>1.01119E-2</v>
+        <v>0.0102446</v>
       </c>
       <c r="G18">
-        <v>3.579975E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003604375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2501,22 +966,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.0259999999999998E-4</v>
+        <v>0.000287</v>
       </c>
       <c r="D19">
-        <v>6.4720000000000001E-4</v>
+        <v>0.0006513999999999999</v>
       </c>
       <c r="E19">
-        <v>2.3709E-3</v>
+        <v>0.0024078</v>
       </c>
       <c r="F19">
-        <v>8.5762999999999985E-3</v>
+        <v>0.008705899999999999</v>
       </c>
       <c r="G19">
-        <v>2.974249999999999E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003013025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2524,22 +989,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>3.6240000000000003E-4</v>
+        <v>0.0003610999999999999</v>
       </c>
       <c r="D20">
-        <v>1.1299000000000001E-3</v>
+        <v>0.0011538</v>
       </c>
       <c r="E20">
-        <v>3.7607000000000001E-3</v>
+        <v>0.003820700000000001</v>
       </c>
       <c r="F20">
-        <v>1.39936E-2</v>
+        <v>0.0140924</v>
       </c>
       <c r="G20">
-        <v>4.8116499999999998E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2547,22 +1012,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>4.6079999999999998E-4</v>
+        <v>0.0004887</v>
       </c>
       <c r="D21">
-        <v>1.3504999999999999E-3</v>
+        <v>0.0013959</v>
       </c>
       <c r="E21">
-        <v>4.8694000000000003E-3</v>
+        <v>0.0049703</v>
       </c>
       <c r="F21">
-        <v>1.96356E-2</v>
+        <v>0.0200179</v>
       </c>
       <c r="G21">
-        <v>6.5790750000000002E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0067182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2570,22 +1035,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>6.4709999999999995E-4</v>
+        <v>0.0006504</v>
       </c>
       <c r="D22">
-        <v>3.7268000000000002E-3</v>
+        <v>0.0037523</v>
       </c>
       <c r="E22">
-        <v>2.6713899999999999E-2</v>
+        <v>0.0263349</v>
       </c>
       <c r="F22">
-        <v>0.2003856</v>
+        <v>0.2031395</v>
       </c>
       <c r="G22">
-        <v>5.7868349999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05846927499999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2593,22 +1058,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>3.9390000000000009E-4</v>
+        <v>0.0004438</v>
       </c>
       <c r="D23">
-        <v>1.1657E-3</v>
+        <v>0.0012397</v>
       </c>
       <c r="E23">
-        <v>3.3812E-3</v>
+        <v>0.003470200000000001</v>
       </c>
       <c r="F23">
-        <v>1.31025E-2</v>
+        <v>0.0129991</v>
       </c>
       <c r="G23">
-        <v>4.5108250000000004E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0045382</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2616,22 +1081,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>4.0870000000000001E-4</v>
+        <v>0.0003916</v>
       </c>
       <c r="D24">
-        <v>1.1922E-3</v>
+        <v>0.0012204</v>
       </c>
       <c r="E24">
-        <v>3.4302999999999998E-3</v>
+        <v>0.0035246</v>
       </c>
       <c r="F24">
-        <v>1.2855999999999999E-2</v>
+        <v>0.012923</v>
       </c>
       <c r="G24">
-        <v>4.4717999999999997E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004514900000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2639,22 +1104,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>4.6769999999999998E-4</v>
+        <v>0.0004538</v>
       </c>
       <c r="D25">
-        <v>1.2600999999999999E-3</v>
+        <v>0.0012665</v>
       </c>
       <c r="E25">
-        <v>3.9680999999999996E-3</v>
+        <v>0.0039822</v>
       </c>
       <c r="F25">
-        <v>1.44168E-2</v>
+        <v>0.0150625</v>
       </c>
       <c r="G25">
-        <v>5.0281750000000002E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00519125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2662,22 +1127,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>3.59E-4</v>
+        <v>0.0003336</v>
       </c>
       <c r="D26">
-        <v>1.457E-3</v>
+        <v>0.0015583</v>
       </c>
       <c r="E26">
-        <v>6.2226999999999994E-3</v>
+        <v>0.006352099999999999</v>
       </c>
       <c r="F26">
-        <v>2.58129E-2</v>
+        <v>0.0268639</v>
       </c>
       <c r="G26">
-        <v>8.4628999999999989E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008776975000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2685,22 +1150,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>3.5770000000000002E-4</v>
+        <v>0.0003819</v>
       </c>
       <c r="D27">
-        <v>1.5666E-3</v>
+        <v>0.0015961</v>
       </c>
       <c r="E27">
-        <v>6.2203999999999992E-3</v>
+        <v>0.006242599999999999</v>
       </c>
       <c r="F27">
-        <v>2.54874E-2</v>
+        <v>0.0260654</v>
       </c>
       <c r="G27">
-        <v>8.4080249999999995E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008571499999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2708,22 +1173,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.9619999999999998E-4</v>
+        <v>0.0004001</v>
       </c>
       <c r="D28">
-        <v>1.4492999999999999E-3</v>
+        <v>0.0015011</v>
       </c>
       <c r="E28">
-        <v>5.3001999999999997E-3</v>
+        <v>0.005512899999999999</v>
       </c>
       <c r="F28">
-        <v>2.2402499999999999E-2</v>
+        <v>0.022947</v>
       </c>
       <c r="G28">
-        <v>7.3870499999999992E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007590275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2731,22 +1196,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>4.5730000000000011E-4</v>
+        <v>0.0004685</v>
       </c>
       <c r="D29">
-        <v>1.4059999999999999E-3</v>
+        <v>0.0014033</v>
       </c>
       <c r="E29">
-        <v>4.8935000000000003E-3</v>
+        <v>0.0050414</v>
       </c>
       <c r="F29">
-        <v>3.2951599999999998E-2</v>
+        <v>0.03194420000000001</v>
       </c>
       <c r="G29">
-        <v>9.9271000000000012E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009714350000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2754,22 +1219,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>4.4860000000000001E-4</v>
+        <v>0.0004933</v>
       </c>
       <c r="D30">
-        <v>1.3891999999999999E-3</v>
+        <v>0.0014421</v>
       </c>
       <c r="E30">
-        <v>5.5275000000000003E-3</v>
+        <v>0.0057133</v>
       </c>
       <c r="F30">
-        <v>3.06004E-2</v>
+        <v>0.031275</v>
       </c>
       <c r="G30">
-        <v>9.4914249999999995E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009730925</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2777,22 +1242,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>4.2329999999999999E-4</v>
+        <v>0.000438</v>
       </c>
       <c r="D31">
-        <v>1.2757000000000001E-3</v>
+        <v>0.0013725</v>
       </c>
       <c r="E31">
-        <v>5.4469999999999996E-3</v>
+        <v>0.005280999999999999</v>
       </c>
       <c r="F31">
-        <v>2.8499099999999999E-2</v>
+        <v>0.0295881</v>
       </c>
       <c r="G31">
-        <v>8.9112749999999998E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0091699</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2800,22 +1265,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>5.5690000000000015E-4</v>
+        <v>0.0005648</v>
       </c>
       <c r="D32">
-        <v>2.8116999999999999E-3</v>
+        <v>0.0028404</v>
       </c>
       <c r="E32">
-        <v>1.7639599999999998E-2</v>
+        <v>0.0171358</v>
       </c>
       <c r="F32">
-        <v>0.1097167</v>
+        <v>0.1129472</v>
       </c>
       <c r="G32">
-        <v>3.2681225000000001E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03337205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2823,22 +1288,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>3.3480000000000001E-4</v>
+        <v>0.0005397999999999999</v>
       </c>
       <c r="D33">
-        <v>9.6080000000000004E-4</v>
+        <v>0.0010465</v>
       </c>
       <c r="E33">
-        <v>3.4223999999999999E-3</v>
+        <v>0.0032869</v>
       </c>
       <c r="F33">
-        <v>1.1478199999999999E-2</v>
+        <v>0.0118465</v>
       </c>
       <c r="G33">
-        <v>4.0490500000000002E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004179924999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2846,22 +1311,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>3.4650000000000002E-4</v>
+        <v>0.0005501</v>
       </c>
       <c r="D34">
-        <v>1.2093E-3</v>
+        <v>0.0012455</v>
       </c>
       <c r="E34">
-        <v>2.7206000000000001E-3</v>
+        <v>0.0027424</v>
       </c>
       <c r="F34">
-        <v>1.04828E-2</v>
+        <v>0.0106157</v>
       </c>
       <c r="G34">
-        <v>3.6898E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003788425</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2869,22 +1334,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>4.17E-4</v>
+        <v>0.0003911</v>
       </c>
       <c r="D35">
-        <v>9.5399999999999999E-4</v>
+        <v>0.0009901999999999999</v>
       </c>
       <c r="E35">
-        <v>2.8495999999999999E-3</v>
+        <v>0.0029881</v>
       </c>
       <c r="F35">
-        <v>1.0089300000000001E-2</v>
+        <v>0.0104352</v>
       </c>
       <c r="G35">
-        <v>3.5774750000000001E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003701149999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2892,22 +1357,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.321E-4</v>
+        <v>0.0003723</v>
       </c>
       <c r="D36">
-        <v>6.533E-4</v>
+        <v>0.0007259</v>
       </c>
       <c r="E36">
-        <v>2.4242000000000001E-3</v>
+        <v>0.0024319</v>
       </c>
       <c r="F36">
-        <v>8.5919000000000013E-3</v>
+        <v>0.0086672</v>
       </c>
       <c r="G36">
-        <v>3.000375E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003049325</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2915,22 +1380,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>2.8679999999999998E-4</v>
+        <v>0.0003903</v>
       </c>
       <c r="D37">
-        <v>6.8689999999999995E-4</v>
+        <v>0.0007314</v>
       </c>
       <c r="E37">
-        <v>1.9995999999999998E-3</v>
+        <v>0.0018907</v>
       </c>
       <c r="F37">
-        <v>8.0951000000000009E-3</v>
+        <v>0.0082445</v>
       </c>
       <c r="G37">
-        <v>2.7671000000000002E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.002814225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2938,22 +1403,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>4.0939999999999998E-4</v>
+        <v>0.0004274</v>
       </c>
       <c r="D38">
-        <v>1.2592E-3</v>
+        <v>0.0012014</v>
       </c>
       <c r="E38">
-        <v>3.8595000000000001E-3</v>
+        <v>0.0038309</v>
       </c>
       <c r="F38">
-        <v>1.3997799999999999E-2</v>
+        <v>0.0142424</v>
       </c>
       <c r="G38">
-        <v>4.8814749999999997E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004925525</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -2961,22 +1426,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>4.7150000000000002E-4</v>
+        <v>0.0004676</v>
       </c>
       <c r="D39">
-        <v>1.2359999999999999E-3</v>
+        <v>0.001364</v>
       </c>
       <c r="E39">
-        <v>3.7206000000000001E-3</v>
+        <v>0.0037042</v>
       </c>
       <c r="F39">
-        <v>1.3164E-2</v>
+        <v>0.0136118</v>
       </c>
       <c r="G39">
-        <v>4.6480250000000001E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0047869</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -2984,22 +1449,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>4.2830000000000011E-4</v>
+        <v>0.0004680999999999999</v>
       </c>
       <c r="D40">
-        <v>1.315E-3</v>
+        <v>0.0013682</v>
       </c>
       <c r="E40">
-        <v>4.1281999999999994E-3</v>
+        <v>0.004082000000000001</v>
       </c>
       <c r="F40">
-        <v>1.5266999999999999E-2</v>
+        <v>0.0157404</v>
       </c>
       <c r="G40">
-        <v>5.2846249999999994E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005414675</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3007,22 +1472,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>4.6860000000000001E-4</v>
+        <v>0.0004528999999999999</v>
       </c>
       <c r="D41">
-        <v>1.2955E-3</v>
+        <v>0.0013055</v>
       </c>
       <c r="E41">
-        <v>4.003399999999999E-3</v>
+        <v>0.0040905</v>
       </c>
       <c r="F41">
-        <v>1.45238E-2</v>
+        <v>0.014953</v>
       </c>
       <c r="G41">
-        <v>5.0728250000000004E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005200475</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -3030,22 +1495,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>4.014E-4</v>
+        <v>0.0003855</v>
       </c>
       <c r="D42">
-        <v>1.6611E-3</v>
+        <v>0.0016983</v>
       </c>
       <c r="E42">
-        <v>6.3416999999999996E-3</v>
+        <v>0.0065439</v>
       </c>
       <c r="F42">
-        <v>2.60238E-2</v>
+        <v>0.0266679</v>
       </c>
       <c r="G42">
-        <v>8.6070000000000001E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.008823900000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -3053,22 +1518,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.0760000000000009E-4</v>
+        <v>0.0005069</v>
       </c>
       <c r="D43">
-        <v>1.3917999999999999E-3</v>
+        <v>0.0013792</v>
       </c>
       <c r="E43">
-        <v>5.4738E-3</v>
+        <v>0.005646</v>
       </c>
       <c r="F43">
-        <v>2.8909799999999999E-2</v>
+        <v>0.0301075</v>
       </c>
       <c r="G43">
-        <v>9.070749999999999E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009409899999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3076,22 +1541,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>3.9780000000000002E-4</v>
+        <v>0.0008211</v>
       </c>
       <c r="D44">
-        <v>1.0667999999999999E-3</v>
+        <v>0.0010627</v>
       </c>
       <c r="E44">
-        <v>3.2905999999999999E-3</v>
+        <v>0.0034025</v>
       </c>
       <c r="F44">
-        <v>1.1816E-2</v>
+        <v>0.0118235</v>
       </c>
       <c r="G44">
-        <v>4.1427999999999986E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00427745</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3099,22 +1564,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>4.5179999999999998E-4</v>
+        <v>0.0006756999999999999</v>
       </c>
       <c r="D45">
-        <v>1.0483999999999999E-3</v>
+        <v>0.0010222</v>
       </c>
       <c r="E45">
-        <v>3.0376000000000001E-3</v>
+        <v>0.0030558</v>
       </c>
       <c r="F45">
-        <v>1.0771599999999999E-2</v>
+        <v>0.0117225</v>
       </c>
       <c r="G45">
-        <v>3.8273500000000002E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00411905</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3122,22 +1587,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>3.8610000000000001E-4</v>
+        <v>0.0004259</v>
       </c>
       <c r="D46">
-        <v>1.2695E-3</v>
+        <v>0.0013026</v>
       </c>
       <c r="E46">
-        <v>2.8814999999999999E-3</v>
+        <v>0.0028875</v>
       </c>
       <c r="F46">
-        <v>1.05725E-2</v>
+        <v>0.010974</v>
       </c>
       <c r="G46">
-        <v>3.7774000000000002E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0038975</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3145,22 +1610,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>3.2130000000000011E-4</v>
+        <v>0.0003392</v>
       </c>
       <c r="D47">
-        <v>7.1730000000000003E-4</v>
+        <v>0.0007567000000000001</v>
       </c>
       <c r="E47">
-        <v>1.9192E-3</v>
+        <v>0.0021037</v>
       </c>
       <c r="F47">
-        <v>8.1326000000000002E-3</v>
+        <v>0.008524799999999999</v>
       </c>
       <c r="G47">
-        <v>2.7726000000000001E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0029311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3168,22 +1633,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>4.994E-4</v>
+        <v>0.0004806</v>
       </c>
       <c r="D48">
-        <v>1.3496999999999999E-3</v>
+        <v>0.0014071</v>
       </c>
       <c r="E48">
-        <v>4.1098000000000011E-3</v>
+        <v>0.004325600000000001</v>
       </c>
       <c r="F48">
-        <v>1.5264700000000001E-2</v>
+        <v>0.0158202</v>
       </c>
       <c r="G48">
-        <v>5.3059000000000014E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005508375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3191,33 +1656,32 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>4.3239999999999999E-4</v>
+        <v>0.0004765999999999999</v>
       </c>
       <c r="D49">
-        <v>1.049E-3</v>
+        <v>0.0011259</v>
       </c>
       <c r="E49">
-        <v>3.0717000000000001E-3</v>
+        <v>0.0030276</v>
       </c>
       <c r="F49">
-        <v>1.08083E-2</v>
+        <v>0.0110679</v>
       </c>
       <c r="G49">
-        <v>3.8403500000000002E-3</v>
+        <v>0.0039245</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +1704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3263,7 +1727,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3286,7 +1750,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3309,7 +1773,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3332,7 +1796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3355,7 +1819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3378,7 +1842,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3401,7 +1865,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3424,7 +1888,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3447,7 +1911,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3470,7 +1934,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3493,7 +1957,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3516,7 +1980,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3539,7 +2003,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3562,7 +2026,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3585,7 +2049,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3608,7 +2072,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -3631,7 +2095,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -3654,7 +2118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -3677,7 +2141,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -3700,7 +2164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -3723,7 +2187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3746,7 +2210,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3769,7 +2233,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3792,7 +2256,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -3815,7 +2279,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3838,7 +2302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3861,7 +2325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -3884,7 +2348,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3907,7 +2371,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3930,7 +2394,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -3953,7 +2417,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -3976,7 +2440,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -3999,7 +2463,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4022,7 +2486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4045,7 +2509,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4068,7 +2532,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4091,7 +2555,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -4114,7 +2578,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -4137,7 +2601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -4160,7 +2624,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -4183,7 +2647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -4206,7 +2670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4229,7 +2693,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4252,7 +2716,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4275,7 +2739,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4298,7 +2762,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -4321,7 +2785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -4350,11 +2814,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4377,7 +2841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4388,19 +2852,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D2">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E2">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F2">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G2">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4408,22 +2872,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D3">
-        <v>49.355339059327378</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E3">
-        <v>99.296464556281663</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F3">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G3">
-        <v>93.053823869162386</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.05382386916239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4434,19 +2898,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D4">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E4">
-        <v>99.053823869162358</v>
+        <v>99.05382386916236</v>
       </c>
       <c r="F4">
-        <v>201.76450198781711</v>
+        <v>201.7645019878171</v>
       </c>
       <c r="G4">
-        <v>93.225396744416173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.22539674441617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4457,19 +2921,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D5">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E5">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F5">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G5">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4480,19 +2944,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D6">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E6">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F6">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G6">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4500,22 +2964,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>23.155327751948541</v>
+        <v>23.15532775194854</v>
       </c>
       <c r="D7">
-        <v>47.354277394962487</v>
+        <v>47.35427739496249</v>
       </c>
       <c r="E7">
-        <v>94.356106399611136</v>
+        <v>94.35610639961114</v>
       </c>
       <c r="F7">
         <v>193.5523624359607</v>
       </c>
       <c r="G7">
-        <v>89.604518495620724</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.60451849562072</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4526,19 +2990,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D8">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E8">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F8">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G8">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4546,22 +3010,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D9">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E9">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F9">
-        <v>200.83556979968259</v>
+        <v>200.8355697996826</v>
       </c>
       <c r="G9">
-        <v>93.053823869162372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.05382386916237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4569,22 +3033,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D10">
-        <v>49.355339059327378</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E10">
-        <v>99.296464556281663</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F10">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G10">
-        <v>93.053823869162386</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.05382386916239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4592,22 +3056,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D11">
-        <v>47.306087770882712</v>
+        <v>47.30608777088271</v>
       </c>
       <c r="E11">
-        <v>93.358333116676704</v>
+        <v>93.3583331166767</v>
       </c>
       <c r="F11">
         <v>189.2486212678381</v>
       </c>
       <c r="G11">
-        <v>88.204108501285347</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88.20410850128535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4615,22 +3079,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D12">
-        <v>49.355339059327378</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E12">
-        <v>99.296464556281663</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F12">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G12">
-        <v>93.053823869162386</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.05382386916239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4638,22 +3102,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D13">
-        <v>47.042603862487432</v>
+        <v>47.04260386248743</v>
       </c>
       <c r="E13">
-        <v>95.399307599757918</v>
+        <v>95.39930759975792</v>
       </c>
       <c r="F13">
-        <v>192.06714970508381</v>
+        <v>192.0671497050838</v>
       </c>
       <c r="G13">
-        <v>89.353113254268251</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.35311325426825</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4664,19 +3128,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D14">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E14">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F14">
-        <v>201.17871555019019</v>
+        <v>201.1787155501902</v>
       </c>
       <c r="G14">
-        <v>92.932503525602726</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.93250352560273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4687,19 +3151,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D15">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E15">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F15">
         <v>198.9360748630709</v>
       </c>
       <c r="G15">
-        <v>92.371843353822896</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.3718433538229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4707,22 +3171,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>22.957417329238151</v>
+        <v>22.95741732923815</v>
       </c>
       <c r="D16">
-        <v>45.927810779193763</v>
+        <v>45.92781077919376</v>
       </c>
       <c r="E16">
-        <v>92.740139471718436</v>
+        <v>92.74013947171844</v>
       </c>
       <c r="F16">
-        <v>186.49127209070201</v>
+        <v>186.491272090702</v>
       </c>
       <c r="G16">
-        <v>87.029159917713088</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>87.02915991771309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4733,19 +3197,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D17">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E17">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F17">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G17">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4756,19 +3220,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D18">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E18">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F18">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G18">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4776,10 +3240,10 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>24.142135623730951</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D19">
-        <v>49.698484809834987</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="E19">
         <v>100.8111831820431</v>
@@ -4788,10 +3252,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G19">
-        <v>94.422095885517081</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.42209588551708</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4802,19 +3266,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D20">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E20">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F20">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G20">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4822,22 +3286,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>23.155327751948541</v>
+        <v>23.15532775194854</v>
       </c>
       <c r="D21">
-        <v>46.489802689448211</v>
+        <v>46.48980268944821</v>
       </c>
       <c r="E21">
-        <v>94.356106399611136</v>
+        <v>94.35610639961114</v>
       </c>
       <c r="F21">
-        <v>194.81313863108201</v>
+        <v>194.813138631082</v>
       </c>
       <c r="G21">
-        <v>89.703593868022466</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.70359386802247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4845,22 +3309,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>22.612283912988389</v>
+        <v>22.61228391298839</v>
       </c>
       <c r="D22">
-        <v>46.759195742250157</v>
+        <v>46.75919574225016</v>
       </c>
       <c r="E22">
-        <v>95.665612683216509</v>
+        <v>95.66561268321651</v>
       </c>
       <c r="F22">
-        <v>193.05283202541881</v>
+        <v>193.0528320254188</v>
       </c>
       <c r="G22">
-        <v>89.522481090968483</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.52248109096848</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -4868,22 +3332,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D23">
-        <v>47.306087770882712</v>
+        <v>47.30608777088271</v>
       </c>
       <c r="E23">
-        <v>95.799708193232973</v>
+        <v>95.79970819323297</v>
       </c>
       <c r="F23">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="G23">
-        <v>89.601080778105612</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.60108077810561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4891,22 +3355,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D24">
-        <v>49.112698372208101</v>
+        <v>49.1126983722081</v>
       </c>
       <c r="E24">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F24">
-        <v>200.83556979968259</v>
+        <v>200.8355697996826</v>
       </c>
       <c r="G24">
-        <v>93.200270478569109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.20027047856911</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4914,22 +3378,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D25">
-        <v>49.112698372208101</v>
+        <v>49.1126983722081</v>
       </c>
       <c r="E25">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F25">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G25">
-        <v>92.786056916196003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.786056916196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4937,22 +3401,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D26">
-        <v>47.054151868677991</v>
+        <v>47.05415186867799</v>
       </c>
       <c r="E26">
-        <v>95.172840611977591</v>
+        <v>95.17284061197759</v>
       </c>
       <c r="F26">
-        <v>191.04858571919809</v>
+        <v>191.0485857191981</v>
       </c>
       <c r="G26">
-        <v>89.044742512399381</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.04474251239938</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4960,22 +3424,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D27">
-        <v>49.355339059327378</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E27">
-        <v>99.296464556281663</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F27">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G27">
-        <v>93.053823869162386</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93.05382386916239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4983,22 +3447,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>23.155327751948541</v>
+        <v>23.15532775194854</v>
       </c>
       <c r="D28">
-        <v>46.802215966473277</v>
+        <v>46.80221596647328</v>
       </c>
       <c r="E28">
-        <v>95.993720869188977</v>
+        <v>95.99372086918898</v>
       </c>
       <c r="F28">
-        <v>192.94076421973639</v>
+        <v>192.9407642197364</v>
       </c>
       <c r="G28">
-        <v>89.723007201836793</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.72300720183679</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5006,22 +3470,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D29">
-        <v>47.042603862487432</v>
+        <v>47.04260386248743</v>
       </c>
       <c r="E29">
-        <v>95.368894328835481</v>
+        <v>95.36889432883548</v>
       </c>
       <c r="F29">
         <v>192.0991124527755</v>
       </c>
       <c r="G29">
-        <v>89.353500623460562</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.35350062346056</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5032,19 +3496,19 @@
         <v>22.93494128361905</v>
       </c>
       <c r="D30">
-        <v>47.127201304036298</v>
+        <v>47.1272013040363</v>
       </c>
       <c r="E30">
-        <v>95.368894328835481</v>
+        <v>95.36889432883548</v>
       </c>
       <c r="F30">
         <v>192.0991124527755</v>
       </c>
       <c r="G30">
-        <v>89.382537342316581</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.38253734231658</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5055,19 +3519,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D31">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E31">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F31">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G31">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5075,22 +3539,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>22.957417329238151</v>
+        <v>22.95741732923815</v>
       </c>
       <c r="D32">
-        <v>45.927810779193763</v>
+        <v>45.92781077919376</v>
       </c>
       <c r="E32">
-        <v>92.740139471718436</v>
+        <v>92.74013947171844</v>
       </c>
       <c r="F32">
-        <v>186.49127209070201</v>
+        <v>186.491272090702</v>
       </c>
       <c r="G32">
-        <v>87.029159917713088</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>87.02915991771309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5101,19 +3565,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D33">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E33">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F33">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G33">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5124,19 +3588,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D34">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E34">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F34">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G34">
-        <v>92.225396744416173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.22539674441617</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5147,19 +3611,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D35">
-        <v>47.142608793074928</v>
+        <v>47.14260879307493</v>
       </c>
       <c r="E35">
-        <v>95.643929748144473</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F35">
         <v>192.6542644043582</v>
       </c>
       <c r="G35">
-        <v>89.631974652513236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.63197465251324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5167,22 +3631,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>23.785844453984339</v>
+        <v>23.78584445398434</v>
       </c>
       <c r="D36">
-        <v>48.107127263266428</v>
+        <v>48.10712726326643</v>
       </c>
       <c r="E36">
-        <v>97.590755547247568</v>
+        <v>97.59075554724757</v>
       </c>
       <c r="F36">
-        <v>196.56376190917649</v>
+        <v>196.5637619091765</v>
       </c>
       <c r="G36">
-        <v>91.511872293418705</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>91.5118722934187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5193,19 +3657,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D37">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E37">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F37">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G37">
-        <v>94.775649276110357</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.77564927611036</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5213,22 +3677,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>22.977182167075231</v>
+        <v>22.97718216707523</v>
       </c>
       <c r="D38">
-        <v>46.489802689448211</v>
+        <v>46.48980268944821</v>
       </c>
       <c r="E38">
-        <v>94.356106399611136</v>
+        <v>94.35610639961114</v>
       </c>
       <c r="F38">
-        <v>190.09446361390371</v>
+        <v>190.0944636139037</v>
       </c>
       <c r="G38">
-        <v>88.479388717509565</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88.47938871750956</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -5236,22 +3700,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D39">
-        <v>47.306087770882712</v>
+        <v>47.30608777088271</v>
       </c>
       <c r="E39">
-        <v>95.799708193232973</v>
+        <v>95.79970819323297</v>
       </c>
       <c r="F39">
         <v>192.528335978423</v>
       </c>
       <c r="G39">
-        <v>89.634380948070628</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.63438094807063</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -5259,22 +3723,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D40">
-        <v>47.306087770882712</v>
+        <v>47.30608777088271</v>
       </c>
       <c r="E40">
-        <v>95.799708193232973</v>
+        <v>95.79970819323297</v>
       </c>
       <c r="F40">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="G40">
-        <v>89.601080778105612</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.60108077810561</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -5282,22 +3746,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>24.384776310850238</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D41">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E41">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F41">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G41">
         <v>92.63961030678928</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -5305,22 +3769,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D42">
-        <v>47.054151868677991</v>
+        <v>47.05415186867799</v>
       </c>
       <c r="E42">
-        <v>95.172840611977591</v>
+        <v>95.17284061197759</v>
       </c>
       <c r="F42">
-        <v>191.04858571919809</v>
+        <v>191.0485857191981</v>
       </c>
       <c r="G42">
-        <v>89.044742512399381</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.04474251239938</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -5331,19 +3795,19 @@
         <v>22.93494128361905</v>
       </c>
       <c r="D43">
-        <v>47.042603862487432</v>
+        <v>47.04260386248743</v>
       </c>
       <c r="E43">
-        <v>95.368894328835481</v>
+        <v>95.36889432883548</v>
       </c>
       <c r="F43">
-        <v>192.03828591093071</v>
+        <v>192.0382859109307</v>
       </c>
       <c r="G43">
-        <v>89.346181346468157</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.34618134646816</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5351,22 +3815,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>23.200058016357438</v>
+        <v>23.20005801635744</v>
       </c>
       <c r="D44">
-        <v>46.368424437027599</v>
+        <v>46.3684244370276</v>
       </c>
       <c r="E44">
-        <v>93.779855779356666</v>
+        <v>93.77985577935667</v>
       </c>
       <c r="F44">
-        <v>188.67305645252739</v>
+        <v>188.6730564525274</v>
       </c>
       <c r="G44">
-        <v>88.005348671317279</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88.00534867131728</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5377,19 +3841,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D45">
-        <v>48.526911934581179</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E45">
-        <v>98.468037431535464</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F45">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="G45">
-        <v>94.775649276110357</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>94.77564927611036</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -5400,19 +3864,19 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D46">
-        <v>46.386801086460778</v>
+        <v>46.38680108646078</v>
       </c>
       <c r="E46">
-        <v>95.643929748144473</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F46">
         <v>192.6542644043582</v>
       </c>
       <c r="G46">
-        <v>89.443022725859691</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.44302272585969</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5420,22 +3884,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>23.155327751948541</v>
+        <v>23.15532775194854</v>
       </c>
       <c r="D47">
         <v>47.6694714437428</v>
       </c>
       <c r="E47">
-        <v>96.715443908200299</v>
+        <v>96.7154439082003</v>
       </c>
       <c r="F47">
         <v>201.3376443991751</v>
       </c>
       <c r="G47">
-        <v>92.219471875766686</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>92.21947187576669</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -5443,22 +3907,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>22.903391849743819</v>
+        <v>22.90339184974382</v>
       </c>
       <c r="D48">
-        <v>47.306087770882712</v>
+        <v>47.30608777088271</v>
       </c>
       <c r="E48">
-        <v>95.799708193232973</v>
+        <v>95.79970819323297</v>
       </c>
       <c r="F48">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="G48">
-        <v>89.601080778105612</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89.60108077810561</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -5469,16 +3933,16 @@
         <v>23.08709566447531</v>
       </c>
       <c r="D49">
-        <v>47.142608793074928</v>
+        <v>47.14260879307493</v>
       </c>
       <c r="E49">
-        <v>95.643929748144473</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F49">
-        <v>199.17877017245129</v>
+        <v>199.1787701724513</v>
       </c>
       <c r="G49">
-        <v>91.263101094536509</v>
+        <v>91.26310109453651</v>
       </c>
     </row>
   </sheetData>
@@ -5487,11 +3951,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +3978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5537,7 +4001,7 @@
         <v>343.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5560,7 +4024,7 @@
         <v>356.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5583,7 +4047,7 @@
         <v>238.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5606,7 +4070,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5629,7 +4093,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5652,7 +4116,7 @@
         <v>343.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5675,7 +4139,7 @@
         <v>278.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5698,7 +4162,7 @@
         <v>281.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5721,7 +4185,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5744,7 +4208,7 @@
         <v>356.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5767,7 +4231,7 @@
         <v>278.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5790,7 +4254,7 @@
         <v>238.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5813,7 +4277,7 @@
         <v>227.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5836,7 +4300,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5859,7 +4323,7 @@
         <v>230.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5882,7 +4346,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5905,7 +4369,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5928,7 +4392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5951,7 +4415,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5974,7 +4438,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5997,7 +4461,7 @@
         <v>278.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6020,7 +4484,7 @@
         <v>281.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6043,7 +4507,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6066,7 +4530,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -6089,7 +4553,7 @@
         <v>206.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -6112,7 +4576,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6135,7 +4599,7 @@
         <v>278.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -6158,7 +4622,7 @@
         <v>227.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6181,7 +4645,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6204,7 +4668,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -6227,7 +4691,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -6250,7 +4714,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6273,7 +4737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6296,7 +4760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6319,7 +4783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6342,7 +4806,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -6365,7 +4829,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -6388,7 +4852,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -6411,7 +4875,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -6434,7 +4898,7 @@
         <v>253.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -6457,7 +4921,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -6480,7 +4944,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6503,7 +4967,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6526,7 +4990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6549,7 +5013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6572,7 +5036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -6595,7 +5059,7 @@
         <v>253.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -6624,11 +5088,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6651,7 +5115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6674,7 +5138,7 @@
         <v>1587.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6697,7 +5161,7 @@
         <v>1186.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6720,7 +5184,7 @@
         <v>200.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6743,7 +5207,7 @@
         <v>953.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6766,7 +5230,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6789,7 +5253,7 @@
         <v>1587.25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6812,7 +5276,7 @@
         <v>1630.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6835,7 +5299,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6858,7 +5322,7 @@
         <v>971.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6881,7 +5345,7 @@
         <v>1186.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6904,7 +5368,7 @@
         <v>1138.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6927,7 +5391,7 @@
         <v>200.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6950,7 +5414,7 @@
         <v>176.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6973,7 +5437,7 @@
         <v>171.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6996,7 +5460,7 @@
         <v>953.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7019,7 +5483,7 @@
         <v>962.75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7042,7 +5506,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7065,7 +5529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7088,7 +5552,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7111,7 +5575,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7134,7 +5598,7 @@
         <v>1630.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7157,7 +5621,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7180,7 +5644,7 @@
         <v>207.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7203,7 +5667,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7226,7 +5690,7 @@
         <v>971.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7249,7 +5713,7 @@
         <v>973.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7272,7 +5736,7 @@
         <v>1138.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7295,7 +5759,7 @@
         <v>176.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7318,7 +5782,7 @@
         <v>171.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7341,7 +5805,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7364,7 +5828,7 @@
         <v>962.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7387,7 +5851,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7410,7 +5874,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7433,7 +5897,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7456,7 +5920,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7479,7 +5943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7502,7 +5966,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -7525,7 +5989,7 @@
         <v>207.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -7548,7 +6012,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -7571,7 +6035,7 @@
         <v>215.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -7594,7 +6058,7 @@
         <v>973.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -7617,7 +6081,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7640,7 +6104,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7663,7 +6127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7686,7 +6150,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7709,7 +6173,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -7732,7 +6196,7 @@
         <v>215.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -7761,11 +6225,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +6252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7811,7 +6275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7834,7 +6298,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7857,7 +6321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7880,7 +6344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -7903,7 +6367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7926,7 +6390,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -7949,7 +6413,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7972,7 +6436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7995,7 +6459,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8018,7 +6482,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8041,7 +6505,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8064,7 +6528,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8087,7 +6551,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8110,7 +6574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8133,7 +6597,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8156,7 +6620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8179,7 +6643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8202,7 +6666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8225,7 +6689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8248,7 +6712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8271,7 +6735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8294,7 +6758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8317,7 +6781,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8340,7 +6804,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8363,7 +6827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8386,7 +6850,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8409,7 +6873,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8432,7 +6896,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8455,7 +6919,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8478,7 +6942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8501,7 +6965,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8524,7 +6988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8547,7 +7011,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8570,7 +7034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8593,7 +7057,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8616,7 +7080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8639,7 +7103,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -8662,7 +7126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -8685,7 +7149,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -8708,7 +7172,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -8731,7 +7195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -8754,7 +7218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -8777,7 +7241,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -8800,7 +7264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -8823,7 +7287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -8846,7 +7310,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -8869,7 +7333,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0005350999999999999</v>
+        <v>0.000546</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0036208</v>
+        <v>0.003684000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0287961</v>
+        <v>0.030357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2103159</v>
+        <v>0.2180022</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06081697500000001</v>
+        <v>0.06314729999999999</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002469</v>
+        <v>0.0002674999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0011112</v>
+        <v>0.0011545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0047854</v>
+        <v>0.0048022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0204948</v>
+        <v>0.0206734</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006659575</v>
+        <v>0.006724399999999999</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004463</v>
+        <v>0.0003776</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001128</v>
+        <v>0.0011538</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0045088</v>
+        <v>0.0042386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0360559</v>
+        <v>0.0218588</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01053475</v>
+        <v>0.0069072</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0004545</v>
+        <v>0.0004648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0025378</v>
+        <v>0.0027194</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0171306</v>
+        <v>0.01741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1181711</v>
+        <v>0.1240879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03457350000000001</v>
+        <v>0.036170525</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0004273</v>
+        <v>0.0004617000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0013179</v>
+        <v>0.0013765</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0048336</v>
+        <v>0.004941599999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0191498</v>
+        <v>0.0192263</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00643215</v>
+        <v>0.006501525</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006041</v>
+        <v>0.0006234999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003675899999999999</v>
+        <v>0.0038125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0283577</v>
+        <v>0.0281771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2101729</v>
+        <v>0.2160788</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06070265000000001</v>
+        <v>0.06217297500000001</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0006243000000000001</v>
+        <v>0.0006391</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003557899999999999</v>
+        <v>0.003597599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0264631</v>
+        <v>0.0267297</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1973065</v>
+        <v>0.2037332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05698795</v>
+        <v>0.0586749</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003744</v>
+        <v>0.0003872</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0010669</v>
+        <v>0.0010871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003531799999999999</v>
+        <v>0.003215</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0118646</v>
+        <v>0.0103866</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004209424999999999</v>
+        <v>0.003768975</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003006</v>
+        <v>0.0003065</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0014428</v>
+        <v>0.0014377</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005953999999999999</v>
+        <v>0.006045500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0252114</v>
+        <v>0.0254324</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0082272</v>
+        <v>0.008305525000000001</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003036</v>
+        <v>0.000281</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001173</v>
+        <v>0.0011939</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005061599999999999</v>
+        <v>0.0050425</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0212078</v>
+        <v>0.0211033</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0069365</v>
+        <v>0.006905175</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003304</v>
+        <v>0.0003613</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0013881</v>
+        <v>0.0013669</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0051584</v>
+        <v>0.005241699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0219206</v>
+        <v>0.021877</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007199375</v>
+        <v>0.007211725</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004527</v>
+        <v>0.0004005</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0012207</v>
+        <v>0.0012621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004614</v>
+        <v>0.0044928</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0361769</v>
+        <v>0.0217566</v>
       </c>
       <c r="G13" t="n">
-        <v>0.010616075</v>
+        <v>0.006978</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004335</v>
+        <v>0.0004347999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0013127</v>
+        <v>0.0013109</v>
       </c>
       <c r="E14" t="n">
-        <v>0.004644000000000001</v>
+        <v>0.0045134</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0314639</v>
+        <v>0.0226044</v>
       </c>
       <c r="G14" t="n">
-        <v>0.009463525</v>
+        <v>0.007215874999999999</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0004091999999999999</v>
+        <v>0.0004049</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0013175</v>
+        <v>0.0014147</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0055352</v>
+        <v>0.004932399999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0295231</v>
+        <v>0.0256787</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00919625</v>
+        <v>0.008107675</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0004631</v>
+        <v>0.0004849999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0026581</v>
+        <v>0.0027005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0177641</v>
+        <v>0.0179767</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1189599</v>
+        <v>0.1228213</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0349613</v>
+        <v>0.035995875</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0004906</v>
+        <v>0.0005078</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0027333</v>
+        <v>0.0027631</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0168155</v>
+        <v>0.0173218</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1063075</v>
+        <v>0.1120969</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031586725</v>
+        <v>0.0331724</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003952</v>
+        <v>0.0003351</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0008968</v>
+        <v>0.0008937999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0029174</v>
+        <v>0.0029088</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0102107</v>
+        <v>0.0104362</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003605025</v>
+        <v>0.003643475</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003128000000000001</v>
+        <v>0.0003003</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0006609000000000001</v>
+        <v>0.00066</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0024157</v>
+        <v>0.0017488</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008409099999999999</v>
+        <v>0.0058041</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002949625</v>
+        <v>0.0021283</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003819</v>
+        <v>0.0003584</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011779</v>
+        <v>0.0011674</v>
       </c>
       <c r="E20" t="n">
-        <v>0.003790299999999999</v>
+        <v>0.0037865</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0140483</v>
+        <v>0.0140926</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0048496</v>
+        <v>0.004851225000000001</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004676</v>
+        <v>0.0004616000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0013761</v>
+        <v>0.0014341</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004935699999999999</v>
+        <v>0.0049436</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0194548</v>
+        <v>0.0199467</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00655855</v>
+        <v>0.0066965</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0006598000000000001</v>
+        <v>0.0006406000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0037132</v>
+        <v>0.0036825</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0280697</v>
+        <v>0.0269687</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1966613</v>
+        <v>0.20486</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05727599999999999</v>
+        <v>0.05903795</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003840000000000001</v>
+        <v>0.0004203</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0011129</v>
+        <v>0.0011084</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0034523</v>
+        <v>0.0033663</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0127766</v>
+        <v>0.0113008</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004431450000000001</v>
+        <v>0.00404895</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00042</v>
+        <v>0.0004102</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0012131</v>
+        <v>0.0012922</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0034753</v>
+        <v>0.003509</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0126612</v>
+        <v>0.0112542</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0044424</v>
+        <v>0.0041164</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004073999999999999</v>
+        <v>0.0004322</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0012761</v>
+        <v>0.0025646</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003966099999999999</v>
+        <v>0.0038514</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0148029</v>
+        <v>0.0139693</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005113125</v>
+        <v>0.005204375000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003367</v>
+        <v>0.0003301</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0014676</v>
+        <v>0.0015485</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006137800000000001</v>
+        <v>0.006173700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0260323</v>
+        <v>0.0259852</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0084936</v>
+        <v>0.008509375000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003566</v>
+        <v>0.0003597</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0015458</v>
+        <v>0.0015893</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006133500000000001</v>
+        <v>0.0062231</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0253372</v>
+        <v>0.0254515</v>
       </c>
       <c r="G27" t="n">
-        <v>0.008343275000000001</v>
+        <v>0.008405899999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003904</v>
+        <v>0.0003724</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0014321</v>
+        <v>0.0014709</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0052959</v>
+        <v>0.0053147</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0223487</v>
+        <v>0.0228021</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007366775</v>
+        <v>0.007490025000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0004909999999999999</v>
+        <v>0.0004310000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0013579</v>
+        <v>0.0013605</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0049507</v>
+        <v>0.0046745</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0313686</v>
+        <v>0.0237458</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00954205</v>
+        <v>0.007552950000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0004226</v>
+        <v>0.0004431</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0013936</v>
+        <v>0.0014071</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0057439</v>
+        <v>0.004991299999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0301943</v>
+        <v>0.0260128</v>
       </c>
       <c r="G30" t="n">
-        <v>0.009438599999999998</v>
+        <v>0.008213575000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0004251</v>
+        <v>0.0004374</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0012805</v>
+        <v>0.0013522</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0054603</v>
+        <v>0.004967500000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0281015</v>
+        <v>0.0266098</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008816850000000001</v>
+        <v>0.008341724999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0005193</v>
+        <v>0.0005307000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0027461</v>
+        <v>0.0029335</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0172731</v>
+        <v>0.0177066</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1065046</v>
+        <v>0.1123257</v>
       </c>
       <c r="G32" t="n">
-        <v>0.031760775</v>
+        <v>0.033374125</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003343</v>
+        <v>0.0003758</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0009469000000000002</v>
+        <v>0.001003</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0032991</v>
+        <v>0.0027288</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0116786</v>
+        <v>0.009828100000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.004064725</v>
+        <v>0.003483925</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0003527</v>
+        <v>0.0003841</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001231</v>
+        <v>0.0012308</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0028008</v>
+        <v>0.0028052</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0107444</v>
+        <v>0.0105294</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003782225</v>
+        <v>0.003737375</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0003635</v>
+        <v>0.0003871</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0009566000000000002</v>
+        <v>0.0009500000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0029133</v>
+        <v>0.002974800000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0101772</v>
+        <v>0.0103504</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00360265</v>
+        <v>0.003665575</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003328</v>
+        <v>0.0003252</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0006847999999999999</v>
+        <v>0.0006824</v>
       </c>
       <c r="E36" t="n">
-        <v>0.002367</v>
+        <v>0.001889</v>
       </c>
       <c r="F36" t="n">
-        <v>0.008440699999999999</v>
+        <v>0.0060915</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002956325</v>
+        <v>0.002247025</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002998</v>
+        <v>0.0002808</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000764</v>
+        <v>0.0007123</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0018546</v>
+        <v>0.0020868</v>
       </c>
       <c r="F37" t="n">
-        <v>0.008230299999999999</v>
+        <v>0.007346199999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002787175</v>
+        <v>0.002606525</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.000379</v>
+        <v>0.0004096</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0011754</v>
+        <v>0.0012078</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003740100000000001</v>
+        <v>0.003845</v>
       </c>
       <c r="F38" t="n">
-        <v>0.014151</v>
+        <v>0.0141298</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004861375</v>
+        <v>0.00489805</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004007999999999999</v>
+        <v>0.0004215</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0012652</v>
+        <v>0.0013187</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0035751</v>
+        <v>0.0036742</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0131896</v>
+        <v>0.0119389</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004607675</v>
+        <v>0.004338325</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0004527</v>
+        <v>0.00044</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0012832</v>
+        <v>0.0013157</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0040211</v>
+        <v>0.00408</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0154514</v>
+        <v>0.0145385</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0053021</v>
+        <v>0.00509355</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0004538</v>
+        <v>0.0004193000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0012875</v>
+        <v>0.0012776</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0040857</v>
+        <v>0.0040456</v>
       </c>
       <c r="F41" t="n">
-        <v>0.014699</v>
+        <v>0.0149416</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005131500000000001</v>
+        <v>0.005171025000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004011</v>
+        <v>0.0003933000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0016442</v>
+        <v>0.0016665</v>
       </c>
       <c r="E42" t="n">
-        <v>0.006397799999999999</v>
+        <v>0.0064125</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0272413</v>
+        <v>0.026673</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008921100000000001</v>
+        <v>0.008786325000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0004963</v>
+        <v>0.0004547</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0014309</v>
+        <v>0.0013888</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0054959</v>
+        <v>0.0051654</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02924429999999999</v>
+        <v>0.0273314</v>
       </c>
       <c r="G43" t="n">
-        <v>0.009166849999999999</v>
+        <v>0.008585074999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003615000000000001</v>
+        <v>0.0003902</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0009916999999999999</v>
+        <v>0.0009990999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0034095</v>
+        <v>0.002857600000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0119526</v>
+        <v>0.0095739</v>
       </c>
       <c r="G44" t="n">
-        <v>0.004178825000000001</v>
+        <v>0.0034552</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004066</v>
+        <v>0.0004337000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0010471</v>
+        <v>0.0009966999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0029922</v>
+        <v>0.0029725</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0110323</v>
+        <v>0.0107656</v>
       </c>
       <c r="G45" t="n">
-        <v>0.003869549999999999</v>
+        <v>0.003792124999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.000394</v>
+        <v>0.0003812000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0012968</v>
+        <v>0.0012756</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0028335</v>
+        <v>0.0028881</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0106086</v>
+        <v>0.010706</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003783225</v>
+        <v>0.003812724999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003046</v>
+        <v>0.0003426999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0007213</v>
+        <v>0.0007721000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0020969</v>
+        <v>0.0022251</v>
       </c>
       <c r="F47" t="n">
-        <v>0.008155699999999998</v>
+        <v>0.007606700000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>0.002819625</v>
+        <v>0.00273665</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0004620999999999999</v>
+        <v>0.0004853</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0013221</v>
+        <v>0.0013604</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0042597</v>
+        <v>0.004343700000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0154079</v>
+        <v>0.0157142</v>
       </c>
       <c r="G48" t="n">
-        <v>0.00536295</v>
+        <v>0.005475900000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004423</v>
+        <v>0.0004546</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0010345</v>
+        <v>0.0010659</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0030974</v>
+        <v>0.0030921</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0111757</v>
+        <v>0.0112333</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003937475</v>
+        <v>0.003961475</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1813,13 @@
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -2066,10 +2066,10 @@
         <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G14" t="n">
-        <v>75.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
         <v>80</v>
@@ -2319,7 +2319,7 @@
         <v>160</v>
       </c>
       <c r="G24" t="n">
-        <v>75.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
@@ -2335,13 +2335,13 @@
         <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
         <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G25" t="n">
         <v>75.25</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
         <v>7</v>
@@ -2619,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="37">
@@ -2641,10 +2641,10 @@
         <v>22</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
@@ -2841,10 +2841,10 @@
         <v>23</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="46">
@@ -2891,10 +2891,10 @@
         <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2941,10 +2941,10 @@
         <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
     </row>
   </sheetData>
@@ -3064,13 +3064,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E4" t="n">
-        <v>99.05382386916236</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F4" t="n">
-        <v>201.7645019878171</v>
+        <v>200.0071426749364</v>
       </c>
       <c r="G4" t="n">
-        <v>93.22539674441617</v>
+        <v>92.63961030678928</v>
       </c>
     </row>
     <row r="5">
@@ -3186,7 +3186,7 @@
         <v>24.38477631085024</v>
       </c>
       <c r="D9" t="n">
-        <v>48.52691193458118</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E9" t="n">
         <v>98.46803743153546</v>
@@ -3195,7 +3195,7 @@
         <v>200.8355697996826</v>
       </c>
       <c r="G9" t="n">
-        <v>93.05382386916237</v>
+        <v>93.26093065034893</v>
       </c>
     </row>
     <row r="10">
@@ -3308,19 +3308,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.55634918610405</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D14" t="n">
-        <v>48.52691193458118</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E14" t="n">
         <v>98.46803743153546</v>
       </c>
       <c r="F14" t="n">
-        <v>201.1787155501902</v>
+        <v>200.0071426749364</v>
       </c>
       <c r="G14" t="n">
-        <v>92.93250352560273</v>
+        <v>93.05382386916239</v>
       </c>
     </row>
     <row r="15">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.14213562373095</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D19" t="n">
         <v>49.69848480983499</v>
@@ -3445,7 +3445,7 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G19" t="n">
-        <v>94.42209588551708</v>
+        <v>94.27564927611036</v>
       </c>
     </row>
     <row r="20">
@@ -3542,10 +3542,10 @@
         <v>95.05671258281731</v>
       </c>
       <c r="F23" t="n">
-        <v>190.8666229152406</v>
+        <v>190.5376445941226</v>
       </c>
       <c r="G23" t="n">
-        <v>88.86499004755807</v>
+        <v>88.78274546727857</v>
       </c>
     </row>
     <row r="24">
@@ -3561,7 +3561,7 @@
         <v>24.38477631085024</v>
       </c>
       <c r="D24" t="n">
-        <v>49.1126983722081</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E24" t="n">
         <v>98.46803743153546</v>
@@ -3570,7 +3570,7 @@
         <v>200.8355697996826</v>
       </c>
       <c r="G24" t="n">
-        <v>93.20027047856911</v>
+        <v>93.26093065034893</v>
       </c>
     </row>
     <row r="25">
@@ -3586,16 +3586,16 @@
         <v>24.38477631085024</v>
       </c>
       <c r="D25" t="n">
-        <v>49.1126983722081</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E25" t="n">
         <v>98.46803743153546</v>
       </c>
       <c r="F25" t="n">
-        <v>199.1787155501902</v>
+        <v>199.7645019878171</v>
       </c>
       <c r="G25" t="n">
-        <v>92.786056916196</v>
+        <v>92.99316369738256</v>
       </c>
     </row>
     <row r="26">
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.62089099732862</v>
+        <v>23.76087902741253</v>
       </c>
       <c r="D29" t="n">
-        <v>46.60059793450297</v>
+        <v>46.54043818792906</v>
       </c>
       <c r="E29" t="n">
         <v>94.57769688972063</v>
@@ -3695,7 +3695,7 @@
         <v>190.5376445941226</v>
       </c>
       <c r="G29" t="n">
-        <v>88.58420760391871</v>
+        <v>88.85416467479621</v>
       </c>
     </row>
     <row r="30">
@@ -3711,16 +3711,16 @@
         <v>22.62089099732862</v>
       </c>
       <c r="D30" t="n">
-        <v>46.65599555703034</v>
+        <v>46.60059793450297</v>
       </c>
       <c r="E30" t="n">
-        <v>94.57769688972063</v>
+        <v>94.72620467643378</v>
       </c>
       <c r="F30" t="n">
         <v>190.5376445941226</v>
       </c>
       <c r="G30" t="n">
-        <v>88.59805700955056</v>
+        <v>88.621334550597</v>
       </c>
     </row>
     <row r="31">
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22.90387700126232</v>
+        <v>22.93245190266634</v>
       </c>
       <c r="D36" t="n">
         <v>46.87266338875516</v>
@@ -3870,7 +3870,7 @@
         <v>190.8923385147889</v>
       </c>
       <c r="G36" t="n">
-        <v>88.88470486692829</v>
+        <v>88.8918485922793</v>
       </c>
     </row>
     <row r="37">
@@ -3892,10 +3892,10 @@
         <v>98.46803743153546</v>
       </c>
       <c r="F37" t="n">
-        <v>208.5512985522207</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G37" t="n">
-        <v>94.77564927611036</v>
+        <v>92.22539674441617</v>
       </c>
     </row>
     <row r="38">
@@ -3936,16 +3936,16 @@
         <v>22.62089099732862</v>
       </c>
       <c r="D39" t="n">
-        <v>46.91573369484568</v>
+        <v>46.55110554604754</v>
       </c>
       <c r="E39" t="n">
         <v>95.05671258281731</v>
       </c>
       <c r="F39" t="n">
-        <v>191.0743075052835</v>
+        <v>190.5376445941226</v>
       </c>
       <c r="G39" t="n">
-        <v>88.91691119506876</v>
+        <v>88.69158843007904</v>
       </c>
     </row>
     <row r="40">
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>22.02629449613479</v>
+        <v>22.62089099732862</v>
       </c>
       <c r="D44" t="n">
         <v>45.97807036099057</v>
@@ -4070,7 +4070,7 @@
         <v>187.2190279793878</v>
       </c>
       <c r="G44" t="n">
-        <v>87.06506325136354</v>
+        <v>87.213712376662</v>
       </c>
     </row>
     <row r="45">
@@ -4092,10 +4092,10 @@
         <v>98.46803743153546</v>
       </c>
       <c r="F45" t="n">
-        <v>208.5512985522207</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G45" t="n">
-        <v>94.77564927611036</v>
+        <v>92.22539674441617</v>
       </c>
     </row>
     <row r="46">
@@ -4142,10 +4142,10 @@
         <v>95.97244829778465</v>
       </c>
       <c r="F47" t="n">
-        <v>199.8836159260355</v>
+        <v>193.3591101579424</v>
       </c>
       <c r="G47" t="n">
-        <v>91.51690837354806</v>
+        <v>89.88578193152478</v>
       </c>
     </row>
     <row r="48">
@@ -4192,10 +4192,10 @@
         <v>94.9009341377288</v>
       </c>
       <c r="F49" t="n">
-        <v>197.7247416993117</v>
+        <v>191.2002359312186</v>
       </c>
       <c r="G49" t="n">
-        <v>90.49970538785178</v>
+        <v>88.86857894582849</v>
       </c>
     </row>
   </sheetData>
@@ -4312,16 +4312,16 @@
         <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F4" t="n">
-        <v>611</v>
+        <v>539</v>
       </c>
       <c r="G4" t="n">
-        <v>238.75</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="5">
@@ -4437,16 +4437,16 @@
         <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E9" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F9" t="n">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="G9" t="n">
-        <v>281.75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -4537,16 +4537,16 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E13" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F13" t="n">
-        <v>611</v>
+        <v>539</v>
       </c>
       <c r="G13" t="n">
-        <v>238.75</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F14" t="n">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="G14" t="n">
-        <v>227.25</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15">
@@ -4587,16 +4587,16 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F15" t="n">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="G15" t="n">
-        <v>214</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="16">
@@ -4684,19 +4684,19 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
         <v>13</v>
       </c>
-      <c r="D19" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15</v>
-      </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="20">
@@ -4787,16 +4787,16 @@
         <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E23" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="F23" t="n">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="G23" t="n">
-        <v>281.75</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24">
@@ -4812,16 +4812,16 @@
         <v>39</v>
       </c>
       <c r="D24" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="F24" t="n">
-        <v>641</v>
+        <v>705</v>
       </c>
       <c r="G24" t="n">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25">
@@ -4837,16 +4837,16 @@
         <v>39</v>
       </c>
       <c r="D25" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E25" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F25" t="n">
-        <v>587</v>
+        <v>551</v>
       </c>
       <c r="G25" t="n">
-        <v>245</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D29" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F29" t="n">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="G29" t="n">
-        <v>227.25</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30">
@@ -4962,16 +4962,16 @@
         <v>37</v>
       </c>
       <c r="D30" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F30" t="n">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="G30" t="n">
-        <v>214</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="31">
@@ -4987,16 +4987,16 @@
         <v>37</v>
       </c>
       <c r="D31" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F31" t="n">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="G31" t="n">
-        <v>217.5</v>
+        <v>225.75</v>
       </c>
     </row>
     <row r="32">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
         <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
-        <v>19.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="34">
@@ -5109,19 +5109,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>14</v>
+      </c>
+      <c r="E36" t="n">
         <v>13</v>
       </c>
-      <c r="D36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E36" t="n">
-        <v>15</v>
-      </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="37">
@@ -5137,16 +5137,16 @@
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="38">
@@ -5187,16 +5187,16 @@
         <v>39</v>
       </c>
       <c r="D39" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="F39" t="n">
-        <v>641</v>
+        <v>705</v>
       </c>
       <c r="G39" t="n">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40">
@@ -5212,16 +5212,16 @@
         <v>39</v>
       </c>
       <c r="D40" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E40" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F40" t="n">
-        <v>587</v>
+        <v>551</v>
       </c>
       <c r="G40" t="n">
-        <v>245</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E41" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F41" t="n">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="G41" t="n">
-        <v>253.25</v>
+        <v>256.75</v>
       </c>
     </row>
     <row r="42">
@@ -5287,16 +5287,16 @@
         <v>37</v>
       </c>
       <c r="D43" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E43" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F43" t="n">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="G43" t="n">
-        <v>217.5</v>
+        <v>225.75</v>
       </c>
     </row>
     <row r="44">
@@ -5309,19 +5309,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
         <v>20</v>
       </c>
       <c r="E44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>19.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="45">
@@ -5387,16 +5387,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F47" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E48" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F48" t="n">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="G48" t="n">
-        <v>253.25</v>
+        <v>256.75</v>
       </c>
     </row>
     <row r="49">
@@ -5563,16 +5563,16 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F4" t="n">
-        <v>598</v>
+        <v>361</v>
       </c>
       <c r="G4" t="n">
-        <v>200.75</v>
+        <v>136.75</v>
       </c>
     </row>
     <row r="5">
@@ -5691,13 +5691,13 @@
         <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F9" t="n">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="G9" t="n">
-        <v>203.75</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -5788,16 +5788,16 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F13" t="n">
-        <v>598</v>
+        <v>361</v>
       </c>
       <c r="G13" t="n">
-        <v>200.75</v>
+        <v>136.75</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
-        <v>503</v>
+        <v>374</v>
       </c>
       <c r="G14" t="n">
-        <v>176.5</v>
+        <v>141.75</v>
       </c>
     </row>
     <row r="15">
@@ -5838,16 +5838,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>476</v>
+        <v>401</v>
       </c>
       <c r="G15" t="n">
-        <v>171.75</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="16">
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -6041,13 +6041,13 @@
         <v>68</v>
       </c>
       <c r="E23" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F23" t="n">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="G23" t="n">
-        <v>203.75</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24">
@@ -6063,16 +6063,16 @@
         <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E24" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F24" t="n">
-        <v>547</v>
+        <v>492</v>
       </c>
       <c r="G24" t="n">
-        <v>207.25</v>
+        <v>194.25</v>
       </c>
     </row>
     <row r="25">
@@ -6088,16 +6088,16 @@
         <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F25" t="n">
-        <v>573</v>
+        <v>512</v>
       </c>
       <c r="G25" t="n">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E29" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F29" t="n">
-        <v>503</v>
+        <v>374</v>
       </c>
       <c r="G29" t="n">
-        <v>176.5</v>
+        <v>141.75</v>
       </c>
     </row>
     <row r="30">
@@ -6213,16 +6213,16 @@
         <v>21</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E30" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F30" t="n">
-        <v>476</v>
+        <v>401</v>
       </c>
       <c r="G30" t="n">
-        <v>171.75</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="31">
@@ -6241,13 +6241,13 @@
         <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F31" t="n">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="G31" t="n">
-        <v>166</v>
+        <v>151.75</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D33" t="n">
         <v>37</v>
       </c>
       <c r="E33" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>35.5</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="34">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F36" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -6388,16 +6388,16 @@
         <v>17</v>
       </c>
       <c r="D37" t="n">
+        <v>26</v>
+      </c>
+      <c r="E37" t="n">
         <v>25</v>
       </c>
-      <c r="E37" t="n">
-        <v>24</v>
-      </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G37" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="38">
@@ -6438,16 +6438,16 @@
         <v>27</v>
       </c>
       <c r="D39" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E39" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F39" t="n">
-        <v>547</v>
+        <v>492</v>
       </c>
       <c r="G39" t="n">
-        <v>207.25</v>
+        <v>194.25</v>
       </c>
     </row>
     <row r="40">
@@ -6463,16 +6463,16 @@
         <v>29</v>
       </c>
       <c r="D40" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E40" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F40" t="n">
-        <v>573</v>
+        <v>512</v>
       </c>
       <c r="G40" t="n">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
         <v>70</v>
       </c>
       <c r="E41" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F41" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G41" t="n">
-        <v>215.5</v>
+        <v>216.25</v>
       </c>
     </row>
     <row r="42">
@@ -6541,13 +6541,13 @@
         <v>48</v>
       </c>
       <c r="E43" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F43" t="n">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="G43" t="n">
-        <v>166</v>
+        <v>151.75</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D44" t="n">
         <v>37</v>
       </c>
       <c r="E44" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F44" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G44" t="n">
-        <v>35.5</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="45">
@@ -6638,16 +6638,16 @@
         <v>17</v>
       </c>
       <c r="D47" t="n">
+        <v>26</v>
+      </c>
+      <c r="E47" t="n">
         <v>25</v>
       </c>
-      <c r="E47" t="n">
-        <v>24</v>
-      </c>
       <c r="F47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G47" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
         <v>70</v>
       </c>
       <c r="E48" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F48" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G48" t="n">
-        <v>215.5</v>
+        <v>216.25</v>
       </c>
     </row>
     <row r="49">
@@ -6814,16 +6814,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="5">
@@ -6939,16 +6939,16 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10">
@@ -7064,16 +7064,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="15">
@@ -7089,16 +7089,16 @@
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -7198,7 +7198,7 @@
         <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="20">
@@ -7317,13 +7317,13 @@
         <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
         <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="25">
@@ -7342,13 +7342,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="26">
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
@@ -7448,7 +7448,7 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
         <v>12</v>
@@ -7548,7 +7548,7 @@
         <v>12</v>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="34">
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
         <v>5</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="37">
@@ -7645,10 +7645,10 @@
         <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -7845,10 +7845,10 @@
         <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -7895,10 +7895,10 @@
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -7945,10 +7945,10 @@
         <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
     </row>
   </sheetData>
@@ -8040,13 +8040,13 @@
         <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D4" t="n">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5">
@@ -8135,13 +8135,13 @@
         <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D9" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E9" t="n">
-        <v>1227</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="10">
@@ -8211,13 +8211,13 @@
         <v>58</v>
       </c>
       <c r="C13" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D13" t="n">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D14" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E14" t="n">
-        <v>1069</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15">
@@ -8249,13 +8249,13 @@
         <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D15" t="n">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="E15" t="n">
-        <v>973</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -8401,13 +8401,13 @@
         <v>66</v>
       </c>
       <c r="C23" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D23" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E23" t="n">
-        <v>1227</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="24">
@@ -8420,13 +8420,13 @@
         <v>66</v>
       </c>
       <c r="C24" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D24" t="n">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E24" t="n">
-        <v>1188</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="25">
@@ -8439,13 +8439,13 @@
         <v>68</v>
       </c>
       <c r="C25" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D25" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E25" t="n">
-        <v>1160</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D29" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E29" t="n">
-        <v>1069</v>
+        <v>915</v>
       </c>
     </row>
     <row r="30">
@@ -8534,13 +8534,13 @@
         <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D30" t="n">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="E30" t="n">
-        <v>973</v>
+        <v>919</v>
       </c>
     </row>
     <row r="31">
@@ -8553,13 +8553,13 @@
         <v>58</v>
       </c>
       <c r="C31" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D31" t="n">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E31" t="n">
-        <v>977</v>
+        <v>967</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C33" t="n">
         <v>57</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E33" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36" t="n">
         <v>38</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E36" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -8667,13 +8667,13 @@
         <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
@@ -8705,13 +8705,13 @@
         <v>66</v>
       </c>
       <c r="C39" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D39" t="n">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E39" t="n">
-        <v>1188</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="40">
@@ -8724,13 +8724,13 @@
         <v>68</v>
       </c>
       <c r="C40" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D40" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E40" t="n">
-        <v>1160</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="41">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C41" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D41" t="n">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E41" t="n">
-        <v>1172</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="42">
@@ -8781,13 +8781,13 @@
         <v>58</v>
       </c>
       <c r="C43" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D43" t="n">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E43" t="n">
-        <v>977</v>
+        <v>967</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C44" t="n">
         <v>57</v>
       </c>
       <c r="D44" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E44" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
@@ -8857,13 +8857,13 @@
         <v>29</v>
       </c>
       <c r="C47" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E47" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C48" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D48" t="n">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E48" t="n">
-        <v>1172</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="49">

--- a/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_3_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.000546</v>
+        <v>0.0005406</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003684000000000001</v>
+        <v>0.0035912</v>
       </c>
       <c r="E2" t="n">
-        <v>0.030357</v>
+        <v>0.0287193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2180022</v>
+        <v>0.208237</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06314729999999999</v>
+        <v>0.060272025</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002674999999999999</v>
+        <v>0.0002488</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0011545</v>
+        <v>0.0010969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0048022</v>
+        <v>0.0047569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0206734</v>
+        <v>0.0202904</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006724399999999999</v>
+        <v>0.006598249999999999</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0003776</v>
+        <v>0.000384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0011538</v>
+        <v>0.0013739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0042386</v>
+        <v>0.0054597</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0218588</v>
+        <v>0.0346657</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0069072</v>
+        <v>0.010470825</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0004648</v>
+        <v>0.0004287</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0027194</v>
+        <v>0.0025759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01741</v>
+        <v>0.01683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1240879</v>
+        <v>0.1163257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.036170525</v>
+        <v>0.034040075</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0004617000000000001</v>
+        <v>0.0004063000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0013765</v>
+        <v>0.0012948</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004941599999999999</v>
+        <v>0.004711600000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0192263</v>
+        <v>0.01906</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006501525</v>
+        <v>0.006368175</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0006234999999999999</v>
+        <v>0.0005910999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0038125</v>
+        <v>0.0036794</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0281771</v>
+        <v>0.027812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2160788</v>
+        <v>0.2072281999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06217297500000001</v>
+        <v>0.05982767499999998</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0006391</v>
+        <v>0.0005942000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003597599999999999</v>
+        <v>0.0035883</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0267297</v>
+        <v>0.0262958</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2037332</v>
+        <v>0.1948316</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0586749</v>
+        <v>0.056327475</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003872</v>
+        <v>0.0003461000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0010871</v>
+        <v>0.0011806</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003215</v>
+        <v>0.0049481</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0103866</v>
+        <v>0.0145884</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003768975</v>
+        <v>0.0052658</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003065</v>
+        <v>0.0003056999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0014377</v>
+        <v>0.0014255</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006045500000000001</v>
+        <v>0.0059554</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0254324</v>
+        <v>0.0245681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008305525000000001</v>
+        <v>0.008063674999999999</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.000281</v>
+        <v>0.0002782</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0011939</v>
+        <v>0.0011953</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0050425</v>
+        <v>0.0049449</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0211033</v>
+        <v>0.0208265</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006905175</v>
+        <v>0.006811225000000001</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003613</v>
+        <v>0.0003296999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0013669</v>
+        <v>0.0013577</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005241699999999999</v>
+        <v>0.0050271</v>
       </c>
       <c r="F12" t="n">
-        <v>0.021877</v>
+        <v>0.0216773</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007211725</v>
+        <v>0.00709795</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004005</v>
+        <v>0.0003966</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0012621</v>
+        <v>0.0014111</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0044928</v>
+        <v>0.0056854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0217566</v>
+        <v>0.03494200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006978</v>
+        <v>0.010608775</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004347999999999999</v>
+        <v>0.0004066</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0013109</v>
+        <v>0.0014969</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0045134</v>
+        <v>0.0057702</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0226044</v>
+        <v>0.0364468</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007215874999999999</v>
+        <v>0.011030125</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0004049</v>
+        <v>0.0004728000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0014147</v>
+        <v>0.0013412</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004932399999999999</v>
+        <v>0.0062116</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0256787</v>
+        <v>0.0395715</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008107675</v>
+        <v>0.011899275</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0004849999999999999</v>
+        <v>0.0004426</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0027005</v>
+        <v>0.0025917</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0179767</v>
+        <v>0.01713070000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1228213</v>
+        <v>0.1169551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.035995875</v>
+        <v>0.03428002500000001</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005078</v>
+        <v>0.0004737999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0027631</v>
+        <v>0.0027196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0173218</v>
+        <v>0.0169224</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1120969</v>
+        <v>0.1066147</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0331724</v>
+        <v>0.031682625</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003351</v>
+        <v>0.0003142</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0008937999999999999</v>
+        <v>0.0012731</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0029088</v>
+        <v>0.0028439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0104362</v>
+        <v>0.009858299999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003643475</v>
+        <v>0.003572375</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003003</v>
+        <v>0.0002684</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00066</v>
+        <v>0.0006847</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0017488</v>
+        <v>0.0016626</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0058041</v>
+        <v>0.007069299999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0021283</v>
+        <v>0.00242125</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003584</v>
+        <v>0.0003291</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011674</v>
+        <v>0.001103</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0037865</v>
+        <v>0.0038145</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0140926</v>
+        <v>0.0138121</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004851225000000001</v>
+        <v>0.004764674999999999</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004616000000000001</v>
+        <v>0.0004325999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0014341</v>
+        <v>0.0014327</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0049436</v>
+        <v>0.0048667</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0199467</v>
+        <v>0.0194009</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0066965</v>
+        <v>0.006533225</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0006406000000000001</v>
+        <v>0.0006385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0036825</v>
+        <v>0.0037021</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0269687</v>
+        <v>0.0263479</v>
       </c>
       <c r="F22" t="n">
-        <v>0.20486</v>
+        <v>0.1957276</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05903795</v>
+        <v>0.056604025</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004203</v>
+        <v>0.0003858</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0011084</v>
+        <v>0.0013</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0033663</v>
+        <v>0.0052062</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0113008</v>
+        <v>0.0149329</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00404895</v>
+        <v>0.005456225</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004102</v>
+        <v>0.0003773</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0012922</v>
+        <v>0.0012615</v>
       </c>
       <c r="E24" t="n">
-        <v>0.003509</v>
+        <v>0.005348800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0112542</v>
+        <v>0.0217612</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0041164</v>
+        <v>0.0071872</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004322</v>
+        <v>0.0004291</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0025646</v>
+        <v>0.001479</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0038514</v>
+        <v>0.0045635</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0139693</v>
+        <v>0.0181245</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005204375000000001</v>
+        <v>0.006149025000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003301</v>
+        <v>0.0003146</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0015485</v>
+        <v>0.0014575</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006173700000000001</v>
+        <v>0.006288199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0259852</v>
+        <v>0.0255018</v>
       </c>
       <c r="G26" t="n">
-        <v>0.008509375000000001</v>
+        <v>0.008390524999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003597</v>
+        <v>0.0003610999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0015893</v>
+        <v>0.0015325</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0062231</v>
+        <v>0.0061663</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0254515</v>
+        <v>0.0250318</v>
       </c>
       <c r="G27" t="n">
-        <v>0.008405899999999999</v>
+        <v>0.008272925</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003724</v>
+        <v>0.0003726</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0014709</v>
+        <v>0.0015131</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0053147</v>
+        <v>0.0052589</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0228021</v>
+        <v>0.022037</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007490025000000001</v>
+        <v>0.0072954</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0004310000000000001</v>
+        <v>0.0004544</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0013605</v>
+        <v>0.0015775</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0046745</v>
+        <v>0.0058296</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0237458</v>
+        <v>0.0367427</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007552950000000001</v>
+        <v>0.01115105</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0004431</v>
+        <v>0.0004335</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0014071</v>
+        <v>0.001416</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004991299999999999</v>
+        <v>0.006374199999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0260128</v>
+        <v>0.0389823</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008213575000000001</v>
+        <v>0.0118015</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0004374</v>
+        <v>0.0004504999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0013522</v>
+        <v>0.0016083</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004967500000000001</v>
+        <v>0.0072383</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0266098</v>
+        <v>0.0471414</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008341724999999999</v>
+        <v>0.014109625</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0005307000000000001</v>
+        <v>0.0005548999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0029335</v>
+        <v>0.0028723</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0177066</v>
+        <v>0.0169324</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1123257</v>
+        <v>0.1068391</v>
       </c>
       <c r="G32" t="n">
-        <v>0.033374125</v>
+        <v>0.031799675</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003758</v>
+        <v>0.0002922</v>
       </c>
       <c r="D33" t="n">
-        <v>0.001003</v>
+        <v>0.0009419999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0027288</v>
+        <v>0.0023578</v>
       </c>
       <c r="F33" t="n">
-        <v>0.009828100000000001</v>
+        <v>0.008117299999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003483925</v>
+        <v>0.002927325</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0003841</v>
+        <v>0.0003244</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0012308</v>
+        <v>0.0011349</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0028052</v>
+        <v>0.0027313</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0105294</v>
+        <v>0.0108963</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003737375</v>
+        <v>0.003771725</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0003871</v>
+        <v>0.0003481</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0009500000000000001</v>
+        <v>0.0013483</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002974800000000001</v>
+        <v>0.0028793</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0103504</v>
+        <v>0.0100264</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003665575</v>
+        <v>0.003650525</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003252</v>
+        <v>0.0003046</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0006824</v>
+        <v>0.0006055</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001889</v>
+        <v>0.0018138</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0060915</v>
+        <v>0.0072147</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002247025</v>
+        <v>0.00248465</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0002808</v>
+        <v>0.0003084</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0007123</v>
+        <v>0.0007482999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0020868</v>
+        <v>0.0025064</v>
       </c>
       <c r="F37" t="n">
-        <v>0.007346199999999999</v>
+        <v>0.0099729</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002606525</v>
+        <v>0.003384</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0004096</v>
+        <v>0.0003561</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0012078</v>
+        <v>0.0011406</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003845</v>
+        <v>0.0037343</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0141298</v>
+        <v>0.0139398</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00489805</v>
+        <v>0.0047927</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004215</v>
+        <v>0.0004014</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0013187</v>
+        <v>0.0013468</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0036742</v>
+        <v>0.0055196</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0119389</v>
+        <v>0.0224393</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004338325</v>
+        <v>0.007426775000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.00044</v>
+        <v>0.0004354</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0013157</v>
+        <v>0.0015743</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00408</v>
+        <v>0.004601100000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0145385</v>
+        <v>0.0187475</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00509355</v>
+        <v>0.006339575</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0004193000000000001</v>
+        <v>0.0004818</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0012776</v>
+        <v>0.0014282</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0040456</v>
+        <v>0.003814199999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0149416</v>
+        <v>0.0142018</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005171025000000001</v>
+        <v>0.004981499999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0003933000000000001</v>
+        <v>0.0003619</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0016665</v>
+        <v>0.001638</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0064125</v>
+        <v>0.006425700000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.026673</v>
+        <v>0.0256011</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008786325000000001</v>
+        <v>0.008506675</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0004547</v>
+        <v>0.0004732</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0013888</v>
+        <v>0.0016736</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0051654</v>
+        <v>0.007274699999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0273314</v>
+        <v>0.04786240000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0.008585074999999999</v>
+        <v>0.014320975</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003902</v>
+        <v>0.0003293</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0009990999999999999</v>
+        <v>0.0008089000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>0.002857600000000001</v>
+        <v>0.0024109</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0095739</v>
+        <v>0.0082074</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0034552</v>
+        <v>0.002939125</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004337000000000001</v>
+        <v>0.0003038</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0009966999999999999</v>
+        <v>0.0007226</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0029725</v>
+        <v>0.0024146</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0107656</v>
+        <v>0.0128624</v>
       </c>
       <c r="G45" t="n">
-        <v>0.003792124999999999</v>
+        <v>0.004075850000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0003812000000000001</v>
+        <v>0.0003618</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0012756</v>
+        <v>0.001181</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0028881</v>
+        <v>0.0028171</v>
       </c>
       <c r="F46" t="n">
-        <v>0.010706</v>
+        <v>0.0105675</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003812724999999999</v>
+        <v>0.00373185</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003426999999999999</v>
+        <v>0.0003495</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0007721000000000001</v>
+        <v>0.0008434</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0022251</v>
+        <v>0.002597</v>
       </c>
       <c r="F47" t="n">
-        <v>0.007606700000000001</v>
+        <v>0.0100498</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00273665</v>
+        <v>0.003459925</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0004853</v>
+        <v>0.0005041000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0013604</v>
+        <v>0.0015305</v>
       </c>
       <c r="E48" t="n">
-        <v>0.004343700000000001</v>
+        <v>0.0039409</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0157142</v>
+        <v>0.0147767</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005475900000000001</v>
+        <v>0.00518805</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004546</v>
+        <v>0.000352</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0010659</v>
+        <v>0.0007733</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0030921</v>
+        <v>0.002492</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0112333</v>
+        <v>0.0133362</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003961475</v>
+        <v>0.004238375</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1813,13 @@
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="5">
@@ -1938,13 +1938,13 @@
         <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
         <v>160</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -2032,19 +2032,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="14">
@@ -2063,13 +2063,13 @@
         <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -2091,10 +2091,10 @@
         <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G15" t="n">
-        <v>75.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -2285,16 +2285,16 @@
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="24">
@@ -2313,13 +2313,13 @@
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F24" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -2341,10 +2341,10 @@
         <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G25" t="n">
-        <v>75.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -2438,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="30">
@@ -2488,13 +2488,13 @@
         <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="32">
@@ -2610,16 +2610,16 @@
         <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="40">
@@ -2713,13 +2713,13 @@
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="41">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -2744,7 +2744,7 @@
         <v>160</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="42">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
         <v>8</v>
@@ -2794,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2832,19 +2832,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G45" t="n">
-        <v>21.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="46">
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
         <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -2935,16 +2935,16 @@
         <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.55634918610405</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D4" t="n">
-        <v>48.52691193458118</v>
+        <v>50.18376618407358</v>
       </c>
       <c r="E4" t="n">
-        <v>98.46803743153546</v>
+        <v>102.3675323681472</v>
       </c>
       <c r="F4" t="n">
-        <v>200.0071426749364</v>
+        <v>204.7350647362943</v>
       </c>
       <c r="G4" t="n">
-        <v>92.63961030678928</v>
+        <v>95.41778489984132</v>
       </c>
     </row>
     <row r="5">
@@ -3186,16 +3186,16 @@
         <v>24.38477631085024</v>
       </c>
       <c r="D9" t="n">
-        <v>49.35533905932738</v>
+        <v>50.18376618407358</v>
       </c>
       <c r="E9" t="n">
-        <v>98.46803743153546</v>
+        <v>104.1248916810278</v>
       </c>
       <c r="F9" t="n">
         <v>200.8355697996826</v>
       </c>
       <c r="G9" t="n">
-        <v>93.26093065034893</v>
+        <v>94.88225099390857</v>
       </c>
     </row>
     <row r="10">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.62089099732862</v>
+        <v>23.76087902741253</v>
       </c>
       <c r="D13" t="n">
-        <v>46.60059793450297</v>
+        <v>46.54043818792906</v>
       </c>
       <c r="E13" t="n">
-        <v>94.57769688972063</v>
+        <v>94.511007484849</v>
       </c>
       <c r="F13" t="n">
-        <v>190.5376445941226</v>
+        <v>190.4679384542775</v>
       </c>
       <c r="G13" t="n">
-        <v>88.58420760391871</v>
+        <v>88.82006578861703</v>
       </c>
     </row>
     <row r="14">
@@ -3314,13 +3314,13 @@
         <v>49.35533905932738</v>
       </c>
       <c r="E14" t="n">
-        <v>98.46803743153546</v>
+        <v>102.3675323681472</v>
       </c>
       <c r="F14" t="n">
-        <v>200.0071426749364</v>
+        <v>207.5634918610404</v>
       </c>
       <c r="G14" t="n">
-        <v>93.05382386916239</v>
+        <v>95.91778489984131</v>
       </c>
     </row>
     <row r="15">
@@ -3342,10 +3342,10 @@
         <v>98.46803743153546</v>
       </c>
       <c r="F15" t="n">
-        <v>198.9360748630709</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G15" t="n">
-        <v>92.3718433538229</v>
+        <v>92.22539674441617</v>
       </c>
     </row>
     <row r="16">
@@ -3436,16 +3436,16 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D19" t="n">
-        <v>49.69848480983499</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E19" t="n">
-        <v>100.8111831820431</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F19" t="n">
-        <v>203.0365799264593</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G19" t="n">
-        <v>94.27564927611036</v>
+        <v>92.22539674441617</v>
       </c>
     </row>
     <row r="20">
@@ -3539,13 +3539,13 @@
         <v>46.91573369484568</v>
       </c>
       <c r="E23" t="n">
-        <v>95.05671258281731</v>
+        <v>95.69616348029015</v>
       </c>
       <c r="F23" t="n">
-        <v>190.5376445941226</v>
+        <v>187.2110349389147</v>
       </c>
       <c r="G23" t="n">
-        <v>88.78274546727857</v>
+        <v>88.11095577784479</v>
       </c>
     </row>
     <row r="24">
@@ -3564,13 +3564,13 @@
         <v>49.35533905932738</v>
       </c>
       <c r="E24" t="n">
-        <v>98.46803743153546</v>
+        <v>104.1248916810278</v>
       </c>
       <c r="F24" t="n">
-        <v>200.8355697996826</v>
+        <v>208.0071426749365</v>
       </c>
       <c r="G24" t="n">
-        <v>93.26093065034893</v>
+        <v>96.46803743153548</v>
       </c>
     </row>
     <row r="25">
@@ -3583,19 +3583,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.38477631085024</v>
+        <v>25.21320343559643</v>
       </c>
       <c r="D25" t="n">
         <v>49.35533905932738</v>
       </c>
       <c r="E25" t="n">
-        <v>98.46803743153546</v>
+        <v>100.953318805774</v>
       </c>
       <c r="F25" t="n">
-        <v>199.7645019878171</v>
+        <v>202.492424049175</v>
       </c>
       <c r="G25" t="n">
-        <v>92.99316369738256</v>
+        <v>94.5035713374682</v>
       </c>
     </row>
     <row r="26">
@@ -3689,13 +3689,13 @@
         <v>46.54043818792906</v>
       </c>
       <c r="E29" t="n">
-        <v>94.57769688972063</v>
+        <v>94.511007484849</v>
       </c>
       <c r="F29" t="n">
-        <v>190.5376445941226</v>
+        <v>190.4679384542775</v>
       </c>
       <c r="G29" t="n">
-        <v>88.85416467479621</v>
+        <v>88.82006578861703</v>
       </c>
     </row>
     <row r="30">
@@ -3714,13 +3714,13 @@
         <v>46.60059793450297</v>
       </c>
       <c r="E30" t="n">
-        <v>94.72620467643378</v>
+        <v>94.57769688972063</v>
       </c>
       <c r="F30" t="n">
-        <v>190.5376445941226</v>
+        <v>190.4679384542775</v>
       </c>
       <c r="G30" t="n">
-        <v>88.621334550597</v>
+        <v>88.56678106895744</v>
       </c>
     </row>
     <row r="31">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23.55634918610405</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D31" t="n">
-        <v>48.52691193458118</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E31" t="n">
-        <v>98.46803743153546</v>
+        <v>101.539105243401</v>
       </c>
       <c r="F31" t="n">
-        <v>198.350288425444</v>
+        <v>207.0782104868019</v>
       </c>
       <c r="G31" t="n">
-        <v>92.22539674441617</v>
+        <v>95.58935777509511</v>
       </c>
     </row>
     <row r="32">
@@ -3861,16 +3861,16 @@
         <v>22.93245190266634</v>
       </c>
       <c r="D36" t="n">
-        <v>46.87266338875516</v>
+        <v>47.27911736770578</v>
       </c>
       <c r="E36" t="n">
-        <v>94.86994056290681</v>
+        <v>95.97244829778465</v>
       </c>
       <c r="F36" t="n">
-        <v>190.8923385147889</v>
+        <v>193.3591101579424</v>
       </c>
       <c r="G36" t="n">
-        <v>88.8918485922793</v>
+        <v>89.88578193152478</v>
       </c>
     </row>
     <row r="37">
@@ -3936,16 +3936,16 @@
         <v>22.62089099732862</v>
       </c>
       <c r="D39" t="n">
-        <v>46.55110554604754</v>
+        <v>46.91573369484568</v>
       </c>
       <c r="E39" t="n">
-        <v>95.05671258281731</v>
+        <v>95.69616348029015</v>
       </c>
       <c r="F39" t="n">
-        <v>190.5376445941226</v>
+        <v>192.8111809335069</v>
       </c>
       <c r="G39" t="n">
-        <v>88.69158843007904</v>
+        <v>89.51099227649286</v>
       </c>
     </row>
     <row r="40">
@@ -3964,13 +3964,13 @@
         <v>46.91573369484568</v>
       </c>
       <c r="E40" t="n">
-        <v>95.05671258281731</v>
+        <v>92.86918160147039</v>
       </c>
       <c r="F40" t="n">
-        <v>190.8666229152406</v>
+        <v>187.2110349389147</v>
       </c>
       <c r="G40" t="n">
-        <v>88.86499004755807</v>
+        <v>87.40421030813985</v>
       </c>
     </row>
     <row r="41">
@@ -3983,19 +3983,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.38477631085024</v>
+        <v>25.79898987322333</v>
       </c>
       <c r="D41" t="n">
-        <v>48.52691193458118</v>
+        <v>50.18376618407358</v>
       </c>
       <c r="E41" t="n">
-        <v>98.46803743153546</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F41" t="n">
         <v>199.1787155501902</v>
       </c>
       <c r="G41" t="n">
-        <v>92.63961030678928</v>
+        <v>93.61448404094219</v>
       </c>
     </row>
     <row r="42">
@@ -4033,19 +4033,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>22.62089099732862</v>
+        <v>23.76087902741253</v>
       </c>
       <c r="D43" t="n">
-        <v>46.60059793450297</v>
+        <v>46.59583581045643</v>
       </c>
       <c r="E43" t="n">
-        <v>94.57769688972063</v>
+        <v>94.52532447833548</v>
       </c>
       <c r="F43" t="n">
-        <v>190.5376445941226</v>
+        <v>190.4679384542775</v>
       </c>
       <c r="G43" t="n">
-        <v>88.58420760391871</v>
+        <v>88.8374944426205</v>
       </c>
     </row>
     <row r="44">
@@ -4083,19 +4083,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23.55634918610405</v>
+        <v>24.97056274847714</v>
       </c>
       <c r="D45" t="n">
-        <v>48.52691193458118</v>
+        <v>54.76955262170047</v>
       </c>
       <c r="E45" t="n">
-        <v>98.46803743153546</v>
+        <v>108.7106781186548</v>
       </c>
       <c r="F45" t="n">
-        <v>198.350288425444</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G45" t="n">
-        <v>92.22539674441617</v>
+        <v>97.87184335382292</v>
       </c>
     </row>
     <row r="46">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22.62089099732862</v>
+        <v>24.16851988016613</v>
       </c>
       <c r="D48" t="n">
-        <v>46.91573369484568</v>
+        <v>46.83834443104679</v>
       </c>
       <c r="E48" t="n">
-        <v>95.05671258281731</v>
+        <v>92.48855241525564</v>
       </c>
       <c r="F48" t="n">
-        <v>190.8666229152406</v>
+        <v>186.3038820133299</v>
       </c>
       <c r="G48" t="n">
-        <v>88.86499004755807</v>
+        <v>87.44982468494962</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22.62089099732862</v>
+        <v>22.92364183909941</v>
       </c>
       <c r="D49" t="n">
-        <v>46.75225471703789</v>
+        <v>46.87967797007779</v>
       </c>
       <c r="E49" t="n">
-        <v>94.9009341377288</v>
+        <v>94.86618086683202</v>
       </c>
       <c r="F49" t="n">
-        <v>191.2002359312186</v>
+        <v>190.9924090733473</v>
       </c>
       <c r="G49" t="n">
-        <v>88.86857894582849</v>
+        <v>88.91547743733915</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
         <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F4" t="n">
-        <v>539</v>
+        <v>625</v>
       </c>
       <c r="G4" t="n">
-        <v>223.5</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E9" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="F9" t="n">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="G9" t="n">
-        <v>287</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
         <v>91</v>
       </c>
       <c r="E13" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F13" t="n">
-        <v>539</v>
+        <v>625</v>
       </c>
       <c r="G13" t="n">
-        <v>223.5</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
@@ -4562,16 +4562,16 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F14" t="n">
-        <v>541</v>
+        <v>610</v>
       </c>
       <c r="G14" t="n">
-        <v>225</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="15">
@@ -4587,16 +4587,16 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E15" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F15" t="n">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="G15" t="n">
-        <v>218.5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16">
@@ -4690,13 +4690,13 @@
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
         <v>14</v>
-      </c>
-      <c r="G19" t="n">
-        <v>13.25</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D23" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E23" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="F23" t="n">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="G23" t="n">
-        <v>287</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E24" t="n">
-        <v>284</v>
+        <v>373</v>
       </c>
       <c r="F24" t="n">
-        <v>705</v>
+        <v>936</v>
       </c>
       <c r="G24" t="n">
-        <v>282</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E25" t="n">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="F25" t="n">
-        <v>551</v>
+        <v>784</v>
       </c>
       <c r="G25" t="n">
-        <v>239.5</v>
+        <v>322.5</v>
       </c>
     </row>
     <row r="26">
@@ -4937,16 +4937,16 @@
         <v>38</v>
       </c>
       <c r="D29" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F29" t="n">
-        <v>541</v>
+        <v>610</v>
       </c>
       <c r="G29" t="n">
-        <v>225</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="30">
@@ -4962,16 +4962,16 @@
         <v>37</v>
       </c>
       <c r="D30" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F30" t="n">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="G30" t="n">
-        <v>218.5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="F31" t="n">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="G31" t="n">
-        <v>225.75</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32">
@@ -5037,16 +5037,16 @@
         <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
-        <v>18.75</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="34">
@@ -5115,13 +5115,13 @@
         <v>14</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
         <v>14</v>
-      </c>
-      <c r="G36" t="n">
-        <v>13.25</v>
       </c>
     </row>
     <row r="37">
@@ -5134,19 +5134,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
         <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G37" t="n">
-        <v>15.75</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="38">
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D39" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E39" t="n">
-        <v>284</v>
+        <v>373</v>
       </c>
       <c r="F39" t="n">
-        <v>705</v>
+        <v>936</v>
       </c>
       <c r="G39" t="n">
-        <v>282</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D40" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E40" t="n">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="F40" t="n">
-        <v>551</v>
+        <v>784</v>
       </c>
       <c r="G40" t="n">
-        <v>239.5</v>
+        <v>322.5</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D41" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E41" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F41" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G41" t="n">
-        <v>256.75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D43" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E43" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="F43" t="n">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="G43" t="n">
-        <v>225.75</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44">
@@ -5312,16 +5312,16 @@
         <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G44" t="n">
-        <v>18.75</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="45">
@@ -5334,16 +5334,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G45" t="n">
         <v>23</v>
@@ -5384,19 +5384,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
         <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G47" t="n">
-        <v>15.75</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D48" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E48" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F48" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G48" t="n">
-        <v>256.75</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49">
@@ -5434,16 +5434,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G49" t="n">
         <v>23</v>
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>361</v>
+        <v>581</v>
       </c>
       <c r="G4" t="n">
-        <v>136.75</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="F9" t="n">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="G9" t="n">
-        <v>187</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="F13" t="n">
-        <v>361</v>
+        <v>581</v>
       </c>
       <c r="G13" t="n">
-        <v>136.75</v>
+        <v>205.75</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="F14" t="n">
-        <v>374</v>
+        <v>592</v>
       </c>
       <c r="G14" t="n">
-        <v>141.75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -5838,16 +5838,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
-        <v>401</v>
+        <v>557</v>
       </c>
       <c r="G15" t="n">
-        <v>149.75</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="16">
@@ -5938,16 +5938,16 @@
         <v>17</v>
       </c>
       <c r="D19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F19" t="n">
         <v>24</v>
       </c>
-      <c r="E19" t="n">
-        <v>22</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21</v>
-      </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="F23" t="n">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="G23" t="n">
-        <v>187</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="F24" t="n">
-        <v>492</v>
+        <v>650</v>
       </c>
       <c r="G24" t="n">
-        <v>194.25</v>
+        <v>239.75</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F25" t="n">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="G25" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="F29" t="n">
-        <v>374</v>
+        <v>592</v>
       </c>
       <c r="G29" t="n">
-        <v>141.75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30">
@@ -6213,16 +6213,16 @@
         <v>21</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="F30" t="n">
-        <v>401</v>
+        <v>557</v>
       </c>
       <c r="G30" t="n">
-        <v>149.75</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="F31" t="n">
-        <v>416</v>
+        <v>690</v>
       </c>
       <c r="G31" t="n">
-        <v>151.75</v>
+        <v>238.75</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F33" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
-        <v>32.25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -6363,16 +6363,16 @@
         <v>17</v>
       </c>
       <c r="D36" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" t="n">
         <v>24</v>
       </c>
-      <c r="E36" t="n">
-        <v>22</v>
-      </c>
-      <c r="F36" t="n">
-        <v>21</v>
-      </c>
       <c r="G36" t="n">
-        <v>21</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="37">
@@ -6385,19 +6385,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>23.25</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D39" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="F39" t="n">
-        <v>492</v>
+        <v>650</v>
       </c>
       <c r="G39" t="n">
-        <v>194.25</v>
+        <v>239.75</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E40" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F40" t="n">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="G40" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41">
@@ -6488,16 +6488,16 @@
         <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E41" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="F41" t="n">
-        <v>569</v>
+        <v>284</v>
       </c>
       <c r="G41" t="n">
-        <v>216.25</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E43" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="F43" t="n">
-        <v>416</v>
+        <v>690</v>
       </c>
       <c r="G43" t="n">
-        <v>151.75</v>
+        <v>238.75</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E44" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G44" t="n">
-        <v>32.25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E45" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -6635,19 +6635,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F47" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G47" t="n">
-        <v>23.25</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="48">
@@ -6663,16 +6663,16 @@
         <v>27</v>
       </c>
       <c r="D48" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E48" t="n">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="F48" t="n">
-        <v>569</v>
+        <v>284</v>
       </c>
       <c r="G48" t="n">
-        <v>216.25</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="49">
@@ -6685,19 +6685,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D49" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G49" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -6811,19 +6811,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>16.5</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="5">
@@ -6939,16 +6939,16 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -7048,7 +7048,7 @@
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -7067,13 +7067,13 @@
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>14.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -7092,13 +7092,13 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -7189,16 +7189,16 @@
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -7292,13 +7292,13 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="24">
@@ -7311,19 +7311,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>12.75</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="25">
@@ -7336,19 +7336,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
         <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="26">
@@ -7486,19 +7486,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
         <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="32">
@@ -7614,16 +7614,16 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -7692,13 +7692,13 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="40">
@@ -7717,13 +7717,13 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="41">
@@ -7736,19 +7736,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
         <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -7836,19 +7836,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>10</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="46">
@@ -7911,19 +7911,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
         <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="49">
@@ -7939,16 +7939,16 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D4" t="n">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="E4" t="n">
-        <v>900</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D9" t="n">
-        <v>477</v>
+        <v>607</v>
       </c>
       <c r="E9" t="n">
-        <v>1179</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D13" t="n">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="E13" t="n">
-        <v>900</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D14" t="n">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="E14" t="n">
-        <v>915</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="15">
@@ -8249,13 +8249,13 @@
         <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D15" t="n">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="E15" t="n">
-        <v>919</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="16">
@@ -8325,13 +8325,13 @@
         <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D23" t="n">
-        <v>477</v>
+        <v>607</v>
       </c>
       <c r="E23" t="n">
-        <v>1179</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D24" t="n">
-        <v>463</v>
+        <v>599</v>
       </c>
       <c r="E24" t="n">
-        <v>1197</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D25" t="n">
-        <v>447</v>
+        <v>513</v>
       </c>
       <c r="E25" t="n">
-        <v>1063</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D29" t="n">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="E29" t="n">
-        <v>915</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="30">
@@ -8534,13 +8534,13 @@
         <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="E30" t="n">
-        <v>919</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C31" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D31" t="n">
-        <v>347</v>
+        <v>427</v>
       </c>
       <c r="E31" t="n">
-        <v>967</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -8648,13 +8648,13 @@
         <v>29</v>
       </c>
       <c r="C36" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D39" t="n">
-        <v>463</v>
+        <v>599</v>
       </c>
       <c r="E39" t="n">
-        <v>1197</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D40" t="n">
-        <v>447</v>
+        <v>513</v>
       </c>
       <c r="E40" t="n">
-        <v>1063</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="41">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C41" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D41" t="n">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="E41" t="n">
-        <v>1183</v>
+        <v>900</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C43" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D43" t="n">
-        <v>347</v>
+        <v>427</v>
       </c>
       <c r="E43" t="n">
-        <v>967</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C44" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E44" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C45" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D47" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C48" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D48" t="n">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="E48" t="n">
-        <v>1183</v>
+        <v>900</v>
       </c>
     </row>
     <row r="49">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C49" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
